--- a/rtl/pbit_register_file.xlsx
+++ b/rtl/pbit_register_file.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Study_material\Study_material\Pbit\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Study_material\Study_material\Pbit\pbit_kings_reduced\pbit_kings\rtl\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{679E1739-D625-489E-922D-5BC0C79F4BE0}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B2419F56-F9C3-4A94-9F66-6879E50FBDEA}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="15360" windowHeight="12645" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1058" uniqueCount="479">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="909" uniqueCount="400">
   <si>
     <t>LEVEL</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -72,9 +72,6 @@
   </si>
   <si>
     <t>1</t>
-  </si>
-  <si>
-    <t>1</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
@@ -83,9 +80,6 @@
   </si>
   <si>
     <t>3</t>
-  </si>
-  <si>
-    <t>3</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
@@ -94,9 +88,6 @@
   </si>
   <si>
     <t>4</t>
-  </si>
-  <si>
-    <t>4</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
@@ -112,13 +103,6 @@
   </si>
   <si>
     <t>正常RUN_START也会自动清除</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>6</t>
-  </si>
-  <si>
-    <t>6</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
@@ -147,24 +131,12 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>ERROR_CLEAR
-清除所有错误标志</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>[31:7]</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>RESERVED</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>0</t>
     <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>2</t>
   </si>
   <si>
     <t>2</t>
@@ -176,10 +148,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>直连</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>RUN_BUSY
 阵列运行标志</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -195,11 +163,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>ERROR
-存在错误</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>RESEVERED</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -208,135 +171,7 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>[7:0]</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>[15:8]</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>[31:16]</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>ROWS
-当前阵列行数</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>COLS
-当前阵列列数</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>N_SPIN
-Node总数</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>0x000C</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>ARRAY_PARAM</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>ERROR_STATUS</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>7</t>
-  </si>
-  <si>
-    <t>8</t>
-  </si>
-  <si>
-    <t>9</t>
-  </si>
-  <si>
-    <t>12</t>
-  </si>
-  <si>
-    <t>13</t>
-  </si>
-  <si>
-    <t>W1C</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>ADDR_ERR
-访问非法地址</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>WR_TO_RO
-写只读寄存器</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>RD_TO_WO
-读只写寄存器</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>NODE_CFG_WHILE_RUN
-运行时修改Node配置</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>EDGE_CFG_WHILE_RUN
-运行时修改Edge配置</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>RUN_WITHOUT_CFG_DONE
-未配置完成就启动运行</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>RUN_WHEN_BUSY
-阵列运行时再次启动</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>NODE_ROW_OOR
-Node行号越界</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>NODE_COL_OOR
-Node列号越界</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>EDGE_ROW_OOR
-Edge行号越界</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>EDGE_COL_OOR
-Edge列号越界</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>EDGE_TYPE_ERR
-Edge类型非法</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>UART_FRAME_ERR
-UART帧格式错误</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>UART_OVERFLOW
-UART接收溢出</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>0x0010</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
@@ -397,11 +232,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>SEED_VALID
-SEED字段有效</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>BIAS_VALID
 BIAS字段有效</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -457,15 +287,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>NODE_RDATA_CFG</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>NODE_RDATA_SEED
-32bitLSFR的初始化种子</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>EDGE_TARGET</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -535,10 +356,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>2</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>APPLY_EDGE
 写入目标edge配置</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -549,24 +366,7 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>READBACK_EDGE
-读回目标edge配置</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>EDGE_RDATA</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>[31:3]</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>RO</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>SPIN_DATA</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
@@ -726,19 +526,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>W1C</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>SNAP_ADDR_OOR
-锁存SNAP寄存器读取地址越界</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>RESERVED</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>NUM_SWEEP
 一次运行包含的sweep数量</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -777,51 +564,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>W1C</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>14</t>
-  </si>
-  <si>
-    <t>NODE_TAEGE_MODE_ERR
-Node Target mode非法</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>该错误动作不会访问任何寄存器</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>run_busy时收到NODE_CMD写指令
-该错误动作不会发出控制信号</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>run_busy时收到EDGE_CMD写指令
-该错误动作不会发出控制信号</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>run_start_pulse的时候cfg_done为0
-该错误动作不会发出控制信号</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>run_busy时收到run_start_pulse
-该错误动作不会发出控制信号</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>该错误动作不会选中任何结点配置寄存器
-且读操作返回0</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>该错误动作不会发出锁存信号</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>[23:0]</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -831,11 +573,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>EDGE_PROB
-Edge采样概率</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>I0_LEVEL0</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -1754,14 +1491,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>0x00E8</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>0x00EC</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>0x00F0</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -1771,10 +1500,6 @@
   </si>
   <si>
     <t>0x00F8</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>0x00FC</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
@@ -1879,11 +1604,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>BIAS_PROB
-BIAS采样概率</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>EDFE_PROB
 Edge采样概率</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -1893,10 +1613,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>[10:4]</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>7bit</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -1909,50 +1625,7 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>[31:11]</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>[31:9]</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>NODE_RDATA_SEED</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>W1C</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>10</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>11</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>SEED_ROW_OOR
-Seed行号越界</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>SEED_COL_OOR
-Seed列号越界</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>15</t>
-  </si>
-  <si>
-    <t>16</t>
-  </si>
-  <si>
-    <t>17</t>
-  </si>
-  <si>
-    <t>[31:18]</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
@@ -1974,21 +1647,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>READBACK_SEED
-将目标作用域的配置读回到
-NODE_RDATA_SEED</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>根据NODE_TARGET内容</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>READBACK_CFG
-将目标作用域的配置读回到NODE_RDATA_CFG</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>APPLY_SEED
 将NODE_SEED写入目标作用域</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -2012,20 +1670,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>[31:8]</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>NODE_CMD_DONE
-Node配置动作已经完成</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>EDGE_CMD_DONE
-Edge配置动作已经完成</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>[28:24]</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -2048,6 +1692,22 @@
   </si>
   <si>
     <t>[7:3]</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>[31:6]</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>[31:4]</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>[31:2]</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>SPIN_DATA</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -2101,21 +1761,15 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="3">
+  <fills count="2">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFF00"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
   </fills>
-  <borders count="2">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -2123,20 +1777,11 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border diagonalDown="1">
-      <left/>
-      <right/>
-      <top/>
-      <bottom/>
-      <diagonal style="thin">
-        <color auto="1"/>
-      </diagonal>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="28">
+  <cellXfs count="23">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -2156,12 +1801,6 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -2172,9 +1811,6 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -2184,38 +1820,32 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="0" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -2497,7 +2127,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:G577"/>
+  <dimension ref="A1:G539"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="12.625" customWidth="1"/>
@@ -2529,7 +2159,7 @@
         <v>4</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>21</v>
+        <v>18</v>
       </c>
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.2">
@@ -2551,13 +2181,13 @@
         <v>9</v>
       </c>
       <c r="D3" s="3" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="E3" s="4">
         <v>0</v>
       </c>
       <c r="F3" s="2" t="s">
-        <v>25</v>
+        <v>20</v>
       </c>
     </row>
     <row r="4" spans="1:7" ht="28.5" x14ac:dyDescent="0.2">
@@ -2565,13 +2195,13 @@
       <c r="B4" s="3"/>
       <c r="C4" s="3"/>
       <c r="D4" s="3" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="E4" s="4">
         <v>1</v>
       </c>
       <c r="F4" s="2" t="s">
-        <v>26</v>
+        <v>21</v>
       </c>
     </row>
     <row r="5" spans="1:7" ht="28.5" x14ac:dyDescent="0.2">
@@ -2579,13 +2209,13 @@
       <c r="B5" s="3"/>
       <c r="C5" s="3"/>
       <c r="D5" s="3" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="E5" s="4">
         <v>2</v>
       </c>
       <c r="F5" s="2" t="s">
-        <v>438</v>
+        <v>374</v>
       </c>
     </row>
     <row r="6" spans="1:7" ht="28.5" x14ac:dyDescent="0.2">
@@ -2593,13 +2223,13 @@
       <c r="B6" s="3"/>
       <c r="C6" s="3"/>
       <c r="D6" s="3" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="E6" s="4" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="F6" s="2" t="s">
-        <v>27</v>
+        <v>22</v>
       </c>
     </row>
     <row r="7" spans="1:7" ht="28.5" x14ac:dyDescent="0.2">
@@ -2607,13 +2237,13 @@
       <c r="B7" s="3"/>
       <c r="C7" s="3"/>
       <c r="D7" s="3" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="E7" s="4" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="F7" s="2" t="s">
-        <v>28</v>
+        <v>23</v>
       </c>
     </row>
     <row r="8" spans="1:7" ht="28.5" x14ac:dyDescent="0.2">
@@ -2621,113 +2251,112 @@
       <c r="B8" s="3"/>
       <c r="C8" s="3"/>
       <c r="D8" s="3" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="E8" s="4" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="F8" s="2" t="s">
-        <v>29</v>
+        <v>24</v>
       </c>
       <c r="G8" s="3" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="9" spans="1:7" ht="28.5" x14ac:dyDescent="0.2">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A9" s="3"/>
       <c r="B9" s="3"/>
       <c r="C9" s="3"/>
-      <c r="D9" s="3" t="s">
-        <v>16</v>
-      </c>
+      <c r="D9" s="3"/>
       <c r="E9" s="4" t="s">
-        <v>24</v>
-      </c>
-      <c r="F9" s="2" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A10" s="3"/>
-      <c r="B10" s="3"/>
-      <c r="C10" s="3"/>
-      <c r="D10" s="3"/>
-      <c r="E10" s="4" t="s">
-        <v>31</v>
-      </c>
-      <c r="F10" s="1" t="s">
-        <v>32</v>
+        <v>396</v>
+      </c>
+      <c r="F9" s="1" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7" ht="28.5" x14ac:dyDescent="0.2">
+      <c r="A10" s="6"/>
+      <c r="B10" s="11" t="s">
+        <v>114</v>
+      </c>
+      <c r="C10" s="11" t="s">
+        <v>115</v>
+      </c>
+      <c r="D10" s="11" t="s">
+        <v>116</v>
+      </c>
+      <c r="E10" s="12" t="s">
+        <v>129</v>
+      </c>
+      <c r="F10" s="13" t="s">
+        <v>120</v>
+      </c>
+      <c r="G10" s="14" t="s">
+        <v>392</v>
       </c>
     </row>
     <row r="11" spans="1:7" ht="28.5" x14ac:dyDescent="0.2">
-      <c r="A11" s="6"/>
-      <c r="B11" s="14" t="s">
-        <v>161</v>
-      </c>
-      <c r="C11" s="14" t="s">
-        <v>162</v>
-      </c>
-      <c r="D11" s="14" t="s">
-        <v>163</v>
-      </c>
-      <c r="E11" s="15" t="s">
-        <v>189</v>
-      </c>
-      <c r="F11" s="16" t="s">
-        <v>170</v>
-      </c>
-      <c r="G11" s="22" t="s">
-        <v>475</v>
-      </c>
-    </row>
-    <row r="12" spans="1:7" ht="28.5" x14ac:dyDescent="0.2">
-      <c r="A12" s="10"/>
-      <c r="B12" s="14"/>
-      <c r="C12" s="14"/>
-      <c r="D12" s="14"/>
-      <c r="E12" s="15" t="s">
-        <v>473</v>
-      </c>
-      <c r="F12" s="16" t="s">
-        <v>171</v>
-      </c>
-      <c r="G12" s="23" t="s">
-        <v>476</v>
-      </c>
-    </row>
-    <row r="13" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A13" s="10"/>
-      <c r="B13" s="10"/>
-      <c r="C13" s="10"/>
-      <c r="D13" s="10"/>
-      <c r="E13" s="11" t="s">
-        <v>474</v>
-      </c>
-      <c r="F13" s="12" t="s">
-        <v>32</v>
-      </c>
-      <c r="G13" s="10"/>
+      <c r="A11" s="8"/>
+      <c r="B11" s="11"/>
+      <c r="C11" s="11"/>
+      <c r="D11" s="11"/>
+      <c r="E11" s="12" t="s">
+        <v>390</v>
+      </c>
+      <c r="F11" s="13" t="s">
+        <v>121</v>
+      </c>
+      <c r="G11" s="15" t="s">
+        <v>393</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A12" s="8"/>
+      <c r="B12" s="8"/>
+      <c r="C12" s="8"/>
+      <c r="D12" s="8"/>
+      <c r="E12" s="9" t="s">
+        <v>391</v>
+      </c>
+      <c r="F12" s="10" t="s">
+        <v>25</v>
+      </c>
+      <c r="G12" s="15"/>
+    </row>
+    <row r="13" spans="1:7" ht="28.5" x14ac:dyDescent="0.2">
+      <c r="A13" s="3"/>
+      <c r="B13" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="C13" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="D13" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="E13" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="F13" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="G13" s="8"/>
     </row>
     <row r="14" spans="1:7" ht="28.5" x14ac:dyDescent="0.2">
       <c r="A14" s="3"/>
-      <c r="B14" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="C14" s="3" t="s">
-        <v>43</v>
-      </c>
+      <c r="B14" s="3"/>
+      <c r="C14" s="3"/>
       <c r="D14" s="3" t="s">
         <v>10</v>
       </c>
       <c r="E14" s="4" t="s">
-        <v>33</v>
+        <v>11</v>
       </c>
       <c r="F14" s="2" t="s">
-        <v>36</v>
-      </c>
-      <c r="G14" s="3" t="s">
-        <v>37</v>
-      </c>
+        <v>29</v>
+      </c>
+      <c r="G14" s="3"/>
     </row>
     <row r="15" spans="1:7" ht="28.5" x14ac:dyDescent="0.2">
       <c r="A15" s="3"/>
@@ -2737,527 +2366,492 @@
         <v>10</v>
       </c>
       <c r="E15" s="4" t="s">
-        <v>12</v>
+        <v>27</v>
       </c>
       <c r="F15" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="G15" s="3" t="s">
-        <v>37</v>
-      </c>
+        <v>30</v>
+      </c>
+      <c r="G15" s="3"/>
     </row>
     <row r="16" spans="1:7" ht="28.5" x14ac:dyDescent="0.2">
-      <c r="A16" s="3"/>
-      <c r="B16" s="3"/>
-      <c r="C16" s="3"/>
-      <c r="D16" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="E16" s="4" t="s">
-        <v>35</v>
-      </c>
-      <c r="F16" s="2" t="s">
-        <v>39</v>
-      </c>
-      <c r="G16" s="3" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="17" spans="1:7" ht="28.5" x14ac:dyDescent="0.2">
-      <c r="A17" s="6"/>
-      <c r="B17" s="6"/>
-      <c r="C17" s="6"/>
-      <c r="D17" s="14" t="s">
-        <v>178</v>
-      </c>
-      <c r="E17" s="15" t="s">
-        <v>15</v>
-      </c>
-      <c r="F17" s="20" t="s">
-        <v>471</v>
-      </c>
-      <c r="G17" s="9"/>
+      <c r="A16" s="6"/>
+      <c r="B16" s="6"/>
+      <c r="C16" s="6"/>
+      <c r="D16" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="E16" s="12" t="s">
+        <v>13</v>
+      </c>
+      <c r="F16" s="13" t="s">
+        <v>31</v>
+      </c>
+      <c r="G16" s="7"/>
+    </row>
+    <row r="17" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A17" s="3"/>
+      <c r="B17" s="3"/>
+      <c r="C17" s="3"/>
+      <c r="D17" s="3"/>
+      <c r="E17" s="4" t="s">
+        <v>397</v>
+      </c>
+      <c r="F17" s="2" t="s">
+        <v>32</v>
+      </c>
     </row>
     <row r="18" spans="1:7" ht="28.5" x14ac:dyDescent="0.2">
-      <c r="A18" s="6"/>
-      <c r="B18" s="6"/>
-      <c r="C18" s="6"/>
-      <c r="D18" s="14" t="s">
-        <v>178</v>
-      </c>
-      <c r="E18" s="15" t="s">
-        <v>18</v>
-      </c>
-      <c r="F18" s="20" t="s">
-        <v>472</v>
-      </c>
-      <c r="G18" s="9"/>
-    </row>
-    <row r="19" spans="1:7" ht="28.5" x14ac:dyDescent="0.2">
-      <c r="A19" s="6"/>
-      <c r="B19" s="6"/>
-      <c r="C19" s="6"/>
-      <c r="D19" s="14" t="s">
-        <v>178</v>
-      </c>
-      <c r="E19" s="15" t="s">
-        <v>20</v>
-      </c>
-      <c r="F19" s="16" t="s">
-        <v>40</v>
-      </c>
-      <c r="G19" s="9"/>
+      <c r="A18" s="8"/>
+      <c r="B18" s="3" t="s">
+        <v>122</v>
+      </c>
+      <c r="C18" s="3" t="s">
+        <v>125</v>
+      </c>
+      <c r="D18" s="3" t="s">
+        <v>123</v>
+      </c>
+      <c r="E18" s="4" t="s">
+        <v>124</v>
+      </c>
+      <c r="F18" s="2" t="s">
+        <v>117</v>
+      </c>
+      <c r="G18" s="3" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="19" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A19" s="8"/>
+      <c r="B19" s="3"/>
+      <c r="C19" s="3"/>
+      <c r="D19" s="3"/>
+      <c r="E19" s="4" t="s">
+        <v>126</v>
+      </c>
+      <c r="F19" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="G19" s="3"/>
     </row>
     <row r="20" spans="1:7" ht="28.5" x14ac:dyDescent="0.2">
-      <c r="A20" s="3"/>
-      <c r="B20" s="3"/>
-      <c r="C20" s="3"/>
+      <c r="A20" s="8"/>
+      <c r="B20" s="3" t="s">
+        <v>131</v>
+      </c>
+      <c r="C20" s="3" t="s">
+        <v>137</v>
+      </c>
       <c r="D20" s="3" t="s">
-        <v>10</v>
+        <v>132</v>
       </c>
       <c r="E20" s="4" t="s">
-        <v>24</v>
+        <v>133</v>
       </c>
       <c r="F20" s="2" t="s">
-        <v>41</v>
-      </c>
+        <v>142</v>
+      </c>
+      <c r="G20" s="3"/>
     </row>
     <row r="21" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A21" s="3"/>
+      <c r="A21" s="8"/>
       <c r="B21" s="3"/>
       <c r="C21" s="3"/>
-      <c r="D21" s="3"/>
+      <c r="D21" s="3" t="s">
+        <v>132</v>
+      </c>
       <c r="E21" s="4" t="s">
-        <v>31</v>
+        <v>138</v>
       </c>
       <c r="F21" s="2" t="s">
-        <v>42</v>
-      </c>
+        <v>32</v>
+      </c>
+      <c r="G21" s="3"/>
     </row>
     <row r="22" spans="1:7" ht="28.5" x14ac:dyDescent="0.2">
-      <c r="A22" s="3"/>
-      <c r="B22" s="3" t="s">
-        <v>51</v>
-      </c>
-      <c r="C22" s="3" t="s">
-        <v>50</v>
-      </c>
+      <c r="A22" s="8"/>
+      <c r="B22" s="3"/>
+      <c r="C22" s="3"/>
       <c r="D22" s="3" t="s">
-        <v>10</v>
+        <v>132</v>
       </c>
       <c r="E22" s="4" t="s">
-        <v>44</v>
+        <v>134</v>
       </c>
       <c r="F22" s="2" t="s">
-        <v>47</v>
-      </c>
-      <c r="G22" s="3">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="23" spans="1:7" ht="28.5" x14ac:dyDescent="0.2">
-      <c r="A23" s="3"/>
+        <v>143</v>
+      </c>
+      <c r="G22" s="3"/>
+    </row>
+    <row r="23" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A23" s="8"/>
       <c r="B23" s="3"/>
       <c r="C23" s="3"/>
       <c r="D23" s="3" t="s">
-        <v>10</v>
+        <v>132</v>
       </c>
       <c r="E23" s="4" t="s">
-        <v>45</v>
+        <v>139</v>
       </c>
       <c r="F23" s="2" t="s">
-        <v>48</v>
-      </c>
-      <c r="G23" s="3">
-        <v>40</v>
-      </c>
+        <v>32</v>
+      </c>
+      <c r="G23" s="3"/>
     </row>
     <row r="24" spans="1:7" ht="28.5" x14ac:dyDescent="0.2">
-      <c r="A24" s="3"/>
+      <c r="A24" s="8"/>
       <c r="B24" s="3"/>
       <c r="C24" s="3"/>
       <c r="D24" s="3" t="s">
-        <v>10</v>
+        <v>132</v>
       </c>
       <c r="E24" s="4" t="s">
-        <v>46</v>
+        <v>135</v>
       </c>
       <c r="F24" s="2" t="s">
-        <v>49</v>
-      </c>
-      <c r="G24" s="3">
-        <v>1600</v>
-      </c>
-    </row>
-    <row r="25" spans="1:7" ht="28.5" x14ac:dyDescent="0.2">
-      <c r="A25" s="10"/>
-      <c r="B25" s="10" t="s">
-        <v>52</v>
-      </c>
-      <c r="C25" s="10" t="s">
-        <v>73</v>
-      </c>
-      <c r="D25" s="10" t="s">
-        <v>58</v>
-      </c>
-      <c r="E25" s="7" t="s">
-        <v>33</v>
-      </c>
-      <c r="F25" s="8" t="s">
-        <v>59</v>
-      </c>
-      <c r="G25" s="10" t="s">
+        <v>144</v>
+      </c>
+      <c r="G24" s="3"/>
+    </row>
+    <row r="25" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A25" s="8"/>
+      <c r="B25" s="3"/>
+      <c r="C25" s="3"/>
+      <c r="D25" s="3" t="s">
+        <v>132</v>
+      </c>
+      <c r="E25" s="4" t="s">
+        <v>140</v>
+      </c>
+      <c r="F25" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="G25" s="3"/>
+    </row>
+    <row r="26" spans="1:7" ht="28.5" x14ac:dyDescent="0.2">
+      <c r="A26" s="8"/>
+      <c r="B26" s="3"/>
+      <c r="C26" s="3"/>
+      <c r="D26" s="3" t="s">
+        <v>132</v>
+      </c>
+      <c r="E26" s="4" t="s">
+        <v>136</v>
+      </c>
+      <c r="F26" s="2" t="s">
+        <v>145</v>
+      </c>
+      <c r="G26" s="3"/>
+    </row>
+    <row r="27" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A27" s="8"/>
+      <c r="B27" s="3"/>
+      <c r="C27" s="3"/>
+      <c r="D27" s="3" t="s">
+        <v>132</v>
+      </c>
+      <c r="E27" s="4" t="s">
+        <v>141</v>
+      </c>
+      <c r="F27" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="G27" s="3"/>
+    </row>
+    <row r="28" spans="1:7" ht="28.5" x14ac:dyDescent="0.2">
+      <c r="A28" s="8"/>
+      <c r="B28" s="3" t="s">
+        <v>169</v>
+      </c>
+      <c r="C28" s="3" t="s">
+        <v>154</v>
+      </c>
+      <c r="D28" s="3" t="s">
+        <v>132</v>
+      </c>
+      <c r="E28" s="4" t="s">
+        <v>133</v>
+      </c>
+      <c r="F28" s="2" t="s">
         <v>182</v>
       </c>
-    </row>
-    <row r="26" spans="1:7" ht="28.5" x14ac:dyDescent="0.2">
-      <c r="A26" s="10"/>
-      <c r="B26" s="10"/>
-      <c r="C26" s="10"/>
-      <c r="D26" s="10" t="s">
-        <v>58</v>
-      </c>
-      <c r="E26" s="7" t="s">
-        <v>11</v>
-      </c>
-      <c r="F26" s="8" t="s">
-        <v>60</v>
-      </c>
-      <c r="G26" s="10" t="s">
-        <v>182</v>
-      </c>
-    </row>
-    <row r="27" spans="1:7" ht="28.5" x14ac:dyDescent="0.2">
-      <c r="A27" s="10"/>
-      <c r="B27" s="10"/>
-      <c r="C27" s="10"/>
-      <c r="D27" s="10" t="s">
-        <v>58</v>
-      </c>
-      <c r="E27" s="7" t="s">
-        <v>34</v>
-      </c>
-      <c r="F27" s="8" t="s">
-        <v>61</v>
-      </c>
-      <c r="G27" s="10" t="s">
-        <v>182</v>
-      </c>
-    </row>
-    <row r="28" spans="1:7" ht="28.5" x14ac:dyDescent="0.2">
-      <c r="A28" s="10"/>
-      <c r="B28" s="10"/>
-      <c r="C28" s="10"/>
-      <c r="D28" s="10" t="s">
-        <v>58</v>
-      </c>
-      <c r="E28" s="7" t="s">
-        <v>14</v>
-      </c>
-      <c r="F28" s="8" t="s">
-        <v>62</v>
-      </c>
-      <c r="G28" s="13" t="s">
+      <c r="G28" s="3"/>
+    </row>
+    <row r="29" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A29" s="8"/>
+      <c r="B29" s="3"/>
+      <c r="C29" s="3"/>
+      <c r="D29" s="3" t="s">
+        <v>132</v>
+      </c>
+      <c r="E29" s="4" t="s">
+        <v>138</v>
+      </c>
+      <c r="F29" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="G29" s="3"/>
+    </row>
+    <row r="30" spans="1:7" ht="28.5" x14ac:dyDescent="0.2">
+      <c r="A30" s="8"/>
+      <c r="B30" s="3"/>
+      <c r="C30" s="3"/>
+      <c r="D30" s="3" t="s">
+        <v>132</v>
+      </c>
+      <c r="E30" s="4" t="s">
+        <v>134</v>
+      </c>
+      <c r="F30" s="2" t="s">
         <v>183</v>
       </c>
-    </row>
-    <row r="29" spans="1:7" ht="28.5" x14ac:dyDescent="0.2">
-      <c r="A29" s="10"/>
-      <c r="B29" s="10"/>
-      <c r="C29" s="10"/>
-      <c r="D29" s="10" t="s">
-        <v>58</v>
-      </c>
-      <c r="E29" s="7" t="s">
-        <v>17</v>
-      </c>
-      <c r="F29" s="8" t="s">
-        <v>63</v>
-      </c>
-      <c r="G29" s="13" t="s">
+      <c r="G30" s="3"/>
+    </row>
+    <row r="31" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A31" s="8"/>
+      <c r="B31" s="3"/>
+      <c r="C31" s="3"/>
+      <c r="D31" s="3" t="s">
+        <v>132</v>
+      </c>
+      <c r="E31" s="4" t="s">
+        <v>139</v>
+      </c>
+      <c r="F31" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="G31" s="3"/>
+    </row>
+    <row r="32" spans="1:7" ht="28.5" x14ac:dyDescent="0.2">
+      <c r="A32" s="8"/>
+      <c r="B32" s="3"/>
+      <c r="C32" s="3"/>
+      <c r="D32" s="3" t="s">
+        <v>132</v>
+      </c>
+      <c r="E32" s="4" t="s">
+        <v>135</v>
+      </c>
+      <c r="F32" s="2" t="s">
         <v>184</v>
       </c>
-    </row>
-    <row r="30" spans="1:7" ht="28.5" x14ac:dyDescent="0.2">
-      <c r="A30" s="10"/>
-      <c r="B30" s="10"/>
-      <c r="C30" s="10"/>
-      <c r="D30" s="10" t="s">
-        <v>58</v>
-      </c>
-      <c r="E30" s="7" t="s">
-        <v>19</v>
-      </c>
-      <c r="F30" s="8" t="s">
-        <v>64</v>
-      </c>
-      <c r="G30" s="13" t="s">
+      <c r="G32" s="3"/>
+    </row>
+    <row r="33" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A33" s="8"/>
+      <c r="B33" s="3"/>
+      <c r="C33" s="3"/>
+      <c r="D33" s="3" t="s">
+        <v>132</v>
+      </c>
+      <c r="E33" s="4" t="s">
+        <v>140</v>
+      </c>
+      <c r="F33" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="G33" s="3"/>
+    </row>
+    <row r="34" spans="1:7" ht="28.5" x14ac:dyDescent="0.2">
+      <c r="A34" s="8"/>
+      <c r="B34" s="3"/>
+      <c r="C34" s="3"/>
+      <c r="D34" s="3" t="s">
+        <v>132</v>
+      </c>
+      <c r="E34" s="4" t="s">
+        <v>136</v>
+      </c>
+      <c r="F34" s="2" t="s">
         <v>185</v>
       </c>
-    </row>
-    <row r="31" spans="1:7" ht="28.5" x14ac:dyDescent="0.2">
-      <c r="A31" s="10"/>
-      <c r="B31" s="10"/>
-      <c r="C31" s="10"/>
-      <c r="D31" s="10" t="s">
-        <v>58</v>
-      </c>
-      <c r="E31" s="7" t="s">
-        <v>23</v>
-      </c>
-      <c r="F31" s="8" t="s">
-        <v>65</v>
-      </c>
-      <c r="G31" s="13" t="s">
+      <c r="G34" s="3"/>
+    </row>
+    <row r="35" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A35" s="8"/>
+      <c r="B35" s="3"/>
+      <c r="C35" s="3"/>
+      <c r="D35" s="3" t="s">
+        <v>132</v>
+      </c>
+      <c r="E35" s="4" t="s">
+        <v>141</v>
+      </c>
+      <c r="F35" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="G35" s="3"/>
+    </row>
+    <row r="36" spans="1:7" ht="28.5" x14ac:dyDescent="0.2">
+      <c r="A36" s="8"/>
+      <c r="B36" s="3" t="s">
+        <v>170</v>
+      </c>
+      <c r="C36" s="3" t="s">
+        <v>155</v>
+      </c>
+      <c r="D36" s="3" t="s">
+        <v>132</v>
+      </c>
+      <c r="E36" s="4" t="s">
+        <v>133</v>
+      </c>
+      <c r="F36" s="2" t="s">
         <v>186</v>
       </c>
-    </row>
-    <row r="32" spans="1:7" ht="42.75" x14ac:dyDescent="0.2">
-      <c r="A32" s="10"/>
-      <c r="B32" s="10"/>
-      <c r="C32" s="10"/>
-      <c r="D32" s="10" t="s">
-        <v>179</v>
-      </c>
-      <c r="E32" s="7" t="s">
-        <v>53</v>
-      </c>
-      <c r="F32" s="8" t="s">
-        <v>181</v>
-      </c>
-      <c r="G32" s="13" t="s">
+      <c r="G36" s="3"/>
+    </row>
+    <row r="37" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A37" s="3"/>
+      <c r="B37" s="3"/>
+      <c r="C37" s="3"/>
+      <c r="D37" s="3" t="s">
+        <v>132</v>
+      </c>
+      <c r="E37" s="4" t="s">
+        <v>138</v>
+      </c>
+      <c r="F37" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="G37" s="3"/>
+    </row>
+    <row r="38" spans="1:7" ht="28.5" x14ac:dyDescent="0.2">
+      <c r="A38" s="3"/>
+      <c r="B38" s="3"/>
+      <c r="C38" s="3"/>
+      <c r="D38" s="3" t="s">
+        <v>132</v>
+      </c>
+      <c r="E38" s="4" t="s">
+        <v>134</v>
+      </c>
+      <c r="F38" s="2" t="s">
         <v>187</v>
       </c>
-    </row>
-    <row r="33" spans="1:7" ht="42.75" x14ac:dyDescent="0.2">
-      <c r="A33" s="10"/>
-      <c r="B33" s="10"/>
-      <c r="C33" s="10"/>
-      <c r="D33" s="10" t="s">
-        <v>58</v>
-      </c>
-      <c r="E33" s="7" t="s">
-        <v>54</v>
-      </c>
-      <c r="F33" s="8" t="s">
-        <v>66</v>
-      </c>
-      <c r="G33" s="13" t="s">
-        <v>187</v>
-      </c>
-    </row>
-    <row r="34" spans="1:7" ht="42.75" x14ac:dyDescent="0.2">
-      <c r="A34" s="10"/>
-      <c r="B34" s="10"/>
-      <c r="C34" s="10"/>
-      <c r="D34" s="10" t="s">
-        <v>58</v>
-      </c>
-      <c r="E34" s="7" t="s">
-        <v>55</v>
-      </c>
-      <c r="F34" s="8" t="s">
-        <v>67</v>
-      </c>
-      <c r="G34" s="13" t="s">
-        <v>187</v>
-      </c>
-    </row>
-    <row r="35" spans="1:7" ht="42.75" x14ac:dyDescent="0.2">
-      <c r="A35" s="10"/>
-      <c r="B35" s="10"/>
-      <c r="C35" s="10"/>
-      <c r="D35" s="10" t="s">
-        <v>449</v>
-      </c>
-      <c r="E35" s="7" t="s">
-        <v>450</v>
-      </c>
-      <c r="F35" s="19" t="s">
-        <v>452</v>
-      </c>
-      <c r="G35" s="13" t="s">
-        <v>187</v>
-      </c>
-    </row>
-    <row r="36" spans="1:7" ht="42.75" x14ac:dyDescent="0.2">
-      <c r="A36" s="10"/>
-      <c r="B36" s="10"/>
-      <c r="C36" s="10"/>
-      <c r="D36" s="10" t="s">
-        <v>449</v>
-      </c>
-      <c r="E36" s="7" t="s">
-        <v>451</v>
-      </c>
-      <c r="F36" s="19" t="s">
-        <v>453</v>
-      </c>
-      <c r="G36" s="13" t="s">
-        <v>187</v>
-      </c>
-    </row>
-    <row r="37" spans="1:7" ht="42.75" x14ac:dyDescent="0.2">
-      <c r="A37" s="10"/>
-      <c r="B37" s="10"/>
-      <c r="C37" s="10"/>
-      <c r="D37" s="10" t="s">
-        <v>58</v>
-      </c>
-      <c r="E37" s="7" t="s">
-        <v>56</v>
-      </c>
-      <c r="F37" s="8" t="s">
-        <v>68</v>
-      </c>
-      <c r="G37" s="13" t="s">
-        <v>187</v>
-      </c>
-    </row>
-    <row r="38" spans="1:7" ht="42.75" x14ac:dyDescent="0.2">
-      <c r="A38" s="10"/>
-      <c r="B38" s="10"/>
-      <c r="C38" s="10"/>
-      <c r="D38" s="10" t="s">
-        <v>58</v>
-      </c>
-      <c r="E38" s="7" t="s">
-        <v>57</v>
-      </c>
-      <c r="F38" s="8" t="s">
-        <v>69</v>
-      </c>
-      <c r="G38" s="13" t="s">
-        <v>187</v>
-      </c>
-    </row>
-    <row r="39" spans="1:7" ht="42.75" x14ac:dyDescent="0.2">
-      <c r="A39" s="10"/>
-      <c r="B39" s="10"/>
-      <c r="C39" s="10"/>
-      <c r="D39" s="10" t="s">
-        <v>58</v>
-      </c>
-      <c r="E39" s="7" t="s">
-        <v>180</v>
-      </c>
-      <c r="F39" s="8" t="s">
-        <v>70</v>
-      </c>
-      <c r="G39" s="13" t="s">
-        <v>187</v>
-      </c>
+      <c r="G38" s="3"/>
+    </row>
+    <row r="39" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A39" s="3"/>
+      <c r="B39" s="3"/>
+      <c r="C39" s="3"/>
+      <c r="D39" s="3" t="s">
+        <v>132</v>
+      </c>
+      <c r="E39" s="4" t="s">
+        <v>139</v>
+      </c>
+      <c r="F39" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="G39" s="3"/>
     </row>
     <row r="40" spans="1:7" ht="28.5" x14ac:dyDescent="0.2">
-      <c r="A40" s="10"/>
-      <c r="B40" s="10"/>
-      <c r="C40" s="10"/>
-      <c r="D40" s="10" t="s">
-        <v>58</v>
-      </c>
-      <c r="E40" s="7" t="s">
-        <v>454</v>
-      </c>
-      <c r="F40" s="8" t="s">
-        <v>71</v>
-      </c>
-      <c r="G40" s="10"/>
-    </row>
-    <row r="41" spans="1:7" ht="28.5" x14ac:dyDescent="0.2">
-      <c r="A41" s="10"/>
-      <c r="B41" s="10"/>
-      <c r="C41" s="10"/>
-      <c r="D41" s="10" t="s">
-        <v>58</v>
-      </c>
-      <c r="E41" s="7" t="s">
-        <v>455</v>
-      </c>
-      <c r="F41" s="8" t="s">
-        <v>72</v>
-      </c>
-      <c r="G41" s="10"/>
+      <c r="A40" s="3"/>
+      <c r="B40" s="3"/>
+      <c r="C40" s="3"/>
+      <c r="D40" s="3" t="s">
+        <v>132</v>
+      </c>
+      <c r="E40" s="4" t="s">
+        <v>135</v>
+      </c>
+      <c r="F40" s="2" t="s">
+        <v>188</v>
+      </c>
+      <c r="G40" s="3"/>
+    </row>
+    <row r="41" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A41" s="3"/>
+      <c r="B41" s="3"/>
+      <c r="C41" s="3"/>
+      <c r="D41" s="3" t="s">
+        <v>132</v>
+      </c>
+      <c r="E41" s="4" t="s">
+        <v>140</v>
+      </c>
+      <c r="F41" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="G41" s="3"/>
     </row>
     <row r="42" spans="1:7" ht="28.5" x14ac:dyDescent="0.2">
-      <c r="A42" s="10"/>
-      <c r="B42" s="10"/>
-      <c r="C42" s="10"/>
-      <c r="D42" s="10" t="s">
-        <v>167</v>
-      </c>
-      <c r="E42" s="7" t="s">
-        <v>456</v>
-      </c>
-      <c r="F42" s="8" t="s">
-        <v>168</v>
-      </c>
-      <c r="G42" s="10" t="s">
-        <v>188</v>
-      </c>
+      <c r="A42" s="3"/>
+      <c r="B42" s="3"/>
+      <c r="C42" s="3"/>
+      <c r="D42" s="3" t="s">
+        <v>132</v>
+      </c>
+      <c r="E42" s="4" t="s">
+        <v>136</v>
+      </c>
+      <c r="F42" s="2" t="s">
+        <v>189</v>
+      </c>
+      <c r="G42" s="3"/>
     </row>
     <row r="43" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A43" s="10"/>
-      <c r="B43" s="10"/>
-      <c r="C43" s="10"/>
-      <c r="D43" s="10"/>
-      <c r="E43" s="7" t="s">
-        <v>457</v>
-      </c>
-      <c r="F43" s="17" t="s">
+      <c r="A43" s="3"/>
+      <c r="B43" s="3"/>
+      <c r="C43" s="3"/>
+      <c r="D43" s="3" t="s">
+        <v>132</v>
+      </c>
+      <c r="E43" s="4" t="s">
+        <v>141</v>
+      </c>
+      <c r="F43" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="G43" s="10"/>
+      <c r="G43" s="3"/>
     </row>
     <row r="44" spans="1:7" ht="28.5" x14ac:dyDescent="0.2">
       <c r="A44" s="3"/>
       <c r="B44" s="3" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="C44" s="3" t="s">
-        <v>175</v>
+        <v>156</v>
       </c>
       <c r="D44" s="3" t="s">
-        <v>173</v>
+        <v>132</v>
       </c>
       <c r="E44" s="4" t="s">
-        <v>174</v>
+        <v>133</v>
       </c>
       <c r="F44" s="2" t="s">
-        <v>164</v>
-      </c>
-      <c r="G44" s="3" t="s">
-        <v>166</v>
-      </c>
+        <v>190</v>
+      </c>
+      <c r="G44" s="3"/>
     </row>
     <row r="45" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A45" s="3"/>
       <c r="B45" s="3"/>
       <c r="C45" s="3"/>
-      <c r="D45" s="3"/>
+      <c r="D45" s="3" t="s">
+        <v>132</v>
+      </c>
       <c r="E45" s="4" t="s">
-        <v>176</v>
+        <v>138</v>
       </c>
       <c r="F45" s="2" t="s">
-        <v>42</v>
+        <v>32</v>
       </c>
       <c r="G45" s="3"/>
     </row>
     <row r="46" spans="1:7" ht="28.5" x14ac:dyDescent="0.2">
       <c r="A46" s="3"/>
-      <c r="B46" s="3" t="s">
-        <v>192</v>
-      </c>
-      <c r="C46" s="3" t="s">
-        <v>198</v>
-      </c>
+      <c r="B46" s="3"/>
+      <c r="C46" s="3"/>
       <c r="D46" s="3" t="s">
-        <v>193</v>
+        <v>132</v>
       </c>
       <c r="E46" s="4" t="s">
-        <v>194</v>
+        <v>134</v>
       </c>
       <c r="F46" s="2" t="s">
-        <v>203</v>
+        <v>191</v>
       </c>
       <c r="G46" s="3"/>
     </row>
@@ -3266,13 +2860,13 @@
       <c r="B47" s="3"/>
       <c r="C47" s="3"/>
       <c r="D47" s="3" t="s">
-        <v>193</v>
+        <v>132</v>
       </c>
       <c r="E47" s="4" t="s">
-        <v>199</v>
+        <v>139</v>
       </c>
       <c r="F47" s="2" t="s">
-        <v>42</v>
+        <v>32</v>
       </c>
       <c r="G47" s="3"/>
     </row>
@@ -3281,13 +2875,13 @@
       <c r="B48" s="3"/>
       <c r="C48" s="3"/>
       <c r="D48" s="3" t="s">
-        <v>193</v>
+        <v>132</v>
       </c>
       <c r="E48" s="4" t="s">
-        <v>195</v>
+        <v>135</v>
       </c>
       <c r="F48" s="2" t="s">
-        <v>204</v>
+        <v>192</v>
       </c>
       <c r="G48" s="3"/>
     </row>
@@ -3296,13 +2890,13 @@
       <c r="B49" s="3"/>
       <c r="C49" s="3"/>
       <c r="D49" s="3" t="s">
-        <v>193</v>
+        <v>132</v>
       </c>
       <c r="E49" s="4" t="s">
-        <v>200</v>
+        <v>140</v>
       </c>
       <c r="F49" s="2" t="s">
-        <v>42</v>
+        <v>32</v>
       </c>
       <c r="G49" s="3"/>
     </row>
@@ -3311,13 +2905,13 @@
       <c r="B50" s="3"/>
       <c r="C50" s="3"/>
       <c r="D50" s="3" t="s">
+        <v>132</v>
+      </c>
+      <c r="E50" s="4" t="s">
+        <v>136</v>
+      </c>
+      <c r="F50" s="2" t="s">
         <v>193</v>
-      </c>
-      <c r="E50" s="4" t="s">
-        <v>196</v>
-      </c>
-      <c r="F50" s="2" t="s">
-        <v>205</v>
       </c>
       <c r="G50" s="3"/>
     </row>
@@ -3326,28 +2920,32 @@
       <c r="B51" s="3"/>
       <c r="C51" s="3"/>
       <c r="D51" s="3" t="s">
-        <v>193</v>
+        <v>132</v>
       </c>
       <c r="E51" s="4" t="s">
-        <v>201</v>
-      </c>
-      <c r="F51" s="2" t="s">
-        <v>42</v>
+        <v>141</v>
+      </c>
+      <c r="F51" s="1" t="s">
+        <v>32</v>
       </c>
       <c r="G51" s="3"/>
     </row>
     <row r="52" spans="1:7" ht="28.5" x14ac:dyDescent="0.2">
       <c r="A52" s="3"/>
-      <c r="B52" s="3"/>
-      <c r="C52" s="3"/>
+      <c r="B52" s="3" t="s">
+        <v>172</v>
+      </c>
+      <c r="C52" s="3" t="s">
+        <v>157</v>
+      </c>
       <c r="D52" s="3" t="s">
-        <v>193</v>
+        <v>132</v>
       </c>
       <c r="E52" s="4" t="s">
-        <v>197</v>
+        <v>133</v>
       </c>
       <c r="F52" s="2" t="s">
-        <v>206</v>
+        <v>194</v>
       </c>
       <c r="G52" s="3"/>
     </row>
@@ -3356,32 +2954,28 @@
       <c r="B53" s="3"/>
       <c r="C53" s="3"/>
       <c r="D53" s="3" t="s">
-        <v>193</v>
+        <v>132</v>
       </c>
       <c r="E53" s="4" t="s">
-        <v>202</v>
-      </c>
-      <c r="F53" s="1" t="s">
-        <v>42</v>
+        <v>138</v>
+      </c>
+      <c r="F53" s="2" t="s">
+        <v>32</v>
       </c>
       <c r="G53" s="3"/>
     </row>
     <row r="54" spans="1:7" ht="28.5" x14ac:dyDescent="0.2">
       <c r="A54" s="3"/>
-      <c r="B54" s="3" t="s">
-        <v>230</v>
-      </c>
-      <c r="C54" s="3" t="s">
-        <v>215</v>
-      </c>
+      <c r="B54" s="3"/>
+      <c r="C54" s="3"/>
       <c r="D54" s="3" t="s">
-        <v>193</v>
+        <v>132</v>
       </c>
       <c r="E54" s="4" t="s">
-        <v>194</v>
+        <v>134</v>
       </c>
       <c r="F54" s="2" t="s">
-        <v>243</v>
+        <v>195</v>
       </c>
       <c r="G54" s="3"/>
     </row>
@@ -3390,13 +2984,13 @@
       <c r="B55" s="3"/>
       <c r="C55" s="3"/>
       <c r="D55" s="3" t="s">
-        <v>193</v>
+        <v>132</v>
       </c>
       <c r="E55" s="4" t="s">
-        <v>199</v>
+        <v>139</v>
       </c>
       <c r="F55" s="2" t="s">
-        <v>42</v>
+        <v>32</v>
       </c>
       <c r="G55" s="3"/>
     </row>
@@ -3405,13 +2999,13 @@
       <c r="B56" s="3"/>
       <c r="C56" s="3"/>
       <c r="D56" s="3" t="s">
-        <v>193</v>
+        <v>132</v>
       </c>
       <c r="E56" s="4" t="s">
-        <v>195</v>
+        <v>135</v>
       </c>
       <c r="F56" s="2" t="s">
-        <v>244</v>
+        <v>196</v>
       </c>
       <c r="G56" s="3"/>
     </row>
@@ -3420,13 +3014,13 @@
       <c r="B57" s="3"/>
       <c r="C57" s="3"/>
       <c r="D57" s="3" t="s">
-        <v>193</v>
+        <v>132</v>
       </c>
       <c r="E57" s="4" t="s">
-        <v>200</v>
+        <v>140</v>
       </c>
       <c r="F57" s="2" t="s">
-        <v>42</v>
+        <v>32</v>
       </c>
       <c r="G57" s="3"/>
     </row>
@@ -3435,13 +3029,13 @@
       <c r="B58" s="3"/>
       <c r="C58" s="3"/>
       <c r="D58" s="3" t="s">
-        <v>193</v>
+        <v>132</v>
       </c>
       <c r="E58" s="4" t="s">
-        <v>196</v>
+        <v>136</v>
       </c>
       <c r="F58" s="2" t="s">
-        <v>245</v>
+        <v>197</v>
       </c>
       <c r="G58" s="3"/>
     </row>
@@ -3450,28 +3044,32 @@
       <c r="B59" s="3"/>
       <c r="C59" s="3"/>
       <c r="D59" s="3" t="s">
-        <v>193</v>
+        <v>132</v>
       </c>
       <c r="E59" s="4" t="s">
-        <v>201</v>
-      </c>
-      <c r="F59" s="2" t="s">
-        <v>42</v>
+        <v>141</v>
+      </c>
+      <c r="F59" s="1" t="s">
+        <v>32</v>
       </c>
       <c r="G59" s="3"/>
     </row>
     <row r="60" spans="1:7" ht="28.5" x14ac:dyDescent="0.2">
       <c r="A60" s="3"/>
-      <c r="B60" s="3"/>
-      <c r="C60" s="3"/>
+      <c r="B60" s="3" t="s">
+        <v>173</v>
+      </c>
+      <c r="C60" s="3" t="s">
+        <v>158</v>
+      </c>
       <c r="D60" s="3" t="s">
-        <v>193</v>
+        <v>132</v>
       </c>
       <c r="E60" s="4" t="s">
-        <v>197</v>
+        <v>133</v>
       </c>
       <c r="F60" s="2" t="s">
-        <v>246</v>
+        <v>198</v>
       </c>
       <c r="G60" s="3"/>
     </row>
@@ -3480,32 +3078,28 @@
       <c r="B61" s="3"/>
       <c r="C61" s="3"/>
       <c r="D61" s="3" t="s">
-        <v>193</v>
+        <v>132</v>
       </c>
       <c r="E61" s="4" t="s">
-        <v>202</v>
-      </c>
-      <c r="F61" s="1" t="s">
-        <v>42</v>
+        <v>138</v>
+      </c>
+      <c r="F61" s="2" t="s">
+        <v>32</v>
       </c>
       <c r="G61" s="3"/>
     </row>
     <row r="62" spans="1:7" ht="28.5" x14ac:dyDescent="0.2">
       <c r="A62" s="3"/>
-      <c r="B62" s="3" t="s">
-        <v>231</v>
-      </c>
-      <c r="C62" s="3" t="s">
-        <v>216</v>
-      </c>
+      <c r="B62" s="3"/>
+      <c r="C62" s="3"/>
       <c r="D62" s="3" t="s">
-        <v>193</v>
+        <v>132</v>
       </c>
       <c r="E62" s="4" t="s">
-        <v>194</v>
+        <v>134</v>
       </c>
       <c r="F62" s="2" t="s">
-        <v>247</v>
+        <v>199</v>
       </c>
       <c r="G62" s="3"/>
     </row>
@@ -3514,13 +3108,13 @@
       <c r="B63" s="3"/>
       <c r="C63" s="3"/>
       <c r="D63" s="3" t="s">
-        <v>193</v>
+        <v>132</v>
       </c>
       <c r="E63" s="4" t="s">
-        <v>199</v>
+        <v>139</v>
       </c>
       <c r="F63" s="2" t="s">
-        <v>42</v>
+        <v>32</v>
       </c>
       <c r="G63" s="3"/>
     </row>
@@ -3529,13 +3123,13 @@
       <c r="B64" s="3"/>
       <c r="C64" s="3"/>
       <c r="D64" s="3" t="s">
-        <v>193</v>
+        <v>132</v>
       </c>
       <c r="E64" s="4" t="s">
-        <v>195</v>
+        <v>135</v>
       </c>
       <c r="F64" s="2" t="s">
-        <v>248</v>
+        <v>200</v>
       </c>
       <c r="G64" s="3"/>
     </row>
@@ -3544,13 +3138,13 @@
       <c r="B65" s="3"/>
       <c r="C65" s="3"/>
       <c r="D65" s="3" t="s">
-        <v>193</v>
+        <v>132</v>
       </c>
       <c r="E65" s="4" t="s">
-        <v>200</v>
+        <v>140</v>
       </c>
       <c r="F65" s="2" t="s">
-        <v>42</v>
+        <v>32</v>
       </c>
       <c r="G65" s="3"/>
     </row>
@@ -3559,13 +3153,13 @@
       <c r="B66" s="3"/>
       <c r="C66" s="3"/>
       <c r="D66" s="3" t="s">
-        <v>193</v>
+        <v>132</v>
       </c>
       <c r="E66" s="4" t="s">
-        <v>196</v>
+        <v>136</v>
       </c>
       <c r="F66" s="2" t="s">
-        <v>249</v>
+        <v>201</v>
       </c>
       <c r="G66" s="3"/>
     </row>
@@ -3574,28 +3168,32 @@
       <c r="B67" s="3"/>
       <c r="C67" s="3"/>
       <c r="D67" s="3" t="s">
-        <v>193</v>
+        <v>132</v>
       </c>
       <c r="E67" s="4" t="s">
-        <v>201</v>
-      </c>
-      <c r="F67" s="2" t="s">
-        <v>42</v>
+        <v>141</v>
+      </c>
+      <c r="F67" s="1" t="s">
+        <v>32</v>
       </c>
       <c r="G67" s="3"/>
     </row>
     <row r="68" spans="1:7" ht="28.5" x14ac:dyDescent="0.2">
       <c r="A68" s="3"/>
-      <c r="B68" s="3"/>
-      <c r="C68" s="3"/>
+      <c r="B68" s="3" t="s">
+        <v>174</v>
+      </c>
+      <c r="C68" s="3" t="s">
+        <v>159</v>
+      </c>
       <c r="D68" s="3" t="s">
-        <v>193</v>
+        <v>132</v>
       </c>
       <c r="E68" s="4" t="s">
-        <v>197</v>
+        <v>133</v>
       </c>
       <c r="F68" s="2" t="s">
-        <v>250</v>
+        <v>202</v>
       </c>
       <c r="G68" s="3"/>
     </row>
@@ -3604,32 +3202,28 @@
       <c r="B69" s="3"/>
       <c r="C69" s="3"/>
       <c r="D69" s="3" t="s">
-        <v>193</v>
+        <v>132</v>
       </c>
       <c r="E69" s="4" t="s">
-        <v>202</v>
-      </c>
-      <c r="F69" s="1" t="s">
-        <v>42</v>
+        <v>138</v>
+      </c>
+      <c r="F69" s="2" t="s">
+        <v>32</v>
       </c>
       <c r="G69" s="3"/>
     </row>
     <row r="70" spans="1:7" ht="28.5" x14ac:dyDescent="0.2">
       <c r="A70" s="3"/>
-      <c r="B70" s="3" t="s">
-        <v>232</v>
-      </c>
-      <c r="C70" s="3" t="s">
-        <v>217</v>
-      </c>
+      <c r="B70" s="3"/>
+      <c r="C70" s="3"/>
       <c r="D70" s="3" t="s">
-        <v>193</v>
+        <v>132</v>
       </c>
       <c r="E70" s="4" t="s">
-        <v>194</v>
+        <v>134</v>
       </c>
       <c r="F70" s="2" t="s">
-        <v>251</v>
+        <v>203</v>
       </c>
       <c r="G70" s="3"/>
     </row>
@@ -3638,13 +3232,13 @@
       <c r="B71" s="3"/>
       <c r="C71" s="3"/>
       <c r="D71" s="3" t="s">
-        <v>193</v>
+        <v>132</v>
       </c>
       <c r="E71" s="4" t="s">
-        <v>199</v>
+        <v>139</v>
       </c>
       <c r="F71" s="2" t="s">
-        <v>42</v>
+        <v>32</v>
       </c>
       <c r="G71" s="3"/>
     </row>
@@ -3653,13 +3247,13 @@
       <c r="B72" s="3"/>
       <c r="C72" s="3"/>
       <c r="D72" s="3" t="s">
-        <v>193</v>
+        <v>132</v>
       </c>
       <c r="E72" s="4" t="s">
-        <v>195</v>
+        <v>135</v>
       </c>
       <c r="F72" s="2" t="s">
-        <v>252</v>
+        <v>212</v>
       </c>
       <c r="G72" s="3"/>
     </row>
@@ -3668,13 +3262,13 @@
       <c r="B73" s="3"/>
       <c r="C73" s="3"/>
       <c r="D73" s="3" t="s">
-        <v>193</v>
+        <v>132</v>
       </c>
       <c r="E73" s="4" t="s">
-        <v>200</v>
+        <v>140</v>
       </c>
       <c r="F73" s="2" t="s">
-        <v>42</v>
+        <v>32</v>
       </c>
       <c r="G73" s="3"/>
     </row>
@@ -3683,13 +3277,13 @@
       <c r="B74" s="3"/>
       <c r="C74" s="3"/>
       <c r="D74" s="3" t="s">
-        <v>193</v>
+        <v>132</v>
       </c>
       <c r="E74" s="4" t="s">
-        <v>196</v>
+        <v>136</v>
       </c>
       <c r="F74" s="2" t="s">
-        <v>253</v>
+        <v>204</v>
       </c>
       <c r="G74" s="3"/>
     </row>
@@ -3698,28 +3292,32 @@
       <c r="B75" s="3"/>
       <c r="C75" s="3"/>
       <c r="D75" s="3" t="s">
-        <v>193</v>
+        <v>132</v>
       </c>
       <c r="E75" s="4" t="s">
-        <v>201</v>
+        <v>141</v>
       </c>
       <c r="F75" s="2" t="s">
-        <v>42</v>
+        <v>32</v>
       </c>
       <c r="G75" s="3"/>
     </row>
     <row r="76" spans="1:7" ht="28.5" x14ac:dyDescent="0.2">
       <c r="A76" s="3"/>
-      <c r="B76" s="3"/>
-      <c r="C76" s="3"/>
+      <c r="B76" s="3" t="s">
+        <v>153</v>
+      </c>
+      <c r="C76" s="3" t="s">
+        <v>160</v>
+      </c>
       <c r="D76" s="3" t="s">
-        <v>193</v>
+        <v>132</v>
       </c>
       <c r="E76" s="4" t="s">
-        <v>197</v>
+        <v>133</v>
       </c>
       <c r="F76" s="2" t="s">
-        <v>254</v>
+        <v>205</v>
       </c>
       <c r="G76" s="3"/>
     </row>
@@ -3728,32 +3326,28 @@
       <c r="B77" s="3"/>
       <c r="C77" s="3"/>
       <c r="D77" s="3" t="s">
-        <v>193</v>
+        <v>132</v>
       </c>
       <c r="E77" s="4" t="s">
-        <v>202</v>
+        <v>138</v>
       </c>
       <c r="F77" s="1" t="s">
-        <v>42</v>
+        <v>32</v>
       </c>
       <c r="G77" s="3"/>
     </row>
     <row r="78" spans="1:7" ht="28.5" x14ac:dyDescent="0.2">
       <c r="A78" s="3"/>
-      <c r="B78" s="3" t="s">
-        <v>233</v>
-      </c>
-      <c r="C78" s="3" t="s">
-        <v>218</v>
-      </c>
+      <c r="B78" s="3"/>
+      <c r="C78" s="3"/>
       <c r="D78" s="3" t="s">
-        <v>193</v>
+        <v>132</v>
       </c>
       <c r="E78" s="4" t="s">
-        <v>194</v>
+        <v>134</v>
       </c>
       <c r="F78" s="2" t="s">
-        <v>255</v>
+        <v>206</v>
       </c>
       <c r="G78" s="3"/>
     </row>
@@ -3762,13 +3356,13 @@
       <c r="B79" s="3"/>
       <c r="C79" s="3"/>
       <c r="D79" s="3" t="s">
-        <v>193</v>
+        <v>132</v>
       </c>
       <c r="E79" s="4" t="s">
-        <v>199</v>
+        <v>139</v>
       </c>
       <c r="F79" s="2" t="s">
-        <v>42</v>
+        <v>32</v>
       </c>
       <c r="G79" s="3"/>
     </row>
@@ -3777,13 +3371,13 @@
       <c r="B80" s="3"/>
       <c r="C80" s="3"/>
       <c r="D80" s="3" t="s">
-        <v>193</v>
+        <v>132</v>
       </c>
       <c r="E80" s="4" t="s">
-        <v>195</v>
+        <v>135</v>
       </c>
       <c r="F80" s="2" t="s">
-        <v>256</v>
+        <v>207</v>
       </c>
       <c r="G80" s="3"/>
     </row>
@@ -3792,13 +3386,13 @@
       <c r="B81" s="3"/>
       <c r="C81" s="3"/>
       <c r="D81" s="3" t="s">
-        <v>193</v>
+        <v>132</v>
       </c>
       <c r="E81" s="4" t="s">
-        <v>200</v>
+        <v>140</v>
       </c>
       <c r="F81" s="2" t="s">
-        <v>42</v>
+        <v>32</v>
       </c>
       <c r="G81" s="3"/>
     </row>
@@ -3807,13 +3401,13 @@
       <c r="B82" s="3"/>
       <c r="C82" s="3"/>
       <c r="D82" s="3" t="s">
-        <v>193</v>
+        <v>132</v>
       </c>
       <c r="E82" s="4" t="s">
-        <v>196</v>
+        <v>136</v>
       </c>
       <c r="F82" s="2" t="s">
-        <v>257</v>
+        <v>208</v>
       </c>
       <c r="G82" s="3"/>
     </row>
@@ -3822,28 +3416,32 @@
       <c r="B83" s="3"/>
       <c r="C83" s="3"/>
       <c r="D83" s="3" t="s">
-        <v>193</v>
+        <v>132</v>
       </c>
       <c r="E83" s="4" t="s">
-        <v>201</v>
+        <v>141</v>
       </c>
       <c r="F83" s="2" t="s">
-        <v>42</v>
+        <v>32</v>
       </c>
       <c r="G83" s="3"/>
     </row>
     <row r="84" spans="1:7" ht="28.5" x14ac:dyDescent="0.2">
       <c r="A84" s="3"/>
-      <c r="B84" s="3"/>
-      <c r="C84" s="3"/>
+      <c r="B84" s="3" t="s">
+        <v>175</v>
+      </c>
+      <c r="C84" s="3" t="s">
+        <v>161</v>
+      </c>
       <c r="D84" s="3" t="s">
-        <v>193</v>
+        <v>132</v>
       </c>
       <c r="E84" s="4" t="s">
-        <v>197</v>
+        <v>133</v>
       </c>
       <c r="F84" s="2" t="s">
-        <v>258</v>
+        <v>209</v>
       </c>
       <c r="G84" s="3"/>
     </row>
@@ -3852,32 +3450,28 @@
       <c r="B85" s="3"/>
       <c r="C85" s="3"/>
       <c r="D85" s="3" t="s">
-        <v>193</v>
+        <v>132</v>
       </c>
       <c r="E85" s="4" t="s">
-        <v>202</v>
+        <v>138</v>
       </c>
       <c r="F85" s="1" t="s">
-        <v>42</v>
+        <v>32</v>
       </c>
       <c r="G85" s="3"/>
     </row>
     <row r="86" spans="1:7" ht="28.5" x14ac:dyDescent="0.2">
       <c r="A86" s="3"/>
-      <c r="B86" s="3" t="s">
-        <v>234</v>
-      </c>
-      <c r="C86" s="3" t="s">
-        <v>219</v>
-      </c>
+      <c r="B86" s="3"/>
+      <c r="C86" s="3"/>
       <c r="D86" s="3" t="s">
-        <v>193</v>
+        <v>132</v>
       </c>
       <c r="E86" s="4" t="s">
-        <v>194</v>
+        <v>134</v>
       </c>
       <c r="F86" s="2" t="s">
-        <v>259</v>
+        <v>210</v>
       </c>
       <c r="G86" s="3"/>
     </row>
@@ -3886,13 +3480,13 @@
       <c r="B87" s="3"/>
       <c r="C87" s="3"/>
       <c r="D87" s="3" t="s">
-        <v>193</v>
+        <v>132</v>
       </c>
       <c r="E87" s="4" t="s">
-        <v>199</v>
+        <v>139</v>
       </c>
       <c r="F87" s="2" t="s">
-        <v>42</v>
+        <v>32</v>
       </c>
       <c r="G87" s="3"/>
     </row>
@@ -3901,13 +3495,13 @@
       <c r="B88" s="3"/>
       <c r="C88" s="3"/>
       <c r="D88" s="3" t="s">
-        <v>193</v>
+        <v>132</v>
       </c>
       <c r="E88" s="4" t="s">
-        <v>195</v>
+        <v>135</v>
       </c>
       <c r="F88" s="2" t="s">
-        <v>260</v>
+        <v>211</v>
       </c>
       <c r="G88" s="3"/>
     </row>
@@ -3916,13 +3510,13 @@
       <c r="B89" s="3"/>
       <c r="C89" s="3"/>
       <c r="D89" s="3" t="s">
-        <v>193</v>
+        <v>132</v>
       </c>
       <c r="E89" s="4" t="s">
-        <v>200</v>
+        <v>140</v>
       </c>
       <c r="F89" s="2" t="s">
-        <v>42</v>
+        <v>32</v>
       </c>
       <c r="G89" s="3"/>
     </row>
@@ -3931,13 +3525,13 @@
       <c r="B90" s="3"/>
       <c r="C90" s="3"/>
       <c r="D90" s="3" t="s">
-        <v>193</v>
+        <v>132</v>
       </c>
       <c r="E90" s="4" t="s">
-        <v>196</v>
+        <v>136</v>
       </c>
       <c r="F90" s="2" t="s">
-        <v>261</v>
+        <v>213</v>
       </c>
       <c r="G90" s="3"/>
     </row>
@@ -3946,28 +3540,32 @@
       <c r="B91" s="3"/>
       <c r="C91" s="3"/>
       <c r="D91" s="3" t="s">
-        <v>193</v>
+        <v>132</v>
       </c>
       <c r="E91" s="4" t="s">
-        <v>201</v>
-      </c>
-      <c r="F91" s="2" t="s">
-        <v>42</v>
+        <v>141</v>
+      </c>
+      <c r="F91" s="1" t="s">
+        <v>32</v>
       </c>
       <c r="G91" s="3"/>
     </row>
     <row r="92" spans="1:7" ht="28.5" x14ac:dyDescent="0.2">
       <c r="A92" s="3"/>
-      <c r="B92" s="3"/>
-      <c r="C92" s="3"/>
+      <c r="B92" s="3" t="s">
+        <v>153</v>
+      </c>
+      <c r="C92" s="3" t="s">
+        <v>162</v>
+      </c>
       <c r="D92" s="3" t="s">
-        <v>193</v>
+        <v>132</v>
       </c>
       <c r="E92" s="4" t="s">
-        <v>197</v>
+        <v>133</v>
       </c>
       <c r="F92" s="2" t="s">
-        <v>262</v>
+        <v>214</v>
       </c>
       <c r="G92" s="3"/>
     </row>
@@ -3976,32 +3574,28 @@
       <c r="B93" s="3"/>
       <c r="C93" s="3"/>
       <c r="D93" s="3" t="s">
-        <v>193</v>
+        <v>132</v>
       </c>
       <c r="E93" s="4" t="s">
-        <v>202</v>
-      </c>
-      <c r="F93" s="1" t="s">
-        <v>42</v>
+        <v>138</v>
+      </c>
+      <c r="F93" s="2" t="s">
+        <v>32</v>
       </c>
       <c r="G93" s="3"/>
     </row>
     <row r="94" spans="1:7" ht="28.5" x14ac:dyDescent="0.2">
       <c r="A94" s="3"/>
-      <c r="B94" s="3" t="s">
-        <v>235</v>
-      </c>
-      <c r="C94" s="3" t="s">
-        <v>220</v>
-      </c>
+      <c r="B94" s="3"/>
+      <c r="C94" s="3"/>
       <c r="D94" s="3" t="s">
-        <v>193</v>
+        <v>132</v>
       </c>
       <c r="E94" s="4" t="s">
-        <v>194</v>
+        <v>134</v>
       </c>
       <c r="F94" s="2" t="s">
-        <v>263</v>
+        <v>215</v>
       </c>
       <c r="G94" s="3"/>
     </row>
@@ -4010,13 +3604,13 @@
       <c r="B95" s="3"/>
       <c r="C95" s="3"/>
       <c r="D95" s="3" t="s">
-        <v>193</v>
+        <v>132</v>
       </c>
       <c r="E95" s="4" t="s">
-        <v>199</v>
+        <v>139</v>
       </c>
       <c r="F95" s="2" t="s">
-        <v>42</v>
+        <v>32</v>
       </c>
       <c r="G95" s="3"/>
     </row>
@@ -4025,13 +3619,13 @@
       <c r="B96" s="3"/>
       <c r="C96" s="3"/>
       <c r="D96" s="3" t="s">
-        <v>193</v>
+        <v>132</v>
       </c>
       <c r="E96" s="4" t="s">
-        <v>195</v>
+        <v>135</v>
       </c>
       <c r="F96" s="2" t="s">
-        <v>264</v>
+        <v>216</v>
       </c>
       <c r="G96" s="3"/>
     </row>
@@ -4040,13 +3634,13 @@
       <c r="B97" s="3"/>
       <c r="C97" s="3"/>
       <c r="D97" s="3" t="s">
-        <v>193</v>
+        <v>132</v>
       </c>
       <c r="E97" s="4" t="s">
-        <v>200</v>
+        <v>140</v>
       </c>
       <c r="F97" s="2" t="s">
-        <v>42</v>
+        <v>32</v>
       </c>
       <c r="G97" s="3"/>
     </row>
@@ -4055,13 +3649,13 @@
       <c r="B98" s="3"/>
       <c r="C98" s="3"/>
       <c r="D98" s="3" t="s">
-        <v>193</v>
+        <v>132</v>
       </c>
       <c r="E98" s="4" t="s">
-        <v>196</v>
+        <v>136</v>
       </c>
       <c r="F98" s="2" t="s">
-        <v>273</v>
+        <v>217</v>
       </c>
       <c r="G98" s="3"/>
     </row>
@@ -4070,28 +3664,32 @@
       <c r="B99" s="3"/>
       <c r="C99" s="3"/>
       <c r="D99" s="3" t="s">
-        <v>193</v>
+        <v>132</v>
       </c>
       <c r="E99" s="4" t="s">
-        <v>201</v>
-      </c>
-      <c r="F99" s="2" t="s">
-        <v>42</v>
+        <v>141</v>
+      </c>
+      <c r="F99" s="1" t="s">
+        <v>32</v>
       </c>
       <c r="G99" s="3"/>
     </row>
     <row r="100" spans="1:7" ht="28.5" x14ac:dyDescent="0.2">
       <c r="A100" s="3"/>
-      <c r="B100" s="3"/>
-      <c r="C100" s="3"/>
+      <c r="B100" s="3" t="s">
+        <v>176</v>
+      </c>
+      <c r="C100" s="3" t="s">
+        <v>163</v>
+      </c>
       <c r="D100" s="3" t="s">
-        <v>193</v>
+        <v>132</v>
       </c>
       <c r="E100" s="4" t="s">
-        <v>197</v>
+        <v>133</v>
       </c>
       <c r="F100" s="2" t="s">
-        <v>265</v>
+        <v>218</v>
       </c>
       <c r="G100" s="3"/>
     </row>
@@ -4100,32 +3698,28 @@
       <c r="B101" s="3"/>
       <c r="C101" s="3"/>
       <c r="D101" s="3" t="s">
-        <v>193</v>
+        <v>132</v>
       </c>
       <c r="E101" s="4" t="s">
-        <v>202</v>
+        <v>138</v>
       </c>
       <c r="F101" s="2" t="s">
-        <v>42</v>
+        <v>32</v>
       </c>
       <c r="G101" s="3"/>
     </row>
     <row r="102" spans="1:7" ht="28.5" x14ac:dyDescent="0.2">
       <c r="A102" s="3"/>
-      <c r="B102" s="3" t="s">
-        <v>214</v>
-      </c>
-      <c r="C102" s="3" t="s">
-        <v>221</v>
-      </c>
+      <c r="B102" s="3"/>
+      <c r="C102" s="3"/>
       <c r="D102" s="3" t="s">
-        <v>193</v>
+        <v>132</v>
       </c>
       <c r="E102" s="4" t="s">
-        <v>194</v>
+        <v>134</v>
       </c>
       <c r="F102" s="2" t="s">
-        <v>266</v>
+        <v>219</v>
       </c>
       <c r="G102" s="3"/>
     </row>
@@ -4134,13 +3728,13 @@
       <c r="B103" s="3"/>
       <c r="C103" s="3"/>
       <c r="D103" s="3" t="s">
-        <v>193</v>
+        <v>132</v>
       </c>
       <c r="E103" s="4" t="s">
-        <v>199</v>
-      </c>
-      <c r="F103" s="1" t="s">
-        <v>42</v>
+        <v>139</v>
+      </c>
+      <c r="F103" s="2" t="s">
+        <v>32</v>
       </c>
       <c r="G103" s="3"/>
     </row>
@@ -4149,13 +3743,13 @@
       <c r="B104" s="3"/>
       <c r="C104" s="3"/>
       <c r="D104" s="3" t="s">
-        <v>193</v>
+        <v>132</v>
       </c>
       <c r="E104" s="4" t="s">
-        <v>195</v>
+        <v>135</v>
       </c>
       <c r="F104" s="2" t="s">
-        <v>267</v>
+        <v>220</v>
       </c>
       <c r="G104" s="3"/>
     </row>
@@ -4164,13 +3758,13 @@
       <c r="B105" s="3"/>
       <c r="C105" s="3"/>
       <c r="D105" s="3" t="s">
-        <v>193</v>
+        <v>132</v>
       </c>
       <c r="E105" s="4" t="s">
-        <v>200</v>
+        <v>140</v>
       </c>
       <c r="F105" s="2" t="s">
-        <v>42</v>
+        <v>32</v>
       </c>
       <c r="G105" s="3"/>
     </row>
@@ -4179,13 +3773,13 @@
       <c r="B106" s="3"/>
       <c r="C106" s="3"/>
       <c r="D106" s="3" t="s">
-        <v>193</v>
+        <v>132</v>
       </c>
       <c r="E106" s="4" t="s">
-        <v>196</v>
+        <v>136</v>
       </c>
       <c r="F106" s="2" t="s">
-        <v>268</v>
+        <v>221</v>
       </c>
       <c r="G106" s="3"/>
     </row>
@@ -4194,28 +3788,32 @@
       <c r="B107" s="3"/>
       <c r="C107" s="3"/>
       <c r="D107" s="3" t="s">
-        <v>193</v>
+        <v>132</v>
       </c>
       <c r="E107" s="4" t="s">
-        <v>201</v>
-      </c>
-      <c r="F107" s="2" t="s">
-        <v>42</v>
+        <v>141</v>
+      </c>
+      <c r="F107" s="1" t="s">
+        <v>32</v>
       </c>
       <c r="G107" s="3"/>
     </row>
     <row r="108" spans="1:7" ht="28.5" x14ac:dyDescent="0.2">
       <c r="A108" s="3"/>
-      <c r="B108" s="3"/>
-      <c r="C108" s="3"/>
+      <c r="B108" s="3" t="s">
+        <v>177</v>
+      </c>
+      <c r="C108" s="3" t="s">
+        <v>164</v>
+      </c>
       <c r="D108" s="3" t="s">
-        <v>193</v>
+        <v>132</v>
       </c>
       <c r="E108" s="4" t="s">
-        <v>197</v>
+        <v>133</v>
       </c>
       <c r="F108" s="2" t="s">
-        <v>269</v>
+        <v>222</v>
       </c>
       <c r="G108" s="3"/>
     </row>
@@ -4224,32 +3822,28 @@
       <c r="B109" s="3"/>
       <c r="C109" s="3"/>
       <c r="D109" s="3" t="s">
-        <v>193</v>
+        <v>132</v>
       </c>
       <c r="E109" s="4" t="s">
-        <v>202</v>
+        <v>138</v>
       </c>
       <c r="F109" s="2" t="s">
-        <v>42</v>
+        <v>32</v>
       </c>
       <c r="G109" s="3"/>
     </row>
     <row r="110" spans="1:7" ht="28.5" x14ac:dyDescent="0.2">
       <c r="A110" s="3"/>
-      <c r="B110" s="3" t="s">
-        <v>236</v>
-      </c>
-      <c r="C110" s="3" t="s">
-        <v>222</v>
-      </c>
+      <c r="B110" s="3"/>
+      <c r="C110" s="3"/>
       <c r="D110" s="3" t="s">
-        <v>193</v>
+        <v>132</v>
       </c>
       <c r="E110" s="4" t="s">
-        <v>194</v>
+        <v>134</v>
       </c>
       <c r="F110" s="2" t="s">
-        <v>270</v>
+        <v>223</v>
       </c>
       <c r="G110" s="3"/>
     </row>
@@ -4258,13 +3852,13 @@
       <c r="B111" s="3"/>
       <c r="C111" s="3"/>
       <c r="D111" s="3" t="s">
-        <v>193</v>
+        <v>132</v>
       </c>
       <c r="E111" s="4" t="s">
-        <v>199</v>
-      </c>
-      <c r="F111" s="1" t="s">
-        <v>42</v>
+        <v>139</v>
+      </c>
+      <c r="F111" s="2" t="s">
+        <v>32</v>
       </c>
       <c r="G111" s="3"/>
     </row>
@@ -4273,13 +3867,13 @@
       <c r="B112" s="3"/>
       <c r="C112" s="3"/>
       <c r="D112" s="3" t="s">
-        <v>193</v>
+        <v>132</v>
       </c>
       <c r="E112" s="4" t="s">
-        <v>195</v>
+        <v>135</v>
       </c>
       <c r="F112" s="2" t="s">
-        <v>271</v>
+        <v>224</v>
       </c>
       <c r="G112" s="3"/>
     </row>
@@ -4288,13 +3882,13 @@
       <c r="B113" s="3"/>
       <c r="C113" s="3"/>
       <c r="D113" s="3" t="s">
-        <v>193</v>
+        <v>132</v>
       </c>
       <c r="E113" s="4" t="s">
-        <v>200</v>
+        <v>140</v>
       </c>
       <c r="F113" s="2" t="s">
-        <v>42</v>
+        <v>32</v>
       </c>
       <c r="G113" s="3"/>
     </row>
@@ -4303,13 +3897,13 @@
       <c r="B114" s="3"/>
       <c r="C114" s="3"/>
       <c r="D114" s="3" t="s">
-        <v>193</v>
+        <v>132</v>
       </c>
       <c r="E114" s="4" t="s">
-        <v>196</v>
+        <v>136</v>
       </c>
       <c r="F114" s="2" t="s">
-        <v>272</v>
+        <v>225</v>
       </c>
       <c r="G114" s="3"/>
     </row>
@@ -4318,28 +3912,32 @@
       <c r="B115" s="3"/>
       <c r="C115" s="3"/>
       <c r="D115" s="3" t="s">
-        <v>193</v>
+        <v>132</v>
       </c>
       <c r="E115" s="4" t="s">
-        <v>201</v>
-      </c>
-      <c r="F115" s="2" t="s">
-        <v>42</v>
+        <v>141</v>
+      </c>
+      <c r="F115" s="1" t="s">
+        <v>32</v>
       </c>
       <c r="G115" s="3"/>
     </row>
     <row r="116" spans="1:7" ht="28.5" x14ac:dyDescent="0.2">
       <c r="A116" s="3"/>
-      <c r="B116" s="3"/>
-      <c r="C116" s="3"/>
+      <c r="B116" s="3" t="s">
+        <v>178</v>
+      </c>
+      <c r="C116" s="3" t="s">
+        <v>165</v>
+      </c>
       <c r="D116" s="3" t="s">
-        <v>193</v>
+        <v>132</v>
       </c>
       <c r="E116" s="4" t="s">
-        <v>197</v>
+        <v>133</v>
       </c>
       <c r="F116" s="2" t="s">
-        <v>274</v>
+        <v>226</v>
       </c>
       <c r="G116" s="3"/>
     </row>
@@ -4348,32 +3946,28 @@
       <c r="B117" s="3"/>
       <c r="C117" s="3"/>
       <c r="D117" s="3" t="s">
-        <v>193</v>
+        <v>132</v>
       </c>
       <c r="E117" s="4" t="s">
-        <v>202</v>
-      </c>
-      <c r="F117" s="1" t="s">
-        <v>42</v>
+        <v>138</v>
+      </c>
+      <c r="F117" s="2" t="s">
+        <v>32</v>
       </c>
       <c r="G117" s="3"/>
     </row>
     <row r="118" spans="1:7" ht="28.5" x14ac:dyDescent="0.2">
       <c r="A118" s="3"/>
-      <c r="B118" s="3" t="s">
-        <v>214</v>
-      </c>
-      <c r="C118" s="3" t="s">
-        <v>223</v>
-      </c>
+      <c r="B118" s="3"/>
+      <c r="C118" s="3"/>
       <c r="D118" s="3" t="s">
-        <v>193</v>
+        <v>132</v>
       </c>
       <c r="E118" s="4" t="s">
-        <v>194</v>
+        <v>134</v>
       </c>
       <c r="F118" s="2" t="s">
-        <v>275</v>
+        <v>227</v>
       </c>
       <c r="G118" s="3"/>
     </row>
@@ -4382,13 +3976,13 @@
       <c r="B119" s="3"/>
       <c r="C119" s="3"/>
       <c r="D119" s="3" t="s">
-        <v>193</v>
+        <v>132</v>
       </c>
       <c r="E119" s="4" t="s">
-        <v>199</v>
+        <v>139</v>
       </c>
       <c r="F119" s="2" t="s">
-        <v>42</v>
+        <v>32</v>
       </c>
       <c r="G119" s="3"/>
     </row>
@@ -4397,13 +3991,13 @@
       <c r="B120" s="3"/>
       <c r="C120" s="3"/>
       <c r="D120" s="3" t="s">
-        <v>193</v>
+        <v>132</v>
       </c>
       <c r="E120" s="4" t="s">
-        <v>195</v>
+        <v>135</v>
       </c>
       <c r="F120" s="2" t="s">
-        <v>276</v>
+        <v>228</v>
       </c>
       <c r="G120" s="3"/>
     </row>
@@ -4412,13 +4006,13 @@
       <c r="B121" s="3"/>
       <c r="C121" s="3"/>
       <c r="D121" s="3" t="s">
-        <v>193</v>
+        <v>132</v>
       </c>
       <c r="E121" s="4" t="s">
-        <v>200</v>
+        <v>140</v>
       </c>
       <c r="F121" s="2" t="s">
-        <v>42</v>
+        <v>32</v>
       </c>
       <c r="G121" s="3"/>
     </row>
@@ -4427,13 +4021,13 @@
       <c r="B122" s="3"/>
       <c r="C122" s="3"/>
       <c r="D122" s="3" t="s">
-        <v>193</v>
+        <v>132</v>
       </c>
       <c r="E122" s="4" t="s">
-        <v>196</v>
+        <v>136</v>
       </c>
       <c r="F122" s="2" t="s">
-        <v>277</v>
+        <v>229</v>
       </c>
       <c r="G122" s="3"/>
     </row>
@@ -4442,28 +4036,32 @@
       <c r="B123" s="3"/>
       <c r="C123" s="3"/>
       <c r="D123" s="3" t="s">
-        <v>193</v>
+        <v>132</v>
       </c>
       <c r="E123" s="4" t="s">
-        <v>201</v>
-      </c>
-      <c r="F123" s="2" t="s">
-        <v>42</v>
+        <v>141</v>
+      </c>
+      <c r="F123" s="1" t="s">
+        <v>32</v>
       </c>
       <c r="G123" s="3"/>
     </row>
     <row r="124" spans="1:7" ht="28.5" x14ac:dyDescent="0.2">
       <c r="A124" s="3"/>
-      <c r="B124" s="3"/>
-      <c r="C124" s="3"/>
+      <c r="B124" s="3" t="s">
+        <v>179</v>
+      </c>
+      <c r="C124" s="3" t="s">
+        <v>166</v>
+      </c>
       <c r="D124" s="3" t="s">
-        <v>193</v>
+        <v>132</v>
       </c>
       <c r="E124" s="4" t="s">
-        <v>197</v>
+        <v>133</v>
       </c>
       <c r="F124" s="2" t="s">
-        <v>278</v>
+        <v>230</v>
       </c>
       <c r="G124" s="3"/>
     </row>
@@ -4472,32 +4070,28 @@
       <c r="B125" s="3"/>
       <c r="C125" s="3"/>
       <c r="D125" s="3" t="s">
-        <v>193</v>
+        <v>132</v>
       </c>
       <c r="E125" s="4" t="s">
-        <v>202</v>
-      </c>
-      <c r="F125" s="1" t="s">
-        <v>42</v>
+        <v>138</v>
+      </c>
+      <c r="F125" s="2" t="s">
+        <v>32</v>
       </c>
       <c r="G125" s="3"/>
     </row>
     <row r="126" spans="1:7" ht="28.5" x14ac:dyDescent="0.2">
       <c r="A126" s="3"/>
-      <c r="B126" s="3" t="s">
-        <v>237</v>
-      </c>
-      <c r="C126" s="3" t="s">
-        <v>224</v>
-      </c>
+      <c r="B126" s="3"/>
+      <c r="C126" s="3"/>
       <c r="D126" s="3" t="s">
-        <v>193</v>
+        <v>132</v>
       </c>
       <c r="E126" s="4" t="s">
-        <v>194</v>
+        <v>134</v>
       </c>
       <c r="F126" s="2" t="s">
-        <v>279</v>
+        <v>231</v>
       </c>
       <c r="G126" s="3"/>
     </row>
@@ -4506,13 +4100,13 @@
       <c r="B127" s="3"/>
       <c r="C127" s="3"/>
       <c r="D127" s="3" t="s">
-        <v>193</v>
+        <v>132</v>
       </c>
       <c r="E127" s="4" t="s">
-        <v>199</v>
+        <v>139</v>
       </c>
       <c r="F127" s="2" t="s">
-        <v>42</v>
+        <v>32</v>
       </c>
       <c r="G127" s="3"/>
     </row>
@@ -4521,13 +4115,13 @@
       <c r="B128" s="3"/>
       <c r="C128" s="3"/>
       <c r="D128" s="3" t="s">
-        <v>193</v>
+        <v>132</v>
       </c>
       <c r="E128" s="4" t="s">
-        <v>195</v>
+        <v>135</v>
       </c>
       <c r="F128" s="2" t="s">
-        <v>280</v>
+        <v>232</v>
       </c>
       <c r="G128" s="3"/>
     </row>
@@ -4536,13 +4130,13 @@
       <c r="B129" s="3"/>
       <c r="C129" s="3"/>
       <c r="D129" s="3" t="s">
-        <v>193</v>
+        <v>132</v>
       </c>
       <c r="E129" s="4" t="s">
-        <v>200</v>
+        <v>140</v>
       </c>
       <c r="F129" s="2" t="s">
-        <v>42</v>
+        <v>32</v>
       </c>
       <c r="G129" s="3"/>
     </row>
@@ -4551,13 +4145,13 @@
       <c r="B130" s="3"/>
       <c r="C130" s="3"/>
       <c r="D130" s="3" t="s">
-        <v>193</v>
+        <v>132</v>
       </c>
       <c r="E130" s="4" t="s">
-        <v>196</v>
+        <v>136</v>
       </c>
       <c r="F130" s="2" t="s">
-        <v>281</v>
+        <v>233</v>
       </c>
       <c r="G130" s="3"/>
     </row>
@@ -4566,28 +4160,32 @@
       <c r="B131" s="3"/>
       <c r="C131" s="3"/>
       <c r="D131" s="3" t="s">
-        <v>193</v>
+        <v>132</v>
       </c>
       <c r="E131" s="4" t="s">
-        <v>201</v>
-      </c>
-      <c r="F131" s="2" t="s">
-        <v>42</v>
+        <v>141</v>
+      </c>
+      <c r="F131" s="1" t="s">
+        <v>32</v>
       </c>
       <c r="G131" s="3"/>
     </row>
     <row r="132" spans="1:7" ht="28.5" x14ac:dyDescent="0.2">
       <c r="A132" s="3"/>
-      <c r="B132" s="3"/>
-      <c r="C132" s="3"/>
+      <c r="B132" s="3" t="s">
+        <v>180</v>
+      </c>
+      <c r="C132" s="3" t="s">
+        <v>167</v>
+      </c>
       <c r="D132" s="3" t="s">
-        <v>193</v>
+        <v>132</v>
       </c>
       <c r="E132" s="4" t="s">
-        <v>197</v>
+        <v>133</v>
       </c>
       <c r="F132" s="2" t="s">
-        <v>282</v>
+        <v>234</v>
       </c>
       <c r="G132" s="3"/>
     </row>
@@ -4596,32 +4194,28 @@
       <c r="B133" s="3"/>
       <c r="C133" s="3"/>
       <c r="D133" s="3" t="s">
-        <v>193</v>
+        <v>132</v>
       </c>
       <c r="E133" s="4" t="s">
-        <v>202</v>
-      </c>
-      <c r="F133" s="1" t="s">
-        <v>42</v>
+        <v>138</v>
+      </c>
+      <c r="F133" s="2" t="s">
+        <v>32</v>
       </c>
       <c r="G133" s="3"/>
     </row>
     <row r="134" spans="1:7" ht="28.5" x14ac:dyDescent="0.2">
       <c r="A134" s="3"/>
-      <c r="B134" s="3" t="s">
-        <v>238</v>
-      </c>
-      <c r="C134" s="3" t="s">
-        <v>225</v>
-      </c>
+      <c r="B134" s="3"/>
+      <c r="C134" s="3"/>
       <c r="D134" s="3" t="s">
-        <v>193</v>
+        <v>132</v>
       </c>
       <c r="E134" s="4" t="s">
-        <v>194</v>
+        <v>134</v>
       </c>
       <c r="F134" s="2" t="s">
-        <v>283</v>
+        <v>235</v>
       </c>
       <c r="G134" s="3"/>
     </row>
@@ -4630,13 +4224,13 @@
       <c r="B135" s="3"/>
       <c r="C135" s="3"/>
       <c r="D135" s="3" t="s">
-        <v>193</v>
+        <v>132</v>
       </c>
       <c r="E135" s="4" t="s">
-        <v>199</v>
+        <v>139</v>
       </c>
       <c r="F135" s="2" t="s">
-        <v>42</v>
+        <v>32</v>
       </c>
       <c r="G135" s="3"/>
     </row>
@@ -4645,13 +4239,13 @@
       <c r="B136" s="3"/>
       <c r="C136" s="3"/>
       <c r="D136" s="3" t="s">
-        <v>193</v>
+        <v>132</v>
       </c>
       <c r="E136" s="4" t="s">
-        <v>195</v>
+        <v>135</v>
       </c>
       <c r="F136" s="2" t="s">
-        <v>284</v>
+        <v>236</v>
       </c>
       <c r="G136" s="3"/>
     </row>
@@ -4660,13 +4254,13 @@
       <c r="B137" s="3"/>
       <c r="C137" s="3"/>
       <c r="D137" s="3" t="s">
-        <v>193</v>
+        <v>132</v>
       </c>
       <c r="E137" s="4" t="s">
-        <v>200</v>
+        <v>140</v>
       </c>
       <c r="F137" s="2" t="s">
-        <v>42</v>
+        <v>32</v>
       </c>
       <c r="G137" s="3"/>
     </row>
@@ -4675,13 +4269,13 @@
       <c r="B138" s="3"/>
       <c r="C138" s="3"/>
       <c r="D138" s="3" t="s">
-        <v>193</v>
+        <v>132</v>
       </c>
       <c r="E138" s="4" t="s">
-        <v>196</v>
+        <v>136</v>
       </c>
       <c r="F138" s="2" t="s">
-        <v>285</v>
+        <v>237</v>
       </c>
       <c r="G138" s="3"/>
     </row>
@@ -4690,28 +4284,32 @@
       <c r="B139" s="3"/>
       <c r="C139" s="3"/>
       <c r="D139" s="3" t="s">
-        <v>193</v>
+        <v>132</v>
       </c>
       <c r="E139" s="4" t="s">
-        <v>201</v>
-      </c>
-      <c r="F139" s="2" t="s">
-        <v>42</v>
+        <v>141</v>
+      </c>
+      <c r="F139" s="1" t="s">
+        <v>32</v>
       </c>
       <c r="G139" s="3"/>
     </row>
     <row r="140" spans="1:7" ht="28.5" x14ac:dyDescent="0.2">
       <c r="A140" s="3"/>
-      <c r="B140" s="3"/>
-      <c r="C140" s="3"/>
+      <c r="B140" s="3" t="s">
+        <v>181</v>
+      </c>
+      <c r="C140" s="3" t="s">
+        <v>168</v>
+      </c>
       <c r="D140" s="3" t="s">
-        <v>193</v>
+        <v>132</v>
       </c>
       <c r="E140" s="4" t="s">
-        <v>197</v>
+        <v>133</v>
       </c>
       <c r="F140" s="2" t="s">
-        <v>286</v>
+        <v>238</v>
       </c>
       <c r="G140" s="3"/>
     </row>
@@ -4720,32 +4318,28 @@
       <c r="B141" s="3"/>
       <c r="C141" s="3"/>
       <c r="D141" s="3" t="s">
-        <v>193</v>
+        <v>132</v>
       </c>
       <c r="E141" s="4" t="s">
-        <v>202</v>
-      </c>
-      <c r="F141" s="1" t="s">
-        <v>42</v>
+        <v>138</v>
+      </c>
+      <c r="F141" s="2" t="s">
+        <v>32</v>
       </c>
       <c r="G141" s="3"/>
     </row>
     <row r="142" spans="1:7" ht="28.5" x14ac:dyDescent="0.2">
       <c r="A142" s="3"/>
-      <c r="B142" s="3" t="s">
+      <c r="B142" s="3"/>
+      <c r="C142" s="3"/>
+      <c r="D142" s="3" t="s">
+        <v>132</v>
+      </c>
+      <c r="E142" s="4" t="s">
+        <v>134</v>
+      </c>
+      <c r="F142" s="2" t="s">
         <v>239</v>
-      </c>
-      <c r="C142" s="3" t="s">
-        <v>226</v>
-      </c>
-      <c r="D142" s="3" t="s">
-        <v>193</v>
-      </c>
-      <c r="E142" s="4" t="s">
-        <v>194</v>
-      </c>
-      <c r="F142" s="2" t="s">
-        <v>287</v>
       </c>
       <c r="G142" s="3"/>
     </row>
@@ -4754,13 +4348,13 @@
       <c r="B143" s="3"/>
       <c r="C143" s="3"/>
       <c r="D143" s="3" t="s">
-        <v>193</v>
+        <v>132</v>
       </c>
       <c r="E143" s="4" t="s">
-        <v>199</v>
+        <v>139</v>
       </c>
       <c r="F143" s="2" t="s">
-        <v>42</v>
+        <v>32</v>
       </c>
       <c r="G143" s="3"/>
     </row>
@@ -4769,13 +4363,13 @@
       <c r="B144" s="3"/>
       <c r="C144" s="3"/>
       <c r="D144" s="3" t="s">
-        <v>193</v>
+        <v>132</v>
       </c>
       <c r="E144" s="4" t="s">
-        <v>195</v>
+        <v>135</v>
       </c>
       <c r="F144" s="2" t="s">
-        <v>288</v>
+        <v>240</v>
       </c>
       <c r="G144" s="3"/>
     </row>
@@ -4784,13 +4378,13 @@
       <c r="B145" s="3"/>
       <c r="C145" s="3"/>
       <c r="D145" s="3" t="s">
-        <v>193</v>
+        <v>132</v>
       </c>
       <c r="E145" s="4" t="s">
-        <v>200</v>
+        <v>140</v>
       </c>
       <c r="F145" s="2" t="s">
-        <v>42</v>
+        <v>32</v>
       </c>
       <c r="G145" s="3"/>
     </row>
@@ -4799,13 +4393,13 @@
       <c r="B146" s="3"/>
       <c r="C146" s="3"/>
       <c r="D146" s="3" t="s">
-        <v>193</v>
+        <v>132</v>
       </c>
       <c r="E146" s="4" t="s">
-        <v>196</v>
+        <v>136</v>
       </c>
       <c r="F146" s="2" t="s">
-        <v>289</v>
+        <v>241</v>
       </c>
       <c r="G146" s="3"/>
     </row>
@@ -4814,606 +4408,646 @@
       <c r="B147" s="3"/>
       <c r="C147" s="3"/>
       <c r="D147" s="3" t="s">
-        <v>193</v>
+        <v>132</v>
       </c>
       <c r="E147" s="4" t="s">
-        <v>201</v>
-      </c>
-      <c r="F147" s="2" t="s">
-        <v>42</v>
+        <v>141</v>
+      </c>
+      <c r="F147" s="1" t="s">
+        <v>32</v>
       </c>
       <c r="G147" s="3"/>
     </row>
     <row r="148" spans="1:7" ht="28.5" x14ac:dyDescent="0.2">
       <c r="A148" s="3"/>
-      <c r="B148" s="3"/>
-      <c r="C148" s="3"/>
+      <c r="B148" s="3" t="s">
+        <v>242</v>
+      </c>
+      <c r="C148" s="3" t="s">
+        <v>243</v>
+      </c>
       <c r="D148" s="3" t="s">
-        <v>193</v>
+        <v>132</v>
       </c>
       <c r="E148" s="4" t="s">
-        <v>197</v>
+        <v>244</v>
       </c>
       <c r="F148" s="2" t="s">
-        <v>290</v>
-      </c>
-      <c r="G148" s="3"/>
-    </row>
-    <row r="149" spans="1:7" x14ac:dyDescent="0.2">
+        <v>246</v>
+      </c>
+      <c r="G148" s="16" t="s">
+        <v>394</v>
+      </c>
+    </row>
+    <row r="149" spans="1:7" ht="28.5" x14ac:dyDescent="0.2">
       <c r="A149" s="3"/>
       <c r="B149" s="3"/>
       <c r="C149" s="3"/>
       <c r="D149" s="3" t="s">
-        <v>193</v>
+        <v>132</v>
       </c>
       <c r="E149" s="4" t="s">
-        <v>202</v>
-      </c>
-      <c r="F149" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="G149" s="3"/>
+        <v>34</v>
+      </c>
+      <c r="F149" s="2" t="s">
+        <v>247</v>
+      </c>
+      <c r="G149" s="16"/>
     </row>
     <row r="150" spans="1:7" ht="28.5" x14ac:dyDescent="0.2">
       <c r="A150" s="3"/>
       <c r="B150" s="3" t="s">
-        <v>240</v>
+        <v>245</v>
       </c>
       <c r="C150" s="3" t="s">
-        <v>227</v>
+        <v>251</v>
       </c>
       <c r="D150" s="3" t="s">
-        <v>193</v>
+        <v>132</v>
       </c>
       <c r="E150" s="4" t="s">
-        <v>194</v>
+        <v>244</v>
       </c>
       <c r="F150" s="2" t="s">
-        <v>291</v>
+        <v>252</v>
       </c>
       <c r="G150" s="3"/>
     </row>
-    <row r="151" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="151" spans="1:7" ht="28.5" x14ac:dyDescent="0.2">
       <c r="A151" s="3"/>
       <c r="B151" s="3"/>
       <c r="C151" s="3"/>
       <c r="D151" s="3" t="s">
-        <v>193</v>
+        <v>132</v>
       </c>
       <c r="E151" s="4" t="s">
-        <v>199</v>
+        <v>34</v>
       </c>
       <c r="F151" s="2" t="s">
-        <v>42</v>
+        <v>253</v>
       </c>
       <c r="G151" s="3"/>
     </row>
     <row r="152" spans="1:7" ht="28.5" x14ac:dyDescent="0.2">
       <c r="A152" s="3"/>
-      <c r="B152" s="3"/>
-      <c r="C152" s="3"/>
+      <c r="B152" s="3" t="s">
+        <v>248</v>
+      </c>
+      <c r="C152" s="3" t="s">
+        <v>61</v>
+      </c>
       <c r="D152" s="3" t="s">
-        <v>193</v>
+        <v>132</v>
       </c>
       <c r="E152" s="4" t="s">
-        <v>195</v>
+        <v>244</v>
       </c>
       <c r="F152" s="2" t="s">
-        <v>292</v>
+        <v>254</v>
       </c>
       <c r="G152" s="3"/>
     </row>
-    <row r="153" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="153" spans="1:7" ht="28.5" x14ac:dyDescent="0.2">
       <c r="A153" s="3"/>
       <c r="B153" s="3"/>
       <c r="C153" s="3"/>
       <c r="D153" s="3" t="s">
-        <v>193</v>
+        <v>132</v>
       </c>
       <c r="E153" s="4" t="s">
-        <v>200</v>
+        <v>34</v>
       </c>
       <c r="F153" s="2" t="s">
-        <v>42</v>
+        <v>255</v>
       </c>
       <c r="G153" s="3"/>
     </row>
     <row r="154" spans="1:7" ht="28.5" x14ac:dyDescent="0.2">
       <c r="A154" s="3"/>
-      <c r="B154" s="3"/>
-      <c r="C154" s="3"/>
+      <c r="B154" s="3" t="s">
+        <v>249</v>
+      </c>
+      <c r="C154" s="3" t="s">
+        <v>67</v>
+      </c>
       <c r="D154" s="3" t="s">
-        <v>193</v>
+        <v>132</v>
       </c>
       <c r="E154" s="4" t="s">
-        <v>196</v>
+        <v>244</v>
       </c>
       <c r="F154" s="2" t="s">
-        <v>293</v>
+        <v>256</v>
       </c>
       <c r="G154" s="3"/>
     </row>
-    <row r="155" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="155" spans="1:7" ht="28.5" x14ac:dyDescent="0.2">
       <c r="A155" s="3"/>
       <c r="B155" s="3"/>
       <c r="C155" s="3"/>
       <c r="D155" s="3" t="s">
-        <v>193</v>
+        <v>132</v>
       </c>
       <c r="E155" s="4" t="s">
-        <v>201</v>
+        <v>34</v>
       </c>
       <c r="F155" s="2" t="s">
-        <v>42</v>
+        <v>257</v>
       </c>
       <c r="G155" s="3"/>
     </row>
     <row r="156" spans="1:7" ht="28.5" x14ac:dyDescent="0.2">
       <c r="A156" s="3"/>
-      <c r="B156" s="3"/>
-      <c r="C156" s="3"/>
+      <c r="B156" s="3" t="s">
+        <v>250</v>
+      </c>
+      <c r="C156" s="3" t="s">
+        <v>74</v>
+      </c>
       <c r="D156" s="3" t="s">
-        <v>193</v>
+        <v>132</v>
       </c>
       <c r="E156" s="4" t="s">
-        <v>197</v>
+        <v>244</v>
       </c>
       <c r="F156" s="2" t="s">
-        <v>294</v>
+        <v>258</v>
       </c>
       <c r="G156" s="3"/>
     </row>
-    <row r="157" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="157" spans="1:7" ht="28.5" x14ac:dyDescent="0.2">
       <c r="A157" s="3"/>
       <c r="B157" s="3"/>
       <c r="C157" s="3"/>
       <c r="D157" s="3" t="s">
-        <v>193</v>
+        <v>132</v>
       </c>
       <c r="E157" s="4" t="s">
-        <v>202</v>
-      </c>
-      <c r="F157" s="1" t="s">
-        <v>42</v>
+        <v>34</v>
+      </c>
+      <c r="F157" s="2" t="s">
+        <v>264</v>
       </c>
       <c r="G157" s="3"/>
     </row>
     <row r="158" spans="1:7" ht="28.5" x14ac:dyDescent="0.2">
       <c r="A158" s="3"/>
       <c r="B158" s="3" t="s">
-        <v>241</v>
+        <v>259</v>
       </c>
       <c r="C158" s="3" t="s">
-        <v>228</v>
+        <v>118</v>
       </c>
       <c r="D158" s="3" t="s">
-        <v>193</v>
+        <v>132</v>
       </c>
       <c r="E158" s="4" t="s">
-        <v>194</v>
+        <v>244</v>
       </c>
       <c r="F158" s="2" t="s">
-        <v>295</v>
+        <v>282</v>
       </c>
       <c r="G158" s="3"/>
     </row>
-    <row r="159" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="159" spans="1:7" ht="28.5" x14ac:dyDescent="0.2">
       <c r="A159" s="3"/>
       <c r="B159" s="3"/>
       <c r="C159" s="3"/>
       <c r="D159" s="3" t="s">
-        <v>193</v>
+        <v>132</v>
       </c>
       <c r="E159" s="4" t="s">
-        <v>199</v>
+        <v>34</v>
       </c>
       <c r="F159" s="2" t="s">
-        <v>42</v>
-      </c>
-      <c r="G159" s="3"/>
+        <v>283</v>
+      </c>
+      <c r="G159" s="2"/>
     </row>
     <row r="160" spans="1:7" ht="28.5" x14ac:dyDescent="0.2">
       <c r="A160" s="3"/>
-      <c r="B160" s="3"/>
-      <c r="C160" s="3"/>
+      <c r="B160" s="3" t="s">
+        <v>260</v>
+      </c>
+      <c r="C160" s="3" t="s">
+        <v>285</v>
+      </c>
       <c r="D160" s="3" t="s">
-        <v>193</v>
+        <v>132</v>
       </c>
       <c r="E160" s="4" t="s">
-        <v>195</v>
+        <v>244</v>
       </c>
       <c r="F160" s="2" t="s">
-        <v>296</v>
-      </c>
-      <c r="G160" s="3"/>
-    </row>
-    <row r="161" spans="1:7" x14ac:dyDescent="0.2">
+        <v>275</v>
+      </c>
+      <c r="G160" s="2"/>
+    </row>
+    <row r="161" spans="1:7" ht="28.5" x14ac:dyDescent="0.2">
       <c r="A161" s="3"/>
       <c r="B161" s="3"/>
       <c r="C161" s="3"/>
       <c r="D161" s="3" t="s">
-        <v>193</v>
+        <v>132</v>
       </c>
       <c r="E161" s="4" t="s">
-        <v>200</v>
+        <v>34</v>
       </c>
       <c r="F161" s="2" t="s">
-        <v>42</v>
-      </c>
-      <c r="G161" s="3"/>
+        <v>276</v>
+      </c>
+      <c r="G161" s="2"/>
     </row>
     <row r="162" spans="1:7" ht="28.5" x14ac:dyDescent="0.2">
       <c r="A162" s="3"/>
-      <c r="B162" s="3"/>
-      <c r="C162" s="3"/>
+      <c r="B162" s="3" t="s">
+        <v>261</v>
+      </c>
+      <c r="C162" s="3" t="s">
+        <v>286</v>
+      </c>
       <c r="D162" s="3" t="s">
-        <v>193</v>
+        <v>132</v>
       </c>
       <c r="E162" s="4" t="s">
-        <v>196</v>
+        <v>244</v>
       </c>
       <c r="F162" s="2" t="s">
-        <v>297</v>
-      </c>
-      <c r="G162" s="3"/>
-    </row>
-    <row r="163" spans="1:7" x14ac:dyDescent="0.2">
+        <v>277</v>
+      </c>
+      <c r="G162" s="2"/>
+    </row>
+    <row r="163" spans="1:7" ht="28.5" x14ac:dyDescent="0.2">
       <c r="A163" s="3"/>
       <c r="B163" s="3"/>
       <c r="C163" s="3"/>
       <c r="D163" s="3" t="s">
-        <v>193</v>
+        <v>132</v>
       </c>
       <c r="E163" s="4" t="s">
-        <v>201</v>
+        <v>34</v>
       </c>
       <c r="F163" s="2" t="s">
-        <v>42</v>
-      </c>
-      <c r="G163" s="3"/>
+        <v>278</v>
+      </c>
+      <c r="G163" s="2"/>
     </row>
     <row r="164" spans="1:7" ht="28.5" x14ac:dyDescent="0.2">
       <c r="A164" s="3"/>
-      <c r="B164" s="3"/>
-      <c r="C164" s="3"/>
+      <c r="B164" s="3" t="s">
+        <v>262</v>
+      </c>
+      <c r="C164" s="3" t="s">
+        <v>287</v>
+      </c>
       <c r="D164" s="3" t="s">
-        <v>193</v>
+        <v>132</v>
       </c>
       <c r="E164" s="4" t="s">
-        <v>197</v>
+        <v>244</v>
       </c>
       <c r="F164" s="2" t="s">
-        <v>298</v>
-      </c>
-      <c r="G164" s="3"/>
-    </row>
-    <row r="165" spans="1:7" x14ac:dyDescent="0.2">
+        <v>279</v>
+      </c>
+      <c r="G164" s="2"/>
+    </row>
+    <row r="165" spans="1:7" ht="28.5" x14ac:dyDescent="0.2">
       <c r="A165" s="3"/>
       <c r="B165" s="3"/>
       <c r="C165" s="3"/>
       <c r="D165" s="3" t="s">
-        <v>193</v>
+        <v>132</v>
       </c>
       <c r="E165" s="4" t="s">
-        <v>202</v>
-      </c>
-      <c r="F165" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="G165" s="3"/>
+        <v>34</v>
+      </c>
+      <c r="F165" s="2" t="s">
+        <v>280</v>
+      </c>
+      <c r="G165" s="2"/>
     </row>
     <row r="166" spans="1:7" ht="28.5" x14ac:dyDescent="0.2">
       <c r="A166" s="3"/>
       <c r="B166" s="3" t="s">
-        <v>242</v>
+        <v>263</v>
       </c>
       <c r="C166" s="3" t="s">
-        <v>229</v>
+        <v>288</v>
       </c>
       <c r="D166" s="3" t="s">
-        <v>193</v>
+        <v>132</v>
       </c>
       <c r="E166" s="4" t="s">
-        <v>194</v>
+        <v>244</v>
       </c>
       <c r="F166" s="2" t="s">
-        <v>299</v>
-      </c>
-      <c r="G166" s="3"/>
-    </row>
-    <row r="167" spans="1:7" x14ac:dyDescent="0.2">
+        <v>281</v>
+      </c>
+      <c r="G166" s="2"/>
+    </row>
+    <row r="167" spans="1:7" ht="28.5" x14ac:dyDescent="0.2">
       <c r="A167" s="3"/>
       <c r="B167" s="3"/>
       <c r="C167" s="3"/>
       <c r="D167" s="3" t="s">
-        <v>193</v>
+        <v>132</v>
       </c>
       <c r="E167" s="4" t="s">
-        <v>199</v>
+        <v>34</v>
       </c>
       <c r="F167" s="2" t="s">
-        <v>42</v>
-      </c>
-      <c r="G167" s="3"/>
+        <v>284</v>
+      </c>
+      <c r="G167" s="2"/>
     </row>
     <row r="168" spans="1:7" ht="28.5" x14ac:dyDescent="0.2">
       <c r="A168" s="3"/>
-      <c r="B168" s="3"/>
-      <c r="C168" s="3"/>
+      <c r="B168" s="3" t="s">
+        <v>265</v>
+      </c>
+      <c r="C168" s="3" t="s">
+        <v>79</v>
+      </c>
       <c r="D168" s="3" t="s">
-        <v>193</v>
+        <v>132</v>
       </c>
       <c r="E168" s="4" t="s">
-        <v>195</v>
+        <v>244</v>
       </c>
       <c r="F168" s="2" t="s">
-        <v>300</v>
-      </c>
-      <c r="G168" s="3"/>
-    </row>
-    <row r="169" spans="1:7" x14ac:dyDescent="0.2">
+        <v>299</v>
+      </c>
+      <c r="G168" s="2"/>
+    </row>
+    <row r="169" spans="1:7" ht="28.5" x14ac:dyDescent="0.2">
       <c r="A169" s="3"/>
       <c r="B169" s="3"/>
       <c r="C169" s="3"/>
       <c r="D169" s="3" t="s">
-        <v>193</v>
+        <v>132</v>
       </c>
       <c r="E169" s="4" t="s">
-        <v>200</v>
+        <v>34</v>
       </c>
       <c r="F169" s="2" t="s">
-        <v>42</v>
-      </c>
-      <c r="G169" s="3"/>
+        <v>300</v>
+      </c>
+      <c r="G169" s="2"/>
     </row>
     <row r="170" spans="1:7" ht="28.5" x14ac:dyDescent="0.2">
       <c r="A170" s="3"/>
-      <c r="B170" s="3"/>
-      <c r="C170" s="3"/>
+      <c r="B170" s="3" t="s">
+        <v>266</v>
+      </c>
+      <c r="C170" s="3" t="s">
+        <v>80</v>
+      </c>
       <c r="D170" s="3" t="s">
-        <v>193</v>
+        <v>132</v>
       </c>
       <c r="E170" s="4" t="s">
-        <v>196</v>
+        <v>244</v>
       </c>
       <c r="F170" s="2" t="s">
         <v>301</v>
       </c>
-      <c r="G170" s="3"/>
-    </row>
-    <row r="171" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="G170" s="2"/>
+    </row>
+    <row r="171" spans="1:7" ht="28.5" x14ac:dyDescent="0.2">
       <c r="A171" s="3"/>
       <c r="B171" s="3"/>
       <c r="C171" s="3"/>
       <c r="D171" s="3" t="s">
-        <v>193</v>
+        <v>132</v>
       </c>
       <c r="E171" s="4" t="s">
-        <v>201</v>
+        <v>34</v>
       </c>
       <c r="F171" s="2" t="s">
-        <v>42</v>
-      </c>
-      <c r="G171" s="3"/>
+        <v>302</v>
+      </c>
+      <c r="G171" s="2"/>
     </row>
     <row r="172" spans="1:7" ht="28.5" x14ac:dyDescent="0.2">
       <c r="A172" s="3"/>
-      <c r="B172" s="3"/>
-      <c r="C172" s="3"/>
+      <c r="B172" s="3" t="s">
+        <v>267</v>
+      </c>
+      <c r="C172" s="3" t="s">
+        <v>81</v>
+      </c>
       <c r="D172" s="3" t="s">
-        <v>193</v>
+        <v>132</v>
       </c>
       <c r="E172" s="4" t="s">
-        <v>197</v>
+        <v>244</v>
       </c>
       <c r="F172" s="2" t="s">
-        <v>302</v>
-      </c>
-      <c r="G172" s="3"/>
-    </row>
-    <row r="173" spans="1:7" x14ac:dyDescent="0.2">
+        <v>303</v>
+      </c>
+      <c r="G172" s="2"/>
+    </row>
+    <row r="173" spans="1:7" ht="28.5" x14ac:dyDescent="0.2">
       <c r="A173" s="3"/>
       <c r="B173" s="3"/>
       <c r="C173" s="3"/>
       <c r="D173" s="3" t="s">
-        <v>193</v>
+        <v>132</v>
       </c>
       <c r="E173" s="4" t="s">
-        <v>202</v>
-      </c>
-      <c r="F173" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="G173" s="3"/>
+        <v>34</v>
+      </c>
+      <c r="F173" s="2" t="s">
+        <v>304</v>
+      </c>
+      <c r="G173" s="2"/>
     </row>
     <row r="174" spans="1:7" ht="28.5" x14ac:dyDescent="0.2">
       <c r="A174" s="3"/>
       <c r="B174" s="3" t="s">
-        <v>303</v>
+        <v>268</v>
       </c>
       <c r="C174" s="3" t="s">
-        <v>304</v>
+        <v>82</v>
       </c>
       <c r="D174" s="3" t="s">
-        <v>193</v>
+        <v>132</v>
       </c>
       <c r="E174" s="4" t="s">
+        <v>244</v>
+      </c>
+      <c r="F174" s="2" t="s">
         <v>305</v>
       </c>
-      <c r="F174" s="2" t="s">
-        <v>307</v>
-      </c>
-      <c r="G174" s="21" t="s">
-        <v>477</v>
-      </c>
+      <c r="G174" s="2"/>
     </row>
     <row r="175" spans="1:7" ht="28.5" x14ac:dyDescent="0.2">
       <c r="A175" s="3"/>
       <c r="B175" s="3"/>
       <c r="C175" s="3"/>
       <c r="D175" s="3" t="s">
-        <v>193</v>
+        <v>132</v>
       </c>
       <c r="E175" s="4" t="s">
-        <v>46</v>
+        <v>34</v>
       </c>
       <c r="F175" s="2" t="s">
-        <v>308</v>
-      </c>
-      <c r="G175" s="3"/>
+        <v>306</v>
+      </c>
+      <c r="G175" s="2"/>
     </row>
     <row r="176" spans="1:7" ht="28.5" x14ac:dyDescent="0.2">
       <c r="A176" s="3"/>
       <c r="B176" s="3" t="s">
-        <v>306</v>
+        <v>269</v>
       </c>
       <c r="C176" s="3" t="s">
-        <v>312</v>
+        <v>83</v>
       </c>
       <c r="D176" s="3" t="s">
-        <v>193</v>
+        <v>132</v>
       </c>
       <c r="E176" s="4" t="s">
-        <v>305</v>
+        <v>244</v>
       </c>
       <c r="F176" s="2" t="s">
-        <v>313</v>
-      </c>
-      <c r="G176" s="3"/>
+        <v>307</v>
+      </c>
+      <c r="G176" s="2"/>
     </row>
     <row r="177" spans="1:7" ht="28.5" x14ac:dyDescent="0.2">
       <c r="A177" s="3"/>
       <c r="B177" s="3"/>
       <c r="C177" s="3"/>
       <c r="D177" s="3" t="s">
-        <v>193</v>
+        <v>132</v>
       </c>
       <c r="E177" s="4" t="s">
-        <v>46</v>
+        <v>34</v>
       </c>
       <c r="F177" s="2" t="s">
-        <v>314</v>
-      </c>
-      <c r="G177" s="3"/>
+        <v>308</v>
+      </c>
+      <c r="G177" s="2"/>
     </row>
     <row r="178" spans="1:7" ht="28.5" x14ac:dyDescent="0.2">
       <c r="A178" s="3"/>
       <c r="B178" s="3" t="s">
-        <v>309</v>
+        <v>270</v>
       </c>
       <c r="C178" s="3" t="s">
-        <v>103</v>
+        <v>84</v>
       </c>
       <c r="D178" s="3" t="s">
-        <v>193</v>
+        <v>132</v>
       </c>
       <c r="E178" s="4" t="s">
-        <v>305</v>
+        <v>244</v>
       </c>
       <c r="F178" s="2" t="s">
-        <v>315</v>
-      </c>
-      <c r="G178" s="3"/>
+        <v>314</v>
+      </c>
+      <c r="G178" s="2"/>
     </row>
     <row r="179" spans="1:7" ht="28.5" x14ac:dyDescent="0.2">
       <c r="A179" s="3"/>
       <c r="B179" s="3"/>
       <c r="C179" s="3"/>
       <c r="D179" s="3" t="s">
-        <v>193</v>
+        <v>132</v>
       </c>
       <c r="E179" s="4" t="s">
-        <v>46</v>
+        <v>34</v>
       </c>
       <c r="F179" s="2" t="s">
-        <v>316</v>
-      </c>
-      <c r="G179" s="3"/>
+        <v>315</v>
+      </c>
+      <c r="G179" s="2"/>
     </row>
     <row r="180" spans="1:7" ht="28.5" x14ac:dyDescent="0.2">
       <c r="A180" s="3"/>
       <c r="B180" s="3" t="s">
-        <v>310</v>
+        <v>271</v>
       </c>
       <c r="C180" s="3" t="s">
-        <v>109</v>
+        <v>85</v>
       </c>
       <c r="D180" s="3" t="s">
-        <v>193</v>
+        <v>132</v>
       </c>
       <c r="E180" s="4" t="s">
-        <v>305</v>
+        <v>244</v>
       </c>
       <c r="F180" s="2" t="s">
-        <v>317</v>
-      </c>
-      <c r="G180" s="3"/>
+        <v>316</v>
+      </c>
+      <c r="G180" s="2"/>
     </row>
     <row r="181" spans="1:7" ht="28.5" x14ac:dyDescent="0.2">
       <c r="A181" s="3"/>
       <c r="B181" s="3"/>
       <c r="C181" s="3"/>
       <c r="D181" s="3" t="s">
-        <v>193</v>
+        <v>132</v>
       </c>
       <c r="E181" s="4" t="s">
-        <v>46</v>
+        <v>34</v>
       </c>
       <c r="F181" s="2" t="s">
-        <v>318</v>
-      </c>
-      <c r="G181" s="3"/>
+        <v>317</v>
+      </c>
+      <c r="G181" s="2"/>
     </row>
     <row r="182" spans="1:7" ht="28.5" x14ac:dyDescent="0.2">
       <c r="A182" s="3"/>
       <c r="B182" s="3" t="s">
-        <v>311</v>
+        <v>272</v>
       </c>
       <c r="C182" s="3" t="s">
-        <v>116</v>
+        <v>86</v>
       </c>
       <c r="D182" s="3" t="s">
-        <v>193</v>
+        <v>132</v>
       </c>
       <c r="E182" s="4" t="s">
-        <v>305</v>
+        <v>244</v>
       </c>
       <c r="F182" s="2" t="s">
-        <v>319</v>
-      </c>
-      <c r="G182" s="3"/>
+        <v>318</v>
+      </c>
+      <c r="G182" s="2"/>
     </row>
     <row r="183" spans="1:7" ht="28.5" x14ac:dyDescent="0.2">
       <c r="A183" s="3"/>
       <c r="B183" s="3"/>
       <c r="C183" s="3"/>
       <c r="D183" s="3" t="s">
-        <v>193</v>
+        <v>132</v>
       </c>
       <c r="E183" s="4" t="s">
-        <v>46</v>
+        <v>34</v>
       </c>
       <c r="F183" s="2" t="s">
-        <v>325</v>
-      </c>
-      <c r="G183" s="3"/>
+        <v>319</v>
+      </c>
+      <c r="G183" s="2"/>
     </row>
     <row r="184" spans="1:7" ht="28.5" x14ac:dyDescent="0.2">
       <c r="A184" s="3"/>
       <c r="B184" s="3" t="s">
+        <v>273</v>
+      </c>
+      <c r="C184" s="3" t="s">
+        <v>87</v>
+      </c>
+      <c r="D184" s="3" t="s">
+        <v>132</v>
+      </c>
+      <c r="E184" s="4" t="s">
+        <v>244</v>
+      </c>
+      <c r="F184" s="2" t="s">
         <v>320</v>
-      </c>
-      <c r="C184" s="3" t="s">
-        <v>165</v>
-      </c>
-      <c r="D184" s="3" t="s">
-        <v>193</v>
-      </c>
-      <c r="E184" s="4" t="s">
-        <v>305</v>
-      </c>
-      <c r="F184" s="2" t="s">
-        <v>343</v>
       </c>
       <c r="G184" s="2"/>
     </row>
@@ -5422,32 +5056,32 @@
       <c r="B185" s="3"/>
       <c r="C185" s="3"/>
       <c r="D185" s="3" t="s">
-        <v>193</v>
+        <v>132</v>
       </c>
       <c r="E185" s="4" t="s">
-        <v>46</v>
+        <v>34</v>
       </c>
       <c r="F185" s="2" t="s">
-        <v>344</v>
+        <v>321</v>
       </c>
       <c r="G185" s="2"/>
     </row>
     <row r="186" spans="1:7" ht="28.5" x14ac:dyDescent="0.2">
       <c r="A186" s="3"/>
       <c r="B186" s="3" t="s">
-        <v>321</v>
+        <v>274</v>
       </c>
       <c r="C186" s="3" t="s">
-        <v>346</v>
+        <v>88</v>
       </c>
       <c r="D186" s="3" t="s">
-        <v>193</v>
+        <v>132</v>
       </c>
       <c r="E186" s="4" t="s">
-        <v>305</v>
+        <v>244</v>
       </c>
       <c r="F186" s="2" t="s">
-        <v>336</v>
+        <v>322</v>
       </c>
       <c r="G186" s="2"/>
     </row>
@@ -5456,32 +5090,32 @@
       <c r="B187" s="3"/>
       <c r="C187" s="3"/>
       <c r="D187" s="3" t="s">
-        <v>193</v>
+        <v>132</v>
       </c>
       <c r="E187" s="4" t="s">
-        <v>46</v>
+        <v>34</v>
       </c>
       <c r="F187" s="2" t="s">
-        <v>337</v>
+        <v>323</v>
       </c>
       <c r="G187" s="2"/>
     </row>
     <row r="188" spans="1:7" ht="28.5" x14ac:dyDescent="0.2">
       <c r="A188" s="3"/>
       <c r="B188" s="3" t="s">
-        <v>322</v>
+        <v>289</v>
       </c>
       <c r="C188" s="3" t="s">
-        <v>347</v>
+        <v>309</v>
       </c>
       <c r="D188" s="3" t="s">
-        <v>193</v>
+        <v>132</v>
       </c>
       <c r="E188" s="4" t="s">
-        <v>305</v>
+        <v>244</v>
       </c>
       <c r="F188" s="2" t="s">
-        <v>338</v>
+        <v>336</v>
       </c>
       <c r="G188" s="2"/>
     </row>
@@ -5490,32 +5124,32 @@
       <c r="B189" s="3"/>
       <c r="C189" s="3"/>
       <c r="D189" s="3" t="s">
-        <v>193</v>
+        <v>132</v>
       </c>
       <c r="E189" s="4" t="s">
-        <v>46</v>
+        <v>34</v>
       </c>
       <c r="F189" s="2" t="s">
-        <v>339</v>
+        <v>337</v>
       </c>
       <c r="G189" s="2"/>
     </row>
     <row r="190" spans="1:7" ht="28.5" x14ac:dyDescent="0.2">
       <c r="A190" s="3"/>
       <c r="B190" s="3" t="s">
-        <v>323</v>
+        <v>290</v>
       </c>
       <c r="C190" s="3" t="s">
-        <v>348</v>
+        <v>310</v>
       </c>
       <c r="D190" s="3" t="s">
-        <v>193</v>
+        <v>132</v>
       </c>
       <c r="E190" s="4" t="s">
-        <v>305</v>
+        <v>244</v>
       </c>
       <c r="F190" s="2" t="s">
-        <v>340</v>
+        <v>338</v>
       </c>
       <c r="G190" s="2"/>
     </row>
@@ -5524,32 +5158,32 @@
       <c r="B191" s="3"/>
       <c r="C191" s="3"/>
       <c r="D191" s="3" t="s">
-        <v>193</v>
+        <v>132</v>
       </c>
       <c r="E191" s="4" t="s">
-        <v>46</v>
+        <v>34</v>
       </c>
       <c r="F191" s="2" t="s">
-        <v>341</v>
+        <v>339</v>
       </c>
       <c r="G191" s="2"/>
     </row>
     <row r="192" spans="1:7" ht="28.5" x14ac:dyDescent="0.2">
       <c r="A192" s="3"/>
       <c r="B192" s="3" t="s">
-        <v>324</v>
+        <v>291</v>
       </c>
       <c r="C192" s="3" t="s">
-        <v>349</v>
+        <v>311</v>
       </c>
       <c r="D192" s="3" t="s">
-        <v>193</v>
+        <v>132</v>
       </c>
       <c r="E192" s="4" t="s">
-        <v>305</v>
+        <v>244</v>
       </c>
       <c r="F192" s="2" t="s">
-        <v>342</v>
+        <v>340</v>
       </c>
       <c r="G192" s="2"/>
     </row>
@@ -5558,32 +5192,32 @@
       <c r="B193" s="3"/>
       <c r="C193" s="3"/>
       <c r="D193" s="3" t="s">
-        <v>193</v>
+        <v>132</v>
       </c>
       <c r="E193" s="4" t="s">
-        <v>46</v>
+        <v>34</v>
       </c>
       <c r="F193" s="2" t="s">
-        <v>345</v>
+        <v>341</v>
       </c>
       <c r="G193" s="2"/>
     </row>
     <row r="194" spans="1:7" ht="28.5" x14ac:dyDescent="0.2">
       <c r="A194" s="3"/>
       <c r="B194" s="3" t="s">
-        <v>326</v>
+        <v>292</v>
       </c>
       <c r="C194" s="3" t="s">
-        <v>126</v>
+        <v>312</v>
       </c>
       <c r="D194" s="3" t="s">
-        <v>193</v>
+        <v>132</v>
       </c>
       <c r="E194" s="4" t="s">
-        <v>305</v>
+        <v>244</v>
       </c>
       <c r="F194" s="2" t="s">
-        <v>360</v>
+        <v>342</v>
       </c>
       <c r="G194" s="2"/>
     </row>
@@ -5592,32 +5226,32 @@
       <c r="B195" s="3"/>
       <c r="C195" s="3"/>
       <c r="D195" s="3" t="s">
-        <v>193</v>
+        <v>132</v>
       </c>
       <c r="E195" s="4" t="s">
-        <v>46</v>
+        <v>34</v>
       </c>
       <c r="F195" s="2" t="s">
-        <v>361</v>
+        <v>343</v>
       </c>
       <c r="G195" s="2"/>
     </row>
     <row r="196" spans="1:7" ht="28.5" x14ac:dyDescent="0.2">
       <c r="A196" s="3"/>
       <c r="B196" s="3" t="s">
-        <v>327</v>
+        <v>293</v>
       </c>
       <c r="C196" s="3" t="s">
-        <v>127</v>
+        <v>313</v>
       </c>
       <c r="D196" s="3" t="s">
-        <v>193</v>
+        <v>132</v>
       </c>
       <c r="E196" s="4" t="s">
-        <v>305</v>
+        <v>244</v>
       </c>
       <c r="F196" s="2" t="s">
-        <v>362</v>
+        <v>344</v>
       </c>
       <c r="G196" s="2"/>
     </row>
@@ -5626,32 +5260,32 @@
       <c r="B197" s="3"/>
       <c r="C197" s="3"/>
       <c r="D197" s="3" t="s">
-        <v>193</v>
+        <v>132</v>
       </c>
       <c r="E197" s="4" t="s">
-        <v>46</v>
+        <v>34</v>
       </c>
       <c r="F197" s="2" t="s">
-        <v>363</v>
+        <v>345</v>
       </c>
       <c r="G197" s="2"/>
     </row>
     <row r="198" spans="1:7" ht="28.5" x14ac:dyDescent="0.2">
       <c r="A198" s="3"/>
       <c r="B198" s="3" t="s">
-        <v>328</v>
+        <v>294</v>
       </c>
       <c r="C198" s="3" t="s">
-        <v>128</v>
+        <v>326</v>
       </c>
       <c r="D198" s="3" t="s">
-        <v>193</v>
+        <v>132</v>
       </c>
       <c r="E198" s="4" t="s">
-        <v>305</v>
+        <v>244</v>
       </c>
       <c r="F198" s="2" t="s">
-        <v>364</v>
+        <v>353</v>
       </c>
       <c r="G198" s="2"/>
     </row>
@@ -5660,32 +5294,32 @@
       <c r="B199" s="3"/>
       <c r="C199" s="3"/>
       <c r="D199" s="3" t="s">
-        <v>193</v>
+        <v>132</v>
       </c>
       <c r="E199" s="4" t="s">
-        <v>46</v>
+        <v>34</v>
       </c>
       <c r="F199" s="2" t="s">
-        <v>365</v>
+        <v>354</v>
       </c>
       <c r="G199" s="2"/>
     </row>
     <row r="200" spans="1:7" ht="28.5" x14ac:dyDescent="0.2">
       <c r="A200" s="3"/>
       <c r="B200" s="3" t="s">
-        <v>329</v>
+        <v>295</v>
       </c>
       <c r="C200" s="3" t="s">
-        <v>129</v>
+        <v>327</v>
       </c>
       <c r="D200" s="3" t="s">
-        <v>193</v>
+        <v>132</v>
       </c>
       <c r="E200" s="4" t="s">
-        <v>305</v>
+        <v>244</v>
       </c>
       <c r="F200" s="2" t="s">
-        <v>366</v>
+        <v>355</v>
       </c>
       <c r="G200" s="2"/>
     </row>
@@ -5694,32 +5328,32 @@
       <c r="B201" s="3"/>
       <c r="C201" s="3"/>
       <c r="D201" s="3" t="s">
-        <v>193</v>
+        <v>132</v>
       </c>
       <c r="E201" s="4" t="s">
-        <v>46</v>
+        <v>34</v>
       </c>
       <c r="F201" s="2" t="s">
-        <v>367</v>
+        <v>356</v>
       </c>
       <c r="G201" s="2"/>
     </row>
     <row r="202" spans="1:7" ht="28.5" x14ac:dyDescent="0.2">
       <c r="A202" s="3"/>
       <c r="B202" s="3" t="s">
-        <v>330</v>
+        <v>296</v>
       </c>
       <c r="C202" s="3" t="s">
-        <v>130</v>
+        <v>328</v>
       </c>
       <c r="D202" s="3" t="s">
-        <v>193</v>
+        <v>132</v>
       </c>
       <c r="E202" s="4" t="s">
-        <v>305</v>
+        <v>244</v>
       </c>
       <c r="F202" s="2" t="s">
-        <v>368</v>
+        <v>357</v>
       </c>
       <c r="G202" s="2"/>
     </row>
@@ -5728,32 +5362,32 @@
       <c r="B203" s="3"/>
       <c r="C203" s="3"/>
       <c r="D203" s="3" t="s">
-        <v>193</v>
+        <v>132</v>
       </c>
       <c r="E203" s="4" t="s">
-        <v>46</v>
+        <v>34</v>
       </c>
       <c r="F203" s="2" t="s">
-        <v>369</v>
+        <v>358</v>
       </c>
       <c r="G203" s="2"/>
     </row>
     <row r="204" spans="1:7" ht="28.5" x14ac:dyDescent="0.2">
       <c r="A204" s="3"/>
       <c r="B204" s="3" t="s">
-        <v>331</v>
+        <v>297</v>
       </c>
       <c r="C204" s="3" t="s">
-        <v>131</v>
+        <v>329</v>
       </c>
       <c r="D204" s="3" t="s">
-        <v>193</v>
+        <v>132</v>
       </c>
       <c r="E204" s="4" t="s">
-        <v>305</v>
+        <v>244</v>
       </c>
       <c r="F204" s="2" t="s">
-        <v>375</v>
+        <v>359</v>
       </c>
       <c r="G204" s="2"/>
     </row>
@@ -5762,32 +5396,32 @@
       <c r="B205" s="3"/>
       <c r="C205" s="3"/>
       <c r="D205" s="3" t="s">
-        <v>193</v>
+        <v>132</v>
       </c>
       <c r="E205" s="4" t="s">
-        <v>46</v>
+        <v>34</v>
       </c>
       <c r="F205" s="2" t="s">
-        <v>376</v>
+        <v>360</v>
       </c>
       <c r="G205" s="2"/>
     </row>
     <row r="206" spans="1:7" ht="28.5" x14ac:dyDescent="0.2">
       <c r="A206" s="3"/>
       <c r="B206" s="3" t="s">
-        <v>332</v>
+        <v>298</v>
       </c>
       <c r="C206" s="3" t="s">
-        <v>132</v>
+        <v>330</v>
       </c>
       <c r="D206" s="3" t="s">
-        <v>193</v>
+        <v>132</v>
       </c>
       <c r="E206" s="4" t="s">
-        <v>305</v>
+        <v>244</v>
       </c>
       <c r="F206" s="2" t="s">
-        <v>377</v>
+        <v>361</v>
       </c>
       <c r="G206" s="2"/>
     </row>
@@ -5796,32 +5430,32 @@
       <c r="B207" s="3"/>
       <c r="C207" s="3"/>
       <c r="D207" s="3" t="s">
-        <v>193</v>
+        <v>132</v>
       </c>
       <c r="E207" s="4" t="s">
-        <v>46</v>
+        <v>34</v>
       </c>
       <c r="F207" s="2" t="s">
-        <v>378</v>
+        <v>362</v>
       </c>
       <c r="G207" s="2"/>
     </row>
     <row r="208" spans="1:7" ht="28.5" x14ac:dyDescent="0.2">
       <c r="A208" s="3"/>
       <c r="B208" s="3" t="s">
-        <v>333</v>
+        <v>324</v>
       </c>
       <c r="C208" s="3" t="s">
-        <v>133</v>
+        <v>331</v>
       </c>
       <c r="D208" s="3" t="s">
-        <v>193</v>
+        <v>132</v>
       </c>
       <c r="E208" s="4" t="s">
-        <v>305</v>
+        <v>244</v>
       </c>
       <c r="F208" s="2" t="s">
-        <v>379</v>
+        <v>370</v>
       </c>
       <c r="G208" s="2"/>
     </row>
@@ -5830,32 +5464,32 @@
       <c r="B209" s="3"/>
       <c r="C209" s="3"/>
       <c r="D209" s="3" t="s">
-        <v>193</v>
+        <v>132</v>
       </c>
       <c r="E209" s="4" t="s">
-        <v>46</v>
+        <v>34</v>
       </c>
       <c r="F209" s="2" t="s">
-        <v>380</v>
+        <v>371</v>
       </c>
       <c r="G209" s="2"/>
     </row>
     <row r="210" spans="1:7" ht="28.5" x14ac:dyDescent="0.2">
       <c r="A210" s="3"/>
       <c r="B210" s="3" t="s">
-        <v>334</v>
+        <v>325</v>
       </c>
       <c r="C210" s="3" t="s">
-        <v>134</v>
+        <v>332</v>
       </c>
       <c r="D210" s="3" t="s">
-        <v>193</v>
+        <v>132</v>
       </c>
       <c r="E210" s="4" t="s">
-        <v>305</v>
+        <v>244</v>
       </c>
       <c r="F210" s="2" t="s">
-        <v>381</v>
+        <v>372</v>
       </c>
       <c r="G210" s="2"/>
     </row>
@@ -5864,575 +5498,533 @@
       <c r="B211" s="3"/>
       <c r="C211" s="3"/>
       <c r="D211" s="3" t="s">
-        <v>193</v>
+        <v>132</v>
       </c>
       <c r="E211" s="4" t="s">
-        <v>46</v>
+        <v>34</v>
       </c>
       <c r="F211" s="2" t="s">
-        <v>382</v>
+        <v>373</v>
       </c>
       <c r="G211" s="2"/>
     </row>
-    <row r="212" spans="1:7" ht="28.5" x14ac:dyDescent="0.2">
-      <c r="A212" s="3"/>
-      <c r="B212" s="3" t="s">
-        <v>335</v>
-      </c>
-      <c r="C212" s="3" t="s">
-        <v>135</v>
-      </c>
-      <c r="D212" s="3" t="s">
-        <v>193</v>
-      </c>
-      <c r="E212" s="4" t="s">
-        <v>305</v>
-      </c>
-      <c r="F212" s="2" t="s">
-        <v>383</v>
-      </c>
+    <row r="212" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A212" s="20" t="s">
+        <v>146</v>
+      </c>
+      <c r="B212" s="3"/>
+      <c r="C212" s="3"/>
+      <c r="D212" s="3"/>
+      <c r="E212" s="4"/>
+      <c r="F212" s="1"/>
       <c r="G212" s="2"/>
     </row>
-    <row r="213" spans="1:7" ht="28.5" x14ac:dyDescent="0.2">
+    <row r="213" spans="1:7" ht="57" x14ac:dyDescent="0.2">
       <c r="A213" s="3"/>
-      <c r="B213" s="3"/>
-      <c r="C213" s="3"/>
+      <c r="B213" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="C213" s="3" t="s">
+        <v>333</v>
+      </c>
       <c r="D213" s="3" t="s">
-        <v>193</v>
+        <v>8</v>
       </c>
       <c r="E213" s="4" t="s">
-        <v>46</v>
-      </c>
-      <c r="F213" s="2" t="s">
-        <v>384</v>
-      </c>
-      <c r="G213" s="2"/>
-    </row>
-    <row r="214" spans="1:7" ht="28.5" x14ac:dyDescent="0.2">
+        <v>147</v>
+      </c>
+      <c r="F213" s="5" t="s">
+        <v>148</v>
+      </c>
+      <c r="G213" s="5" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="214" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A214" s="3"/>
-      <c r="B214" s="3" t="s">
-        <v>350</v>
-      </c>
-      <c r="C214" s="3" t="s">
-        <v>370</v>
-      </c>
-      <c r="D214" s="3" t="s">
-        <v>193</v>
-      </c>
+      <c r="B214" s="3"/>
+      <c r="C214" s="3"/>
+      <c r="D214" s="3"/>
       <c r="E214" s="4" t="s">
-        <v>305</v>
-      </c>
-      <c r="F214" s="2" t="s">
-        <v>397</v>
-      </c>
-      <c r="G214" s="2"/>
+        <v>149</v>
+      </c>
+      <c r="F214" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="G214" s="5"/>
     </row>
     <row r="215" spans="1:7" ht="28.5" x14ac:dyDescent="0.2">
       <c r="A215" s="3"/>
       <c r="B215" s="3"/>
       <c r="C215" s="3"/>
       <c r="D215" s="3" t="s">
-        <v>193</v>
+        <v>8</v>
       </c>
       <c r="E215" s="4" t="s">
-        <v>46</v>
-      </c>
-      <c r="F215" s="2" t="s">
-        <v>398</v>
-      </c>
-      <c r="G215" s="2"/>
-    </row>
-    <row r="216" spans="1:7" ht="28.5" x14ac:dyDescent="0.2">
+        <v>134</v>
+      </c>
+      <c r="F215" s="5" t="s">
+        <v>150</v>
+      </c>
+      <c r="G215" s="3"/>
+    </row>
+    <row r="216" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A216" s="3"/>
-      <c r="B216" s="3" t="s">
-        <v>351</v>
-      </c>
-      <c r="C216" s="3" t="s">
-        <v>371</v>
-      </c>
-      <c r="D216" s="3" t="s">
-        <v>193</v>
-      </c>
+      <c r="B216" s="3"/>
+      <c r="C216" s="3"/>
+      <c r="D216" s="3"/>
       <c r="E216" s="4" t="s">
-        <v>305</v>
-      </c>
-      <c r="F216" s="2" t="s">
-        <v>399</v>
-      </c>
-      <c r="G216" s="2"/>
+        <v>139</v>
+      </c>
+      <c r="F216" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="G216" s="3"/>
     </row>
     <row r="217" spans="1:7" ht="28.5" x14ac:dyDescent="0.2">
       <c r="A217" s="3"/>
       <c r="B217" s="3"/>
       <c r="C217" s="3"/>
       <c r="D217" s="3" t="s">
-        <v>193</v>
+        <v>8</v>
       </c>
       <c r="E217" s="4" t="s">
-        <v>46</v>
-      </c>
-      <c r="F217" s="2" t="s">
-        <v>400</v>
-      </c>
-      <c r="G217" s="2"/>
-    </row>
-    <row r="218" spans="1:7" ht="28.5" x14ac:dyDescent="0.2">
+        <v>135</v>
+      </c>
+      <c r="F217" s="5" t="s">
+        <v>151</v>
+      </c>
+      <c r="G217" s="3"/>
+    </row>
+    <row r="218" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A218" s="3"/>
-      <c r="B218" s="3" t="s">
-        <v>352</v>
-      </c>
-      <c r="C218" s="3" t="s">
-        <v>372</v>
-      </c>
-      <c r="D218" s="3" t="s">
-        <v>193</v>
-      </c>
+      <c r="B218" s="3"/>
+      <c r="C218" s="3"/>
+      <c r="D218" s="3"/>
       <c r="E218" s="4" t="s">
-        <v>305</v>
-      </c>
-      <c r="F218" s="2" t="s">
-        <v>401</v>
-      </c>
-      <c r="G218" s="2"/>
+        <v>152</v>
+      </c>
+      <c r="F218" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="G218" s="3"/>
     </row>
     <row r="219" spans="1:7" ht="28.5" x14ac:dyDescent="0.2">
       <c r="A219" s="3"/>
-      <c r="B219" s="3"/>
-      <c r="C219" s="3"/>
+      <c r="B219" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="C219" s="3" t="s">
+        <v>334</v>
+      </c>
       <c r="D219" s="3" t="s">
-        <v>193</v>
+        <v>8</v>
       </c>
       <c r="E219" s="4" t="s">
-        <v>46</v>
-      </c>
-      <c r="F219" s="2" t="s">
-        <v>402</v>
-      </c>
-      <c r="G219" s="2"/>
+        <v>26</v>
+      </c>
+      <c r="F219" s="5" t="s">
+        <v>47</v>
+      </c>
+      <c r="G219" s="3"/>
     </row>
     <row r="220" spans="1:7" ht="28.5" x14ac:dyDescent="0.2">
       <c r="A220" s="3"/>
-      <c r="B220" s="3" t="s">
-        <v>353</v>
-      </c>
-      <c r="C220" s="3" t="s">
-        <v>373</v>
-      </c>
+      <c r="B220" s="3"/>
+      <c r="C220" s="3"/>
       <c r="D220" s="3" t="s">
-        <v>193</v>
-      </c>
-      <c r="E220" s="4" t="s">
-        <v>305</v>
-      </c>
-      <c r="F220" s="2" t="s">
-        <v>403</v>
-      </c>
-      <c r="G220" s="2"/>
+        <v>8</v>
+      </c>
+      <c r="E220" s="17" t="s">
+        <v>11</v>
+      </c>
+      <c r="F220" s="18" t="s">
+        <v>46</v>
+      </c>
+      <c r="G220" s="19"/>
     </row>
     <row r="221" spans="1:7" ht="28.5" x14ac:dyDescent="0.2">
       <c r="A221" s="3"/>
       <c r="B221" s="3"/>
       <c r="C221" s="3"/>
       <c r="D221" s="3" t="s">
-        <v>193</v>
-      </c>
-      <c r="E221" s="4" t="s">
-        <v>46</v>
-      </c>
-      <c r="F221" s="2" t="s">
-        <v>404</v>
-      </c>
-      <c r="G221" s="2"/>
-    </row>
-    <row r="222" spans="1:7" ht="28.5" x14ac:dyDescent="0.2">
+        <v>8</v>
+      </c>
+      <c r="E221" s="17" t="s">
+        <v>27</v>
+      </c>
+      <c r="F221" s="18" t="s">
+        <v>48</v>
+      </c>
+      <c r="G221" s="16"/>
+    </row>
+    <row r="222" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A222" s="3"/>
-      <c r="B222" s="3" t="s">
-        <v>354</v>
-      </c>
-      <c r="C222" s="3" t="s">
-        <v>374</v>
-      </c>
-      <c r="D222" s="3" t="s">
-        <v>193</v>
-      </c>
+      <c r="B222" s="3"/>
+      <c r="C222" s="3"/>
+      <c r="D222" s="3"/>
       <c r="E222" s="4" t="s">
-        <v>305</v>
-      </c>
-      <c r="F222" s="2" t="s">
-        <v>405</v>
-      </c>
-      <c r="G222" s="2"/>
+        <v>395</v>
+      </c>
+      <c r="F222" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="G222" s="3"/>
     </row>
     <row r="223" spans="1:7" ht="28.5" x14ac:dyDescent="0.2">
       <c r="A223" s="3"/>
       <c r="B223" s="3"/>
       <c r="C223" s="3"/>
       <c r="D223" s="3" t="s">
-        <v>193</v>
+        <v>8</v>
       </c>
       <c r="E223" s="4" t="s">
-        <v>46</v>
-      </c>
-      <c r="F223" s="2" t="s">
-        <v>406</v>
-      </c>
-      <c r="G223" s="2"/>
+        <v>42</v>
+      </c>
+      <c r="F223" s="5" t="s">
+        <v>50</v>
+      </c>
+      <c r="G223" s="3"/>
     </row>
     <row r="224" spans="1:7" ht="28.5" x14ac:dyDescent="0.2">
       <c r="A224" s="3"/>
-      <c r="B224" s="3" t="s">
-        <v>355</v>
-      </c>
-      <c r="C224" s="3" t="s">
-        <v>387</v>
-      </c>
+      <c r="B224" s="3"/>
+      <c r="C224" s="3"/>
       <c r="D224" s="3" t="s">
-        <v>193</v>
+        <v>8</v>
       </c>
       <c r="E224" s="4" t="s">
-        <v>305</v>
-      </c>
-      <c r="F224" s="2" t="s">
-        <v>417</v>
-      </c>
-      <c r="G224" s="2"/>
+        <v>43</v>
+      </c>
+      <c r="F224" s="5" t="s">
+        <v>51</v>
+      </c>
+      <c r="G224" s="3"/>
     </row>
     <row r="225" spans="1:7" ht="28.5" x14ac:dyDescent="0.2">
       <c r="A225" s="3"/>
       <c r="B225" s="3"/>
       <c r="C225" s="3"/>
       <c r="D225" s="3" t="s">
-        <v>193</v>
+        <v>8</v>
       </c>
       <c r="E225" s="4" t="s">
-        <v>46</v>
-      </c>
-      <c r="F225" s="2" t="s">
-        <v>418</v>
-      </c>
-      <c r="G225" s="2"/>
+        <v>44</v>
+      </c>
+      <c r="F225" s="5" t="s">
+        <v>52</v>
+      </c>
+      <c r="G225" s="3"/>
     </row>
     <row r="226" spans="1:7" ht="28.5" x14ac:dyDescent="0.2">
       <c r="A226" s="3"/>
-      <c r="B226" s="3" t="s">
-        <v>356</v>
-      </c>
-      <c r="C226" s="3" t="s">
-        <v>388</v>
-      </c>
+      <c r="B226" s="3"/>
+      <c r="C226" s="3"/>
       <c r="D226" s="3" t="s">
-        <v>193</v>
+        <v>8</v>
       </c>
       <c r="E226" s="4" t="s">
-        <v>305</v>
-      </c>
-      <c r="F226" s="2" t="s">
-        <v>419</v>
-      </c>
-      <c r="G226" s="2"/>
+        <v>45</v>
+      </c>
+      <c r="F226" s="5" t="s">
+        <v>49</v>
+      </c>
+      <c r="G226" s="3" t="s">
+        <v>53</v>
+      </c>
     </row>
     <row r="227" spans="1:7" ht="28.5" x14ac:dyDescent="0.2">
       <c r="A227" s="3"/>
       <c r="B227" s="3"/>
       <c r="C227" s="3"/>
       <c r="D227" s="3" t="s">
-        <v>193</v>
+        <v>8</v>
       </c>
       <c r="E227" s="4" t="s">
-        <v>46</v>
-      </c>
-      <c r="F227" s="2" t="s">
-        <v>420</v>
-      </c>
-      <c r="G227" s="2"/>
-    </row>
-    <row r="228" spans="1:7" ht="28.5" x14ac:dyDescent="0.2">
+        <v>378</v>
+      </c>
+      <c r="F227" s="5" t="s">
+        <v>130</v>
+      </c>
+      <c r="G227" s="3" t="s">
+        <v>377</v>
+      </c>
+    </row>
+    <row r="228" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A228" s="3"/>
-      <c r="B228" s="3" t="s">
-        <v>357</v>
-      </c>
-      <c r="C228" s="3" t="s">
-        <v>389</v>
-      </c>
-      <c r="D228" s="3" t="s">
-        <v>193</v>
-      </c>
+      <c r="B228" s="3"/>
+      <c r="C228" s="3"/>
+      <c r="D228" s="3"/>
       <c r="E228" s="4" t="s">
-        <v>305</v>
-      </c>
-      <c r="F228" s="2" t="s">
-        <v>421</v>
-      </c>
-      <c r="G228" s="2"/>
+        <v>379</v>
+      </c>
+      <c r="F228" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="G228" s="3"/>
     </row>
     <row r="229" spans="1:7" ht="28.5" x14ac:dyDescent="0.2">
       <c r="A229" s="3"/>
-      <c r="B229" s="3"/>
-      <c r="C229" s="3"/>
+      <c r="B229" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="C229" s="3" t="s">
+        <v>335</v>
+      </c>
       <c r="D229" s="3" t="s">
-        <v>193</v>
+        <v>8</v>
       </c>
       <c r="E229" s="4" t="s">
-        <v>46</v>
-      </c>
-      <c r="F229" s="2" t="s">
-        <v>422</v>
-      </c>
-      <c r="G229" s="2"/>
+        <v>35</v>
+      </c>
+      <c r="F229" s="5" t="s">
+        <v>55</v>
+      </c>
+      <c r="G229" s="3"/>
     </row>
     <row r="230" spans="1:7" ht="28.5" x14ac:dyDescent="0.2">
-      <c r="A230" s="3"/>
-      <c r="B230" s="3" t="s">
-        <v>358</v>
-      </c>
-      <c r="C230" s="3" t="s">
-        <v>390</v>
-      </c>
-      <c r="D230" s="3" t="s">
-        <v>193</v>
-      </c>
-      <c r="E230" s="4" t="s">
-        <v>305</v>
-      </c>
-      <c r="F230" s="2" t="s">
-        <v>423</v>
-      </c>
-      <c r="G230" s="2"/>
+      <c r="A230" s="20"/>
+      <c r="B230" s="20" t="s">
+        <v>56</v>
+      </c>
+      <c r="C230" s="20" t="s">
+        <v>346</v>
+      </c>
+      <c r="D230" s="20" t="s">
+        <v>14</v>
+      </c>
+      <c r="E230" s="21" t="s">
+        <v>26</v>
+      </c>
+      <c r="F230" s="22" t="s">
+        <v>383</v>
+      </c>
+      <c r="G230" s="20"/>
     </row>
     <row r="231" spans="1:7" ht="28.5" x14ac:dyDescent="0.2">
-      <c r="A231" s="3"/>
-      <c r="B231" s="3"/>
-      <c r="C231" s="3"/>
-      <c r="D231" s="3" t="s">
-        <v>193</v>
-      </c>
-      <c r="E231" s="4" t="s">
-        <v>46</v>
-      </c>
-      <c r="F231" s="2" t="s">
-        <v>424</v>
-      </c>
-      <c r="G231" s="2"/>
+      <c r="A231" s="20"/>
+      <c r="B231" s="20"/>
+      <c r="C231" s="20"/>
+      <c r="D231" s="20" t="s">
+        <v>381</v>
+      </c>
+      <c r="E231" s="21" t="s">
+        <v>382</v>
+      </c>
+      <c r="F231" s="22" t="s">
+        <v>385</v>
+      </c>
+      <c r="G231" s="20"/>
     </row>
     <row r="232" spans="1:7" ht="28.5" x14ac:dyDescent="0.2">
-      <c r="A232" s="3"/>
-      <c r="B232" s="3" t="s">
-        <v>359</v>
-      </c>
-      <c r="C232" s="3" t="s">
-        <v>391</v>
-      </c>
-      <c r="D232" s="3" t="s">
-        <v>193</v>
-      </c>
-      <c r="E232" s="4" t="s">
-        <v>305</v>
-      </c>
-      <c r="F232" s="2" t="s">
-        <v>425</v>
-      </c>
-      <c r="G232" s="2"/>
+      <c r="A232" s="20"/>
+      <c r="B232" s="20"/>
+      <c r="C232" s="20"/>
+      <c r="D232" s="20" t="s">
+        <v>14</v>
+      </c>
+      <c r="E232" s="21" t="s">
+        <v>27</v>
+      </c>
+      <c r="F232" s="22" t="s">
+        <v>384</v>
+      </c>
+      <c r="G232" s="20" t="s">
+        <v>58</v>
+      </c>
     </row>
     <row r="233" spans="1:7" ht="28.5" x14ac:dyDescent="0.2">
-      <c r="A233" s="3"/>
-      <c r="B233" s="3"/>
-      <c r="C233" s="3"/>
-      <c r="D233" s="3" t="s">
-        <v>193</v>
-      </c>
-      <c r="E233" s="4" t="s">
-        <v>46</v>
-      </c>
-      <c r="F233" s="2" t="s">
-        <v>426</v>
-      </c>
-      <c r="G233" s="2"/>
+      <c r="A233" s="20"/>
+      <c r="B233" s="20"/>
+      <c r="C233" s="20"/>
+      <c r="D233" s="20" t="s">
+        <v>14</v>
+      </c>
+      <c r="E233" s="21" t="s">
+        <v>13</v>
+      </c>
+      <c r="F233" s="22" t="s">
+        <v>389</v>
+      </c>
+      <c r="G233" s="20" t="s">
+        <v>127</v>
+      </c>
     </row>
     <row r="234" spans="1:7" ht="28.5" x14ac:dyDescent="0.2">
-      <c r="A234" s="3"/>
-      <c r="B234" s="3" t="s">
-        <v>385</v>
-      </c>
-      <c r="C234" s="3" t="s">
-        <v>392</v>
-      </c>
-      <c r="D234" s="3" t="s">
-        <v>193</v>
-      </c>
-      <c r="E234" s="4" t="s">
-        <v>305</v>
-      </c>
-      <c r="F234" s="2" t="s">
-        <v>434</v>
-      </c>
-      <c r="G234" s="2"/>
+      <c r="A234" s="20"/>
+      <c r="B234" s="20"/>
+      <c r="C234" s="20"/>
+      <c r="D234" s="20" t="s">
+        <v>386</v>
+      </c>
+      <c r="E234" s="21" t="s">
+        <v>387</v>
+      </c>
+      <c r="F234" s="22" t="s">
+        <v>388</v>
+      </c>
+      <c r="G234" s="20" t="s">
+        <v>127</v>
+      </c>
     </row>
     <row r="235" spans="1:7" ht="28.5" x14ac:dyDescent="0.2">
-      <c r="A235" s="3"/>
-      <c r="B235" s="3"/>
-      <c r="C235" s="3"/>
-      <c r="D235" s="3" t="s">
-        <v>193</v>
-      </c>
-      <c r="E235" s="4" t="s">
-        <v>46</v>
-      </c>
-      <c r="F235" s="2" t="s">
-        <v>435</v>
-      </c>
-      <c r="G235" s="2"/>
-    </row>
-    <row r="236" spans="1:7" ht="28.5" x14ac:dyDescent="0.2">
-      <c r="A236" s="3"/>
-      <c r="B236" s="3" t="s">
-        <v>386</v>
-      </c>
-      <c r="C236" s="3" t="s">
-        <v>393</v>
-      </c>
-      <c r="D236" s="3" t="s">
-        <v>193</v>
-      </c>
-      <c r="E236" s="4" t="s">
-        <v>305</v>
-      </c>
-      <c r="F236" s="2" t="s">
-        <v>436</v>
-      </c>
-      <c r="G236" s="2"/>
-    </row>
-    <row r="237" spans="1:7" ht="28.5" x14ac:dyDescent="0.2">
-      <c r="A237" s="3"/>
+      <c r="A235" s="20"/>
+      <c r="B235" s="20"/>
+      <c r="C235" s="20"/>
+      <c r="D235" s="20" t="s">
+        <v>14</v>
+      </c>
+      <c r="E235" s="21" t="s">
+        <v>16</v>
+      </c>
+      <c r="F235" s="22" t="s">
+        <v>57</v>
+      </c>
+      <c r="G235" s="20"/>
+    </row>
+    <row r="236" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A236" s="20"/>
+      <c r="B236" s="20"/>
+      <c r="C236" s="20"/>
+      <c r="D236" s="20"/>
+      <c r="E236" s="21" t="s">
+        <v>396</v>
+      </c>
+      <c r="F236" s="20" t="s">
+        <v>25</v>
+      </c>
+      <c r="G236" s="20"/>
+    </row>
+    <row r="237" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A237" s="3" t="s">
+        <v>59</v>
+      </c>
       <c r="B237" s="3"/>
       <c r="C237" s="3"/>
-      <c r="D237" s="3" t="s">
-        <v>193</v>
-      </c>
-      <c r="E237" s="4" t="s">
-        <v>46</v>
-      </c>
-      <c r="F237" s="2" t="s">
-        <v>437</v>
-      </c>
-      <c r="G237" s="2"/>
-    </row>
-    <row r="238" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A238" s="3" t="s">
-        <v>207</v>
-      </c>
-      <c r="B238" s="3"/>
-      <c r="C238" s="3"/>
-      <c r="D238" s="3"/>
-      <c r="E238" s="4"/>
-      <c r="F238" s="1"/>
+      <c r="D237" s="3"/>
+      <c r="E237" s="4"/>
+      <c r="F237" s="3"/>
+      <c r="G237" s="3"/>
+    </row>
+    <row r="238" spans="1:7" ht="28.5" x14ac:dyDescent="0.2">
+      <c r="A238" s="3"/>
+      <c r="B238" s="3" t="s">
+        <v>60</v>
+      </c>
+      <c r="C238" s="3" t="s">
+        <v>347</v>
+      </c>
+      <c r="D238" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E238" s="4" t="s">
+        <v>37</v>
+      </c>
+      <c r="F238" s="5" t="s">
+        <v>62</v>
+      </c>
       <c r="G238" s="3"/>
     </row>
-    <row r="239" spans="1:7" ht="57" x14ac:dyDescent="0.2">
+    <row r="239" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A239" s="3"/>
-      <c r="B239" s="3" t="s">
-        <v>75</v>
-      </c>
-      <c r="C239" s="3" t="s">
-        <v>394</v>
-      </c>
-      <c r="D239" s="3" t="s">
-        <v>8</v>
-      </c>
+      <c r="B239" s="3"/>
+      <c r="C239" s="3"/>
+      <c r="D239" s="3"/>
       <c r="E239" s="4" t="s">
-        <v>208</v>
-      </c>
-      <c r="F239" s="5" t="s">
-        <v>209</v>
-      </c>
-      <c r="G239" s="5" t="s">
-        <v>78</v>
-      </c>
-    </row>
-    <row r="240" spans="1:7" x14ac:dyDescent="0.2">
+        <v>38</v>
+      </c>
+      <c r="F239" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="G239" s="3"/>
+    </row>
+    <row r="240" spans="1:7" ht="28.5" x14ac:dyDescent="0.2">
       <c r="A240" s="3"/>
       <c r="B240" s="3"/>
       <c r="C240" s="3"/>
-      <c r="D240" s="3"/>
+      <c r="D240" s="3" t="s">
+        <v>8</v>
+      </c>
       <c r="E240" s="4" t="s">
-        <v>210</v>
-      </c>
-      <c r="F240" s="3" t="s">
-        <v>79</v>
+        <v>110</v>
+      </c>
+      <c r="F240" s="5" t="s">
+        <v>63</v>
       </c>
       <c r="G240" s="3"/>
     </row>
-    <row r="241" spans="1:7" ht="28.5" x14ac:dyDescent="0.2">
+    <row r="241" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A241" s="3"/>
       <c r="B241" s="3"/>
       <c r="C241" s="3"/>
-      <c r="D241" s="3" t="s">
-        <v>8</v>
-      </c>
+      <c r="D241" s="3"/>
       <c r="E241" s="4" t="s">
-        <v>195</v>
-      </c>
-      <c r="F241" s="5" t="s">
-        <v>211</v>
+        <v>111</v>
+      </c>
+      <c r="F241" s="3" t="s">
+        <v>64</v>
       </c>
       <c r="G241" s="3"/>
     </row>
-    <row r="242" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="242" spans="1:7" ht="28.5" x14ac:dyDescent="0.2">
       <c r="A242" s="3"/>
       <c r="B242" s="3"/>
       <c r="C242" s="3"/>
-      <c r="D242" s="3"/>
+      <c r="D242" s="3" t="s">
+        <v>8</v>
+      </c>
       <c r="E242" s="4" t="s">
-        <v>200</v>
-      </c>
-      <c r="F242" s="3" t="s">
-        <v>79</v>
+        <v>112</v>
+      </c>
+      <c r="F242" s="5" t="s">
+        <v>65</v>
       </c>
       <c r="G242" s="3"/>
     </row>
-    <row r="243" spans="1:7" ht="28.5" x14ac:dyDescent="0.2">
+    <row r="243" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A243" s="3"/>
       <c r="B243" s="3"/>
       <c r="C243" s="3"/>
-      <c r="D243" s="3" t="s">
-        <v>8</v>
-      </c>
+      <c r="D243" s="3"/>
       <c r="E243" s="4" t="s">
-        <v>196</v>
-      </c>
-      <c r="F243" s="5" t="s">
-        <v>212</v>
+        <v>113</v>
+      </c>
+      <c r="F243" s="3" t="s">
+        <v>25</v>
       </c>
       <c r="G243" s="3"/>
     </row>
-    <row r="244" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="244" spans="1:7" ht="28.5" x14ac:dyDescent="0.2">
       <c r="A244" s="3"/>
-      <c r="B244" s="3"/>
-      <c r="C244" s="3"/>
-      <c r="D244" s="3"/>
+      <c r="B244" s="3" t="s">
+        <v>66</v>
+      </c>
+      <c r="C244" s="3" t="s">
+        <v>348</v>
+      </c>
+      <c r="D244" s="3" t="s">
+        <v>68</v>
+      </c>
       <c r="E244" s="4" t="s">
-        <v>213</v>
-      </c>
-      <c r="F244" s="3" t="s">
-        <v>79</v>
+        <v>69</v>
+      </c>
+      <c r="F244" s="5" t="s">
+        <v>71</v>
       </c>
       <c r="G244" s="3"/>
     </row>
     <row r="245" spans="1:7" ht="28.5" x14ac:dyDescent="0.2">
       <c r="A245" s="3"/>
-      <c r="B245" s="3" t="s">
-        <v>80</v>
-      </c>
-      <c r="C245" s="3" t="s">
-        <v>395</v>
-      </c>
+      <c r="B245" s="3"/>
+      <c r="C245" s="3"/>
       <c r="D245" s="3" t="s">
-        <v>8</v>
+        <v>68</v>
       </c>
       <c r="E245" s="4" t="s">
-        <v>33</v>
+        <v>70</v>
       </c>
       <c r="F245" s="5" t="s">
-        <v>86</v>
+        <v>72</v>
       </c>
       <c r="G245" s="3"/>
     </row>
@@ -6440,397 +6032,357 @@
       <c r="A246" s="3"/>
       <c r="B246" s="3"/>
       <c r="C246" s="3"/>
-      <c r="D246" s="24" t="s">
-        <v>8</v>
-      </c>
-      <c r="E246" s="25" t="s">
-        <v>12</v>
-      </c>
-      <c r="F246" s="26" t="s">
-        <v>87</v>
-      </c>
-      <c r="G246" s="24"/>
-    </row>
-    <row r="247" spans="1:7" ht="28.5" x14ac:dyDescent="0.2">
+      <c r="D246" s="3" t="s">
+        <v>68</v>
+      </c>
+      <c r="E246" s="4" t="s">
+        <v>376</v>
+      </c>
+      <c r="F246" s="5" t="s">
+        <v>375</v>
+      </c>
+      <c r="G246" s="3"/>
+    </row>
+    <row r="247" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A247" s="3"/>
       <c r="B247" s="3"/>
       <c r="C247" s="3"/>
-      <c r="D247" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="E247" s="27" t="s">
-        <v>12</v>
-      </c>
-      <c r="F247" s="5" t="s">
-        <v>85</v>
+      <c r="D247" s="3"/>
+      <c r="E247" s="4" t="s">
+        <v>380</v>
+      </c>
+      <c r="F247" s="3" t="s">
+        <v>25</v>
       </c>
       <c r="G247" s="3"/>
     </row>
     <row r="248" spans="1:7" ht="28.5" x14ac:dyDescent="0.2">
       <c r="A248" s="3"/>
-      <c r="B248" s="3"/>
-      <c r="C248" s="3"/>
+      <c r="B248" s="3" t="s">
+        <v>73</v>
+      </c>
+      <c r="C248" s="3" t="s">
+        <v>349</v>
+      </c>
       <c r="D248" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="E248" s="27" t="s">
-        <v>35</v>
+        <v>75</v>
+      </c>
+      <c r="E248" s="4" t="s">
+        <v>69</v>
       </c>
       <c r="F248" s="5" t="s">
-        <v>88</v>
+        <v>76</v>
       </c>
       <c r="G248" s="3"/>
     </row>
-    <row r="249" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="249" spans="1:7" ht="28.5" x14ac:dyDescent="0.2">
       <c r="A249" s="3"/>
       <c r="B249" s="3"/>
       <c r="C249" s="3"/>
-      <c r="D249" s="3"/>
+      <c r="D249" s="3" t="s">
+        <v>75</v>
+      </c>
       <c r="E249" s="4" t="s">
-        <v>478</v>
-      </c>
-      <c r="F249" s="3" t="s">
-        <v>32</v>
+        <v>70</v>
+      </c>
+      <c r="F249" s="5" t="s">
+        <v>77</v>
       </c>
       <c r="G249" s="3"/>
     </row>
-    <row r="250" spans="1:7" ht="28.5" x14ac:dyDescent="0.2">
+    <row r="250" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A250" s="3"/>
       <c r="B250" s="3"/>
       <c r="C250" s="3"/>
-      <c r="D250" s="3" t="s">
-        <v>8</v>
-      </c>
+      <c r="D250" s="3"/>
       <c r="E250" s="4" t="s">
-        <v>81</v>
+        <v>398</v>
       </c>
       <c r="F250" s="5" t="s">
-        <v>90</v>
+        <v>25</v>
       </c>
       <c r="G250" s="3"/>
     </row>
-    <row r="251" spans="1:7" ht="28.5" x14ac:dyDescent="0.2">
-      <c r="A251" s="3"/>
+    <row r="251" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A251" s="3" t="s">
+        <v>399</v>
+      </c>
       <c r="B251" s="3"/>
       <c r="C251" s="3"/>
-      <c r="D251" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="E251" s="4" t="s">
-        <v>82</v>
-      </c>
-      <c r="F251" s="5" t="s">
+      <c r="D251" s="3"/>
+      <c r="E251" s="4"/>
+      <c r="F251" s="3"/>
+      <c r="G251" s="3"/>
+    </row>
+    <row r="252" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A252" s="3"/>
+      <c r="B252" s="3" t="s">
+        <v>89</v>
+      </c>
+      <c r="C252" s="3" t="s">
+        <v>350</v>
+      </c>
+      <c r="D252" s="3" t="s">
+        <v>78</v>
+      </c>
+      <c r="E252" s="4" t="s">
+        <v>99</v>
+      </c>
+      <c r="F252" s="3" t="s">
+        <v>100</v>
+      </c>
+      <c r="G252" s="3"/>
+    </row>
+    <row r="253" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A253" s="3"/>
+      <c r="B253" s="3" t="s">
+        <v>90</v>
+      </c>
+      <c r="C253" s="3" t="s">
+        <v>351</v>
+      </c>
+      <c r="D253" s="3" t="s">
+        <v>78</v>
+      </c>
+      <c r="E253" s="4" t="s">
+        <v>99</v>
+      </c>
+      <c r="F253" s="3" t="s">
+        <v>101</v>
+      </c>
+      <c r="G253" s="3"/>
+    </row>
+    <row r="254" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A254" s="3"/>
+      <c r="B254" s="3" t="s">
         <v>91</v>
       </c>
-      <c r="G251" s="3"/>
-    </row>
-    <row r="252" spans="1:7" ht="28.5" x14ac:dyDescent="0.2">
-      <c r="A252" s="3"/>
-      <c r="B252" s="3"/>
-      <c r="C252" s="3"/>
-      <c r="D252" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="E252" s="4" t="s">
-        <v>83</v>
-      </c>
-      <c r="F252" s="5" t="s">
-        <v>92</v>
-      </c>
-      <c r="G252" s="3"/>
-    </row>
-    <row r="253" spans="1:7" ht="28.5" x14ac:dyDescent="0.2">
-      <c r="A253" s="3"/>
-      <c r="B253" s="3"/>
-      <c r="C253" s="3"/>
-      <c r="D253" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="E253" s="4" t="s">
-        <v>84</v>
-      </c>
-      <c r="F253" s="5" t="s">
-        <v>89</v>
-      </c>
-      <c r="G253" s="3" t="s">
-        <v>93</v>
-      </c>
-    </row>
-    <row r="254" spans="1:7" ht="28.5" x14ac:dyDescent="0.2">
-      <c r="A254" s="3"/>
-      <c r="B254" s="3"/>
-      <c r="C254" s="3"/>
+      <c r="C254" s="3" t="s">
+        <v>352</v>
+      </c>
       <c r="D254" s="3" t="s">
-        <v>8</v>
+        <v>78</v>
       </c>
       <c r="E254" s="4" t="s">
-        <v>444</v>
-      </c>
-      <c r="F254" s="5" t="s">
-        <v>190</v>
-      </c>
-      <c r="G254" s="3" t="s">
-        <v>443</v>
-      </c>
+        <v>99</v>
+      </c>
+      <c r="F254" s="3" t="s">
+        <v>102</v>
+      </c>
+      <c r="G254" s="3"/>
     </row>
     <row r="255" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A255" s="3"/>
-      <c r="B255" s="3"/>
-      <c r="C255" s="3"/>
-      <c r="D255" s="3"/>
+      <c r="B255" s="3" t="s">
+        <v>92</v>
+      </c>
+      <c r="C255" s="3" t="s">
+        <v>363</v>
+      </c>
+      <c r="D255" s="3" t="s">
+        <v>78</v>
+      </c>
       <c r="E255" s="4" t="s">
-        <v>445</v>
+        <v>99</v>
       </c>
       <c r="F255" s="3" t="s">
-        <v>32</v>
+        <v>103</v>
       </c>
       <c r="G255" s="3"/>
     </row>
-    <row r="256" spans="1:7" ht="28.5" x14ac:dyDescent="0.2">
-      <c r="A256" s="3" t="s">
+    <row r="256" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A256" s="3"/>
+      <c r="B256" s="3" t="s">
+        <v>93</v>
+      </c>
+      <c r="C256" s="3" t="s">
+        <v>364</v>
+      </c>
+      <c r="D256" s="3" t="s">
+        <v>78</v>
+      </c>
+      <c r="E256" s="4" t="s">
         <v>99</v>
       </c>
-      <c r="B256" s="3" t="s">
+      <c r="F256" s="3" t="s">
+        <v>104</v>
+      </c>
+      <c r="G256" s="3"/>
+    </row>
+    <row r="257" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A257" s="3"/>
+      <c r="B257" s="3" t="s">
         <v>94</v>
       </c>
-      <c r="C256" s="3" t="s">
-        <v>396</v>
-      </c>
-      <c r="D256" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="E256" s="4" t="s">
-        <v>74</v>
-      </c>
-      <c r="F256" s="5" t="s">
+      <c r="C257" s="3" t="s">
+        <v>365</v>
+      </c>
+      <c r="D257" s="3" t="s">
+        <v>78</v>
+      </c>
+      <c r="E257" s="4" t="s">
+        <v>99</v>
+      </c>
+      <c r="F257" s="3" t="s">
+        <v>105</v>
+      </c>
+      <c r="G257" s="3"/>
+    </row>
+    <row r="258" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A258" s="3"/>
+      <c r="B258" s="3" t="s">
         <v>95</v>
       </c>
-      <c r="G256" s="3"/>
-    </row>
-    <row r="257" spans="1:7" ht="28.5" x14ac:dyDescent="0.2">
-      <c r="A257" s="3"/>
-      <c r="B257" s="10" t="s">
+      <c r="C258" s="3" t="s">
+        <v>366</v>
+      </c>
+      <c r="D258" s="3" t="s">
+        <v>78</v>
+      </c>
+      <c r="E258" s="4" t="s">
+        <v>99</v>
+      </c>
+      <c r="F258" s="3" t="s">
+        <v>106</v>
+      </c>
+      <c r="G258" s="3"/>
+    </row>
+    <row r="259" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A259" s="3"/>
+      <c r="B259" s="3" t="s">
         <v>96</v>
       </c>
-      <c r="C257" s="10" t="s">
-        <v>407</v>
-      </c>
-      <c r="D257" s="10" t="s">
-        <v>16</v>
-      </c>
-      <c r="E257" s="7" t="s">
-        <v>33</v>
-      </c>
-      <c r="F257" s="18" t="s">
-        <v>460</v>
-      </c>
-      <c r="G257" s="10"/>
-    </row>
-    <row r="258" spans="1:7" ht="28.5" x14ac:dyDescent="0.2">
-      <c r="A258" s="3"/>
-      <c r="B258" s="10"/>
-      <c r="C258" s="10"/>
-      <c r="D258" s="10" t="s">
-        <v>458</v>
-      </c>
-      <c r="E258" s="7" t="s">
-        <v>459</v>
-      </c>
-      <c r="F258" s="18" t="s">
-        <v>465</v>
-      </c>
-      <c r="G258" s="10"/>
-    </row>
-    <row r="259" spans="1:7" ht="28.5" x14ac:dyDescent="0.2">
-      <c r="A259" s="3"/>
-      <c r="B259" s="10"/>
-      <c r="C259" s="10"/>
-      <c r="D259" s="10" t="s">
-        <v>16</v>
-      </c>
-      <c r="E259" s="7" t="s">
-        <v>35</v>
-      </c>
-      <c r="F259" s="18" t="s">
-        <v>461</v>
-      </c>
-      <c r="G259" s="10" t="s">
+      <c r="C259" s="3" t="s">
+        <v>367</v>
+      </c>
+      <c r="D259" s="3" t="s">
+        <v>78</v>
+      </c>
+      <c r="E259" s="4" t="s">
+        <v>99</v>
+      </c>
+      <c r="F259" s="3" t="s">
+        <v>107</v>
+      </c>
+      <c r="G259" s="3"/>
+    </row>
+    <row r="260" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A260" s="3"/>
+      <c r="B260" s="3" t="s">
+        <v>97</v>
+      </c>
+      <c r="C260" s="3" t="s">
+        <v>368</v>
+      </c>
+      <c r="D260" s="3" t="s">
+        <v>78</v>
+      </c>
+      <c r="E260" s="4" t="s">
+        <v>99</v>
+      </c>
+      <c r="F260" s="3" t="s">
+        <v>109</v>
+      </c>
+      <c r="G260" s="3"/>
+    </row>
+    <row r="261" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A261" s="3"/>
+      <c r="B261" s="3" t="s">
         <v>98</v>
       </c>
-    </row>
-    <row r="260" spans="1:7" ht="28.5" x14ac:dyDescent="0.2">
-      <c r="A260" s="3"/>
-      <c r="B260" s="10"/>
-      <c r="C260" s="10"/>
-      <c r="D260" s="10" t="s">
-        <v>16</v>
-      </c>
-      <c r="E260" s="7" t="s">
-        <v>15</v>
-      </c>
-      <c r="F260" s="18" t="s">
-        <v>469</v>
-      </c>
-      <c r="G260" s="10" t="s">
-        <v>177</v>
-      </c>
-    </row>
-    <row r="261" spans="1:7" ht="28.5" x14ac:dyDescent="0.2">
-      <c r="A261" s="3"/>
-      <c r="B261" s="10"/>
-      <c r="C261" s="10"/>
-      <c r="D261" s="10" t="s">
-        <v>466</v>
-      </c>
-      <c r="E261" s="7" t="s">
-        <v>467</v>
-      </c>
-      <c r="F261" s="18" t="s">
-        <v>468</v>
-      </c>
-      <c r="G261" s="10" t="s">
-        <v>177</v>
-      </c>
-    </row>
-    <row r="262" spans="1:7" ht="28.5" x14ac:dyDescent="0.2">
+      <c r="C261" s="3" t="s">
+        <v>369</v>
+      </c>
+      <c r="D261" s="3" t="s">
+        <v>78</v>
+      </c>
+      <c r="E261" s="4" t="s">
+        <v>99</v>
+      </c>
+      <c r="F261" s="3" t="s">
+        <v>108</v>
+      </c>
+      <c r="G261" s="3"/>
+    </row>
+    <row r="262" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A262" s="3"/>
-      <c r="B262" s="10"/>
-      <c r="C262" s="10"/>
-      <c r="D262" s="10" t="s">
-        <v>16</v>
-      </c>
-      <c r="E262" s="7" t="s">
-        <v>19</v>
-      </c>
-      <c r="F262" s="13" t="s">
-        <v>97</v>
-      </c>
-      <c r="G262" s="10"/>
-    </row>
-    <row r="263" spans="1:7" ht="42.75" x14ac:dyDescent="0.2">
+      <c r="B262" s="3"/>
+      <c r="C262" s="3"/>
+      <c r="D262" s="3"/>
+      <c r="E262" s="4"/>
+      <c r="F262" s="3"/>
+      <c r="G262" s="3"/>
+    </row>
+    <row r="263" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A263" s="3"/>
-      <c r="B263" s="10"/>
-      <c r="C263" s="10"/>
-      <c r="D263" s="10" t="s">
-        <v>16</v>
-      </c>
-      <c r="E263" s="7" t="s">
-        <v>23</v>
-      </c>
-      <c r="F263" s="18" t="s">
-        <v>464</v>
-      </c>
-      <c r="G263" s="10" t="s">
-        <v>177</v>
-      </c>
-    </row>
-    <row r="264" spans="1:7" ht="42.75" x14ac:dyDescent="0.2">
+      <c r="B263" s="3"/>
+      <c r="C263" s="3"/>
+      <c r="D263" s="3"/>
+      <c r="E263" s="4"/>
+      <c r="F263" s="5"/>
+      <c r="G263" s="3"/>
+    </row>
+    <row r="264" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A264" s="3"/>
-      <c r="B264" s="10"/>
-      <c r="C264" s="10"/>
-      <c r="D264" s="10" t="s">
-        <v>16</v>
-      </c>
-      <c r="E264" s="7" t="s">
-        <v>53</v>
-      </c>
-      <c r="F264" s="18" t="s">
-        <v>462</v>
-      </c>
-      <c r="G264" s="10" t="s">
-        <v>463</v>
-      </c>
+      <c r="B264" s="3"/>
+      <c r="C264" s="3"/>
+      <c r="D264" s="3"/>
+      <c r="E264" s="4"/>
+      <c r="F264" s="3"/>
+      <c r="G264" s="3"/>
     </row>
     <row r="265" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A265" s="3"/>
-      <c r="B265" s="10"/>
-      <c r="C265" s="10"/>
-      <c r="D265" s="10"/>
-      <c r="E265" s="7" t="s">
-        <v>470</v>
-      </c>
-      <c r="F265" s="10" t="s">
-        <v>32</v>
-      </c>
-      <c r="G265" s="10"/>
-    </row>
-    <row r="266" spans="1:7" ht="28.5" x14ac:dyDescent="0.2">
+      <c r="B265" s="3"/>
+      <c r="C265" s="3"/>
+      <c r="D265" s="3"/>
+      <c r="E265" s="4"/>
+      <c r="F265" s="3"/>
+      <c r="G265" s="3"/>
+    </row>
+    <row r="266" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A266" s="3"/>
-      <c r="B266" s="3" t="s">
-        <v>100</v>
-      </c>
-      <c r="C266" s="3" t="s">
-        <v>408</v>
-      </c>
-      <c r="D266" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="E266" s="4" t="s">
-        <v>33</v>
-      </c>
-      <c r="F266" s="5" t="s">
-        <v>90</v>
-      </c>
+      <c r="B266" s="3"/>
+      <c r="C266" s="3"/>
+      <c r="D266" s="3"/>
+      <c r="E266" s="4"/>
+      <c r="F266" s="3"/>
       <c r="G266" s="3"/>
     </row>
-    <row r="267" spans="1:7" ht="28.5" x14ac:dyDescent="0.2">
+    <row r="267" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A267" s="3"/>
       <c r="B267" s="3"/>
       <c r="C267" s="3"/>
-      <c r="D267" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="E267" s="4" t="s">
-        <v>12</v>
-      </c>
-      <c r="F267" s="5" t="s">
-        <v>91</v>
-      </c>
+      <c r="D267" s="3"/>
+      <c r="E267" s="4"/>
+      <c r="F267" s="3"/>
       <c r="G267" s="3"/>
     </row>
-    <row r="268" spans="1:7" ht="28.5" x14ac:dyDescent="0.2">
+    <row r="268" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A268" s="3"/>
       <c r="B268" s="3"/>
       <c r="C268" s="3"/>
-      <c r="D268" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="E268" s="4" t="s">
-        <v>35</v>
-      </c>
-      <c r="F268" s="5" t="s">
-        <v>92</v>
-      </c>
+      <c r="D268" s="3"/>
+      <c r="E268" s="4"/>
+      <c r="F268" s="3"/>
       <c r="G268" s="3"/>
     </row>
-    <row r="269" spans="1:7" ht="28.5" x14ac:dyDescent="0.2">
+    <row r="269" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A269" s="3"/>
       <c r="B269" s="3"/>
       <c r="C269" s="3"/>
-      <c r="D269" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="E269" s="4" t="s">
-        <v>15</v>
-      </c>
-      <c r="F269" s="5" t="s">
-        <v>89</v>
-      </c>
+      <c r="D269" s="3"/>
+      <c r="E269" s="4"/>
+      <c r="F269" s="3"/>
       <c r="G269" s="3"/>
     </row>
-    <row r="270" spans="1:7" ht="28.5" x14ac:dyDescent="0.2">
+    <row r="270" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A270" s="3"/>
       <c r="B270" s="3"/>
       <c r="C270" s="3"/>
-      <c r="D270" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="E270" s="4" t="s">
-        <v>442</v>
-      </c>
-      <c r="F270" s="5" t="s">
-        <v>439</v>
-      </c>
+      <c r="D270" s="3"/>
+      <c r="E270" s="4"/>
+      <c r="F270" s="3"/>
       <c r="G270" s="3"/>
     </row>
     <row r="271" spans="1:7" x14ac:dyDescent="0.2">
@@ -6838,31 +6390,17 @@
       <c r="B271" s="3"/>
       <c r="C271" s="3"/>
       <c r="D271" s="3"/>
-      <c r="E271" s="4" t="s">
-        <v>446</v>
-      </c>
-      <c r="F271" s="3" t="s">
-        <v>169</v>
-      </c>
+      <c r="E271" s="4"/>
+      <c r="F271" s="3"/>
       <c r="G271" s="3"/>
     </row>
-    <row r="272" spans="1:7" ht="28.5" x14ac:dyDescent="0.2">
+    <row r="272" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A272" s="3"/>
-      <c r="B272" s="3" t="s">
-        <v>448</v>
-      </c>
-      <c r="C272" s="3" t="s">
-        <v>409</v>
-      </c>
-      <c r="D272" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="E272" s="4" t="s">
-        <v>74</v>
-      </c>
-      <c r="F272" s="5" t="s">
-        <v>101</v>
-      </c>
+      <c r="B272" s="3"/>
+      <c r="C272" s="3"/>
+      <c r="D272" s="3"/>
+      <c r="E272" s="4"/>
+      <c r="F272" s="3"/>
       <c r="G272" s="3"/>
     </row>
     <row r="273" spans="1:7" x14ac:dyDescent="0.2">
@@ -6883,23 +6421,13 @@
       <c r="F274" s="3"/>
       <c r="G274" s="3"/>
     </row>
-    <row r="275" spans="1:7" ht="28.5" x14ac:dyDescent="0.2">
+    <row r="275" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A275" s="3"/>
-      <c r="B275" s="3" t="s">
-        <v>102</v>
-      </c>
-      <c r="C275" s="3" t="s">
-        <v>410</v>
-      </c>
-      <c r="D275" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="E275" s="4" t="s">
-        <v>76</v>
-      </c>
-      <c r="F275" s="5" t="s">
-        <v>104</v>
-      </c>
+      <c r="B275" s="3"/>
+      <c r="C275" s="3"/>
+      <c r="D275" s="3"/>
+      <c r="E275" s="4"/>
+      <c r="F275" s="3"/>
       <c r="G275" s="3"/>
     </row>
     <row r="276" spans="1:7" x14ac:dyDescent="0.2">
@@ -6907,27 +6435,17 @@
       <c r="B276" s="3"/>
       <c r="C276" s="3"/>
       <c r="D276" s="3"/>
-      <c r="E276" s="4" t="s">
-        <v>77</v>
-      </c>
-      <c r="F276" s="3" t="s">
-        <v>32</v>
-      </c>
+      <c r="E276" s="4"/>
+      <c r="F276" s="3"/>
       <c r="G276" s="3"/>
     </row>
-    <row r="277" spans="1:7" ht="28.5" x14ac:dyDescent="0.2">
+    <row r="277" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A277" s="3"/>
       <c r="B277" s="3"/>
       <c r="C277" s="3"/>
-      <c r="D277" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="E277" s="4" t="s">
-        <v>157</v>
-      </c>
-      <c r="F277" s="5" t="s">
-        <v>105</v>
-      </c>
+      <c r="D277" s="3"/>
+      <c r="E277" s="4"/>
+      <c r="F277" s="3"/>
       <c r="G277" s="3"/>
     </row>
     <row r="278" spans="1:7" x14ac:dyDescent="0.2">
@@ -6935,27 +6453,17 @@
       <c r="B278" s="3"/>
       <c r="C278" s="3"/>
       <c r="D278" s="3"/>
-      <c r="E278" s="4" t="s">
-        <v>158</v>
-      </c>
-      <c r="F278" s="3" t="s">
-        <v>106</v>
-      </c>
+      <c r="E278" s="4"/>
+      <c r="F278" s="3"/>
       <c r="G278" s="3"/>
     </row>
-    <row r="279" spans="1:7" ht="28.5" x14ac:dyDescent="0.2">
+    <row r="279" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A279" s="3"/>
       <c r="B279" s="3"/>
       <c r="C279" s="3"/>
-      <c r="D279" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="E279" s="4" t="s">
-        <v>159</v>
-      </c>
-      <c r="F279" s="5" t="s">
-        <v>107</v>
-      </c>
+      <c r="D279" s="3"/>
+      <c r="E279" s="4"/>
+      <c r="F279" s="3"/>
       <c r="G279" s="3"/>
     </row>
     <row r="280" spans="1:7" x14ac:dyDescent="0.2">
@@ -6963,61 +6471,35 @@
       <c r="B280" s="3"/>
       <c r="C280" s="3"/>
       <c r="D280" s="3"/>
-      <c r="E280" s="4" t="s">
-        <v>160</v>
-      </c>
-      <c r="F280" s="3" t="s">
-        <v>32</v>
-      </c>
+      <c r="E280" s="4"/>
+      <c r="F280" s="3"/>
       <c r="G280" s="3"/>
     </row>
-    <row r="281" spans="1:7" ht="28.5" x14ac:dyDescent="0.2">
+    <row r="281" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A281" s="3"/>
-      <c r="B281" s="3" t="s">
-        <v>108</v>
-      </c>
-      <c r="C281" s="3" t="s">
-        <v>411</v>
-      </c>
-      <c r="D281" s="3" t="s">
-        <v>110</v>
-      </c>
-      <c r="E281" s="4" t="s">
-        <v>111</v>
-      </c>
-      <c r="F281" s="5" t="s">
-        <v>113</v>
-      </c>
+      <c r="B281" s="3"/>
+      <c r="C281" s="3"/>
+      <c r="D281" s="3"/>
+      <c r="E281" s="4"/>
+      <c r="F281" s="3"/>
       <c r="G281" s="3"/>
     </row>
-    <row r="282" spans="1:7" ht="28.5" x14ac:dyDescent="0.2">
+    <row r="282" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A282" s="3"/>
       <c r="B282" s="3"/>
       <c r="C282" s="3"/>
-      <c r="D282" s="3" t="s">
-        <v>110</v>
-      </c>
-      <c r="E282" s="4" t="s">
-        <v>112</v>
-      </c>
-      <c r="F282" s="5" t="s">
-        <v>114</v>
-      </c>
+      <c r="D282" s="3"/>
+      <c r="E282" s="4"/>
+      <c r="F282" s="3"/>
       <c r="G282" s="3"/>
     </row>
-    <row r="283" spans="1:7" ht="28.5" x14ac:dyDescent="0.2">
+    <row r="283" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A283" s="3"/>
       <c r="B283" s="3"/>
       <c r="C283" s="3"/>
-      <c r="D283" s="3" t="s">
-        <v>110</v>
-      </c>
-      <c r="E283" s="4" t="s">
-        <v>441</v>
-      </c>
-      <c r="F283" s="5" t="s">
-        <v>440</v>
-      </c>
+      <c r="D283" s="3"/>
+      <c r="E283" s="4"/>
+      <c r="F283" s="3"/>
       <c r="G283" s="3"/>
     </row>
     <row r="284" spans="1:7" x14ac:dyDescent="0.2">
@@ -7025,61 +6507,35 @@
       <c r="B284" s="3"/>
       <c r="C284" s="3"/>
       <c r="D284" s="3"/>
-      <c r="E284" s="4" t="s">
-        <v>447</v>
-      </c>
-      <c r="F284" s="3" t="s">
-        <v>32</v>
-      </c>
+      <c r="E284" s="4"/>
+      <c r="F284" s="3"/>
       <c r="G284" s="3"/>
     </row>
-    <row r="285" spans="1:7" ht="28.5" x14ac:dyDescent="0.2">
+    <row r="285" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A285" s="3"/>
-      <c r="B285" s="3" t="s">
-        <v>115</v>
-      </c>
-      <c r="C285" s="3" t="s">
-        <v>412</v>
-      </c>
-      <c r="D285" s="3" t="s">
-        <v>117</v>
-      </c>
-      <c r="E285" s="4" t="s">
-        <v>111</v>
-      </c>
-      <c r="F285" s="5" t="s">
-        <v>119</v>
-      </c>
+      <c r="B285" s="3"/>
+      <c r="C285" s="3"/>
+      <c r="D285" s="3"/>
+      <c r="E285" s="4"/>
+      <c r="F285" s="3"/>
       <c r="G285" s="3"/>
     </row>
-    <row r="286" spans="1:7" ht="28.5" x14ac:dyDescent="0.2">
+    <row r="286" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A286" s="3"/>
       <c r="B286" s="3"/>
       <c r="C286" s="3"/>
-      <c r="D286" s="3" t="s">
-        <v>117</v>
-      </c>
-      <c r="E286" s="4" t="s">
-        <v>112</v>
-      </c>
-      <c r="F286" s="5" t="s">
-        <v>120</v>
-      </c>
+      <c r="D286" s="3"/>
+      <c r="E286" s="4"/>
+      <c r="F286" s="3"/>
       <c r="G286" s="3"/>
     </row>
-    <row r="287" spans="1:7" ht="28.5" x14ac:dyDescent="0.2">
+    <row r="287" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A287" s="3"/>
       <c r="B287" s="3"/>
       <c r="C287" s="3"/>
-      <c r="D287" s="3" t="s">
-        <v>117</v>
-      </c>
-      <c r="E287" s="4" t="s">
-        <v>118</v>
-      </c>
-      <c r="F287" s="5" t="s">
-        <v>121</v>
-      </c>
+      <c r="D287" s="3"/>
+      <c r="E287" s="4"/>
+      <c r="F287" s="3"/>
       <c r="G287" s="3"/>
     </row>
     <row r="288" spans="1:7" x14ac:dyDescent="0.2">
@@ -7087,57 +6543,35 @@
       <c r="B288" s="3"/>
       <c r="C288" s="3"/>
       <c r="D288" s="3"/>
-      <c r="E288" s="4" t="s">
-        <v>123</v>
-      </c>
-      <c r="F288" s="5" t="s">
-        <v>32</v>
-      </c>
+      <c r="E288" s="4"/>
+      <c r="F288" s="3"/>
       <c r="G288" s="3"/>
     </row>
-    <row r="289" spans="1:7" ht="28.5" x14ac:dyDescent="0.2">
+    <row r="289" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A289" s="3"/>
-      <c r="B289" s="3" t="s">
-        <v>122</v>
-      </c>
-      <c r="C289" s="3" t="s">
-        <v>413</v>
-      </c>
-      <c r="D289" s="3" t="s">
-        <v>124</v>
-      </c>
-      <c r="E289" s="4" t="s">
-        <v>111</v>
-      </c>
-      <c r="F289" s="5" t="s">
-        <v>113</v>
-      </c>
+      <c r="B289" s="3"/>
+      <c r="C289" s="3"/>
+      <c r="D289" s="3"/>
+      <c r="E289" s="4"/>
+      <c r="F289" s="3"/>
       <c r="G289" s="3"/>
     </row>
-    <row r="290" spans="1:7" ht="28.5" x14ac:dyDescent="0.2">
+    <row r="290" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A290" s="3"/>
       <c r="B290" s="3"/>
       <c r="C290" s="3"/>
       <c r="D290" s="3"/>
-      <c r="E290" s="4" t="s">
-        <v>112</v>
-      </c>
-      <c r="F290" s="5" t="s">
-        <v>114</v>
-      </c>
+      <c r="E290" s="4"/>
+      <c r="F290" s="3"/>
       <c r="G290" s="3"/>
     </row>
-    <row r="291" spans="1:7" ht="28.5" x14ac:dyDescent="0.2">
+    <row r="291" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A291" s="3"/>
       <c r="B291" s="3"/>
       <c r="C291" s="3"/>
       <c r="D291" s="3"/>
-      <c r="E291" s="4" t="s">
-        <v>441</v>
-      </c>
-      <c r="F291" s="5" t="s">
-        <v>191</v>
-      </c>
+      <c r="E291" s="4"/>
+      <c r="F291" s="3"/>
       <c r="G291" s="3"/>
     </row>
     <row r="292" spans="1:7" x14ac:dyDescent="0.2">
@@ -7145,18 +6579,12 @@
       <c r="B292" s="3"/>
       <c r="C292" s="3"/>
       <c r="D292" s="3"/>
-      <c r="E292" s="4" t="s">
-        <v>447</v>
-      </c>
-      <c r="F292" s="3" t="s">
-        <v>32</v>
-      </c>
+      <c r="E292" s="4"/>
+      <c r="F292" s="3"/>
       <c r="G292" s="3"/>
     </row>
     <row r="293" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A293" s="3" t="s">
-        <v>125</v>
-      </c>
+      <c r="A293" s="3"/>
       <c r="B293" s="3"/>
       <c r="C293" s="3"/>
       <c r="D293" s="3"/>
@@ -7166,192 +6594,92 @@
     </row>
     <row r="294" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A294" s="3"/>
-      <c r="B294" s="3" t="s">
-        <v>136</v>
-      </c>
-      <c r="C294" s="3" t="s">
-        <v>414</v>
-      </c>
-      <c r="D294" s="3" t="s">
-        <v>124</v>
-      </c>
-      <c r="E294" s="4" t="s">
-        <v>146</v>
-      </c>
-      <c r="F294" s="3" t="s">
-        <v>147</v>
-      </c>
+      <c r="B294" s="3"/>
+      <c r="C294" s="3"/>
+      <c r="D294" s="3"/>
+      <c r="E294" s="4"/>
+      <c r="F294" s="3"/>
       <c r="G294" s="3"/>
     </row>
     <row r="295" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A295" s="3"/>
-      <c r="B295" s="3" t="s">
-        <v>137</v>
-      </c>
-      <c r="C295" s="3" t="s">
-        <v>415</v>
-      </c>
-      <c r="D295" s="3" t="s">
-        <v>124</v>
-      </c>
-      <c r="E295" s="4" t="s">
-        <v>146</v>
-      </c>
-      <c r="F295" s="3" t="s">
-        <v>148</v>
-      </c>
+      <c r="B295" s="3"/>
+      <c r="C295" s="3"/>
+      <c r="D295" s="3"/>
+      <c r="E295" s="4"/>
+      <c r="F295" s="3"/>
       <c r="G295" s="3"/>
     </row>
     <row r="296" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A296" s="3"/>
-      <c r="B296" s="3" t="s">
-        <v>138</v>
-      </c>
-      <c r="C296" s="3" t="s">
-        <v>416</v>
-      </c>
-      <c r="D296" s="3" t="s">
-        <v>124</v>
-      </c>
-      <c r="E296" s="4" t="s">
-        <v>146</v>
-      </c>
-      <c r="F296" s="3" t="s">
-        <v>149</v>
-      </c>
+      <c r="B296" s="3"/>
+      <c r="C296" s="3"/>
+      <c r="D296" s="3"/>
+      <c r="E296" s="4"/>
+      <c r="F296" s="3"/>
       <c r="G296" s="3"/>
     </row>
     <row r="297" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A297" s="3"/>
-      <c r="B297" s="3" t="s">
-        <v>139</v>
-      </c>
-      <c r="C297" s="3" t="s">
-        <v>427</v>
-      </c>
-      <c r="D297" s="3" t="s">
-        <v>124</v>
-      </c>
-      <c r="E297" s="4" t="s">
-        <v>146</v>
-      </c>
-      <c r="F297" s="3" t="s">
-        <v>150</v>
-      </c>
+      <c r="B297" s="3"/>
+      <c r="C297" s="3"/>
+      <c r="D297" s="3"/>
+      <c r="E297" s="4"/>
+      <c r="F297" s="3"/>
       <c r="G297" s="3"/>
     </row>
     <row r="298" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A298" s="3"/>
-      <c r="B298" s="3" t="s">
-        <v>140</v>
-      </c>
-      <c r="C298" s="3" t="s">
-        <v>428</v>
-      </c>
-      <c r="D298" s="3" t="s">
-        <v>124</v>
-      </c>
-      <c r="E298" s="4" t="s">
-        <v>146</v>
-      </c>
-      <c r="F298" s="3" t="s">
-        <v>151</v>
-      </c>
+      <c r="B298" s="3"/>
+      <c r="C298" s="3"/>
+      <c r="D298" s="3"/>
+      <c r="E298" s="4"/>
+      <c r="F298" s="3"/>
       <c r="G298" s="3"/>
     </row>
     <row r="299" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A299" s="3"/>
-      <c r="B299" s="3" t="s">
-        <v>141</v>
-      </c>
-      <c r="C299" s="3" t="s">
-        <v>429</v>
-      </c>
-      <c r="D299" s="3" t="s">
-        <v>124</v>
-      </c>
-      <c r="E299" s="4" t="s">
-        <v>146</v>
-      </c>
-      <c r="F299" s="3" t="s">
-        <v>152</v>
-      </c>
+      <c r="B299" s="3"/>
+      <c r="C299" s="3"/>
+      <c r="D299" s="3"/>
+      <c r="E299" s="4"/>
+      <c r="F299" s="3"/>
       <c r="G299" s="3"/>
     </row>
     <row r="300" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A300" s="3"/>
-      <c r="B300" s="3" t="s">
-        <v>142</v>
-      </c>
-      <c r="C300" s="3" t="s">
-        <v>430</v>
-      </c>
-      <c r="D300" s="3" t="s">
-        <v>124</v>
-      </c>
-      <c r="E300" s="4" t="s">
-        <v>146</v>
-      </c>
-      <c r="F300" s="3" t="s">
-        <v>153</v>
-      </c>
+      <c r="B300" s="3"/>
+      <c r="C300" s="3"/>
+      <c r="D300" s="3"/>
+      <c r="E300" s="4"/>
+      <c r="F300" s="3"/>
       <c r="G300" s="3"/>
     </row>
     <row r="301" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A301" s="3"/>
-      <c r="B301" s="3" t="s">
-        <v>143</v>
-      </c>
-      <c r="C301" s="3" t="s">
-        <v>431</v>
-      </c>
-      <c r="D301" s="3" t="s">
-        <v>124</v>
-      </c>
-      <c r="E301" s="4" t="s">
-        <v>146</v>
-      </c>
-      <c r="F301" s="3" t="s">
-        <v>154</v>
-      </c>
+      <c r="B301" s="3"/>
+      <c r="C301" s="3"/>
+      <c r="D301" s="3"/>
+      <c r="E301" s="4"/>
+      <c r="F301" s="3"/>
       <c r="G301" s="3"/>
     </row>
     <row r="302" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A302" s="3"/>
-      <c r="B302" s="3" t="s">
-        <v>144</v>
-      </c>
-      <c r="C302" s="3" t="s">
-        <v>432</v>
-      </c>
-      <c r="D302" s="3" t="s">
-        <v>124</v>
-      </c>
-      <c r="E302" s="4" t="s">
-        <v>146</v>
-      </c>
-      <c r="F302" s="3" t="s">
-        <v>156</v>
-      </c>
+      <c r="B302" s="3"/>
+      <c r="C302" s="3"/>
+      <c r="D302" s="3"/>
+      <c r="E302" s="4"/>
+      <c r="F302" s="3"/>
       <c r="G302" s="3"/>
     </row>
     <row r="303" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A303" s="3"/>
-      <c r="B303" s="3" t="s">
-        <v>145</v>
-      </c>
-      <c r="C303" s="3" t="s">
-        <v>433</v>
-      </c>
-      <c r="D303" s="3" t="s">
-        <v>124</v>
-      </c>
-      <c r="E303" s="4" t="s">
-        <v>146</v>
-      </c>
-      <c r="F303" s="3" t="s">
-        <v>155</v>
-      </c>
+      <c r="B303" s="3"/>
+      <c r="C303" s="3"/>
+      <c r="D303" s="3"/>
+      <c r="E303" s="4"/>
+      <c r="F303" s="3"/>
       <c r="G303" s="3"/>
     </row>
     <row r="304" spans="1:7" x14ac:dyDescent="0.2">
@@ -7369,7 +6697,7 @@
       <c r="C305" s="3"/>
       <c r="D305" s="3"/>
       <c r="E305" s="4"/>
-      <c r="F305" s="5"/>
+      <c r="F305" s="3"/>
       <c r="G305" s="3"/>
     </row>
     <row r="306" spans="1:7" x14ac:dyDescent="0.2">
@@ -9420,7 +8748,7 @@
       <c r="B533" s="3"/>
       <c r="C533" s="3"/>
       <c r="D533" s="3"/>
-      <c r="E533" s="4"/>
+      <c r="E533" s="3"/>
       <c r="F533" s="3"/>
       <c r="G533" s="3"/>
     </row>
@@ -9429,376 +8757,26 @@
       <c r="B534" s="3"/>
       <c r="C534" s="3"/>
       <c r="D534" s="3"/>
-      <c r="E534" s="4"/>
-      <c r="F534" s="3"/>
+      <c r="E534" s="3"/>
       <c r="G534" s="3"/>
     </row>
     <row r="535" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A535" s="3"/>
       <c r="B535" s="3"/>
-      <c r="C535" s="3"/>
-      <c r="D535" s="3"/>
-      <c r="E535" s="4"/>
-      <c r="F535" s="3"/>
       <c r="G535" s="3"/>
     </row>
     <row r="536" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A536" s="3"/>
-      <c r="B536" s="3"/>
-      <c r="C536" s="3"/>
-      <c r="D536" s="3"/>
-      <c r="E536" s="4"/>
-      <c r="F536" s="3"/>
       <c r="G536" s="3"/>
     </row>
     <row r="537" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A537" s="3"/>
-      <c r="B537" s="3"/>
-      <c r="C537" s="3"/>
-      <c r="D537" s="3"/>
-      <c r="E537" s="4"/>
-      <c r="F537" s="3"/>
-      <c r="G537" s="3"/>
     </row>
     <row r="538" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A538" s="3"/>
-      <c r="B538" s="3"/>
-      <c r="C538" s="3"/>
-      <c r="D538" s="3"/>
-      <c r="E538" s="4"/>
-      <c r="F538" s="3"/>
-      <c r="G538" s="3"/>
     </row>
     <row r="539" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A539" s="3"/>
-      <c r="B539" s="3"/>
-      <c r="C539" s="3"/>
-      <c r="D539" s="3"/>
-      <c r="E539" s="4"/>
-      <c r="F539" s="3"/>
-      <c r="G539" s="3"/>
-    </row>
-    <row r="540" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A540" s="3"/>
-      <c r="B540" s="3"/>
-      <c r="C540" s="3"/>
-      <c r="D540" s="3"/>
-      <c r="E540" s="4"/>
-      <c r="F540" s="3"/>
-      <c r="G540" s="3"/>
-    </row>
-    <row r="541" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A541" s="3"/>
-      <c r="B541" s="3"/>
-      <c r="C541" s="3"/>
-      <c r="D541" s="3"/>
-      <c r="E541" s="4"/>
-      <c r="F541" s="3"/>
-      <c r="G541" s="3"/>
-    </row>
-    <row r="542" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A542" s="3"/>
-      <c r="B542" s="3"/>
-      <c r="C542" s="3"/>
-      <c r="D542" s="3"/>
-      <c r="E542" s="4"/>
-      <c r="F542" s="3"/>
-      <c r="G542" s="3"/>
-    </row>
-    <row r="543" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A543" s="3"/>
-      <c r="B543" s="3"/>
-      <c r="C543" s="3"/>
-      <c r="D543" s="3"/>
-      <c r="E543" s="4"/>
-      <c r="F543" s="3"/>
-      <c r="G543" s="3"/>
-    </row>
-    <row r="544" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A544" s="3"/>
-      <c r="B544" s="3"/>
-      <c r="C544" s="3"/>
-      <c r="D544" s="3"/>
-      <c r="E544" s="4"/>
-      <c r="F544" s="3"/>
-      <c r="G544" s="3"/>
-    </row>
-    <row r="545" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A545" s="3"/>
-      <c r="B545" s="3"/>
-      <c r="C545" s="3"/>
-      <c r="D545" s="3"/>
-      <c r="E545" s="4"/>
-      <c r="F545" s="3"/>
-      <c r="G545" s="3"/>
-    </row>
-    <row r="546" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A546" s="3"/>
-      <c r="B546" s="3"/>
-      <c r="C546" s="3"/>
-      <c r="D546" s="3"/>
-      <c r="E546" s="4"/>
-      <c r="F546" s="3"/>
-      <c r="G546" s="3"/>
-    </row>
-    <row r="547" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A547" s="3"/>
-      <c r="B547" s="3"/>
-      <c r="C547" s="3"/>
-      <c r="D547" s="3"/>
-      <c r="E547" s="4"/>
-      <c r="F547" s="3"/>
-      <c r="G547" s="3"/>
-    </row>
-    <row r="548" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A548" s="3"/>
-      <c r="B548" s="3"/>
-      <c r="C548" s="3"/>
-      <c r="D548" s="3"/>
-      <c r="E548" s="4"/>
-      <c r="F548" s="3"/>
-      <c r="G548" s="3"/>
-    </row>
-    <row r="549" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A549" s="3"/>
-      <c r="B549" s="3"/>
-      <c r="C549" s="3"/>
-      <c r="D549" s="3"/>
-      <c r="E549" s="4"/>
-      <c r="F549" s="3"/>
-      <c r="G549" s="3"/>
-    </row>
-    <row r="550" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A550" s="3"/>
-      <c r="B550" s="3"/>
-      <c r="C550" s="3"/>
-      <c r="D550" s="3"/>
-      <c r="E550" s="4"/>
-      <c r="F550" s="3"/>
-      <c r="G550" s="3"/>
-    </row>
-    <row r="551" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A551" s="3"/>
-      <c r="B551" s="3"/>
-      <c r="C551" s="3"/>
-      <c r="D551" s="3"/>
-      <c r="E551" s="4"/>
-      <c r="F551" s="3"/>
-      <c r="G551" s="3"/>
-    </row>
-    <row r="552" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A552" s="3"/>
-      <c r="B552" s="3"/>
-      <c r="C552" s="3"/>
-      <c r="D552" s="3"/>
-      <c r="E552" s="4"/>
-      <c r="F552" s="3"/>
-      <c r="G552" s="3"/>
-    </row>
-    <row r="553" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A553" s="3"/>
-      <c r="B553" s="3"/>
-      <c r="C553" s="3"/>
-      <c r="D553" s="3"/>
-      <c r="E553" s="4"/>
-      <c r="F553" s="3"/>
-      <c r="G553" s="3"/>
-    </row>
-    <row r="554" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A554" s="3"/>
-      <c r="B554" s="3"/>
-      <c r="C554" s="3"/>
-      <c r="D554" s="3"/>
-      <c r="E554" s="4"/>
-      <c r="F554" s="3"/>
-      <c r="G554" s="3"/>
-    </row>
-    <row r="555" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A555" s="3"/>
-      <c r="B555" s="3"/>
-      <c r="C555" s="3"/>
-      <c r="D555" s="3"/>
-      <c r="E555" s="4"/>
-      <c r="F555" s="3"/>
-      <c r="G555" s="3"/>
-    </row>
-    <row r="556" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A556" s="3"/>
-      <c r="B556" s="3"/>
-      <c r="C556" s="3"/>
-      <c r="D556" s="3"/>
-      <c r="E556" s="4"/>
-      <c r="F556" s="3"/>
-      <c r="G556" s="3"/>
-    </row>
-    <row r="557" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A557" s="3"/>
-      <c r="B557" s="3"/>
-      <c r="C557" s="3"/>
-      <c r="D557" s="3"/>
-      <c r="E557" s="4"/>
-      <c r="F557" s="3"/>
-      <c r="G557" s="3"/>
-    </row>
-    <row r="558" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A558" s="3"/>
-      <c r="B558" s="3"/>
-      <c r="C558" s="3"/>
-      <c r="D558" s="3"/>
-      <c r="E558" s="4"/>
-      <c r="F558" s="3"/>
-      <c r="G558" s="3"/>
-    </row>
-    <row r="559" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A559" s="3"/>
-      <c r="B559" s="3"/>
-      <c r="C559" s="3"/>
-      <c r="D559" s="3"/>
-      <c r="E559" s="4"/>
-      <c r="F559" s="3"/>
-      <c r="G559" s="3"/>
-    </row>
-    <row r="560" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A560" s="3"/>
-      <c r="B560" s="3"/>
-      <c r="C560" s="3"/>
-      <c r="D560" s="3"/>
-      <c r="E560" s="4"/>
-      <c r="F560" s="3"/>
-      <c r="G560" s="3"/>
-    </row>
-    <row r="561" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A561" s="3"/>
-      <c r="B561" s="3"/>
-      <c r="C561" s="3"/>
-      <c r="D561" s="3"/>
-      <c r="E561" s="4"/>
-      <c r="F561" s="3"/>
-      <c r="G561" s="3"/>
-    </row>
-    <row r="562" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A562" s="3"/>
-      <c r="B562" s="3"/>
-      <c r="C562" s="3"/>
-      <c r="D562" s="3"/>
-      <c r="E562" s="4"/>
-      <c r="F562" s="3"/>
-      <c r="G562" s="3"/>
-    </row>
-    <row r="563" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="B563" s="3"/>
-      <c r="C563" s="3"/>
-      <c r="D563" s="3"/>
-      <c r="E563" s="4"/>
-      <c r="F563" s="3"/>
-      <c r="G563" s="3"/>
-    </row>
-    <row r="564" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="B564" s="3"/>
-      <c r="C564" s="3"/>
-      <c r="D564" s="3"/>
-      <c r="E564" s="4"/>
-      <c r="F564" s="3"/>
-      <c r="G564" s="3"/>
-    </row>
-    <row r="565" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="B565" s="3"/>
-      <c r="C565" s="3"/>
-      <c r="D565" s="3"/>
-      <c r="E565" s="4"/>
-      <c r="F565" s="3"/>
-      <c r="G565" s="3"/>
-    </row>
-    <row r="566" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="B566" s="3"/>
-      <c r="C566" s="3"/>
-      <c r="D566" s="3"/>
-      <c r="E566" s="4"/>
-      <c r="F566" s="3"/>
-      <c r="G566" s="3"/>
-    </row>
-    <row r="567" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="B567" s="3"/>
-      <c r="C567" s="3"/>
-      <c r="D567" s="3"/>
-      <c r="E567" s="4"/>
-      <c r="F567" s="3"/>
-      <c r="G567" s="3"/>
-    </row>
-    <row r="568" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="B568" s="3"/>
-      <c r="C568" s="3"/>
-      <c r="D568" s="3"/>
-      <c r="E568" s="4"/>
-      <c r="F568" s="3"/>
-      <c r="G568" s="3"/>
-    </row>
-    <row r="569" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="B569" s="3"/>
-      <c r="C569" s="3"/>
-      <c r="D569" s="3"/>
-      <c r="E569" s="4"/>
-      <c r="F569" s="3"/>
-      <c r="G569" s="3"/>
-    </row>
-    <row r="570" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="B570" s="3"/>
-      <c r="C570" s="3"/>
-      <c r="D570" s="3"/>
-      <c r="E570" s="4"/>
-      <c r="F570" s="3"/>
-      <c r="G570" s="3"/>
-    </row>
-    <row r="571" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="B571" s="3"/>
-      <c r="C571" s="3"/>
-      <c r="D571" s="3"/>
-      <c r="E571" s="4"/>
-      <c r="F571" s="3"/>
-      <c r="G571" s="3"/>
-    </row>
-    <row r="572" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="B572" s="3"/>
-      <c r="C572" s="3"/>
-      <c r="D572" s="3"/>
-      <c r="E572" s="4"/>
-      <c r="F572" s="3"/>
-      <c r="G572" s="3"/>
-    </row>
-    <row r="573" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="B573" s="3"/>
-      <c r="C573" s="3"/>
-      <c r="D573" s="3"/>
-      <c r="E573" s="4"/>
-      <c r="F573" s="3"/>
-      <c r="G573" s="3"/>
-    </row>
-    <row r="574" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="B574" s="3"/>
-      <c r="C574" s="3"/>
-      <c r="D574" s="3"/>
-      <c r="E574" s="4"/>
-      <c r="F574" s="3"/>
-      <c r="G574" s="3"/>
-    </row>
-    <row r="575" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="B575" s="3"/>
-      <c r="C575" s="3"/>
-      <c r="D575" s="3"/>
-      <c r="E575" s="3"/>
-      <c r="F575" s="3"/>
-      <c r="G575" s="3"/>
-    </row>
-    <row r="576" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="B576" s="3"/>
-      <c r="C576" s="3"/>
-      <c r="D576" s="3"/>
-      <c r="E576" s="3"/>
-      <c r="G576" s="3"/>
-    </row>
-    <row r="577" spans="2:7" x14ac:dyDescent="0.2">
-      <c r="B577" s="3"/>
-      <c r="G577" s="3"/>
     </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>

--- a/rtl/pbit_register_file.xlsx
+++ b/rtl/pbit_register_file.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Study_material\Study_material\Pbit\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Study_material\Study_material\Pbit\pbit_kings\pbit_kings\rtl\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{679E1739-D625-489E-922D-5BC0C79F4BE0}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{388BEF30-27AD-4423-A56C-9533B99C327C}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="15360" windowHeight="12645" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1058" uniqueCount="479">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1055" uniqueCount="478">
   <si>
     <t>LEVEL</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -394,11 +394,6 @@
   <si>
     <t>INIT_VALID
 INIT_SPIN字段有效</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>SEED_VALID
-SEED字段有效</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
@@ -2115,7 +2110,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -2123,20 +2118,11 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border diagonalDown="1">
-      <left/>
-      <right/>
-      <top/>
-      <bottom/>
-      <diagonal style="thin">
-        <color auto="1"/>
-      </diagonal>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="28">
+  <cellXfs count="25">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -2204,15 +2190,6 @@
     </xf>
     <xf numFmtId="0" fontId="5" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="0" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="49" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -2497,7 +2474,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:G577"/>
+  <dimension ref="A1:G575"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="12.625" customWidth="1"/>
@@ -2585,7 +2562,7 @@
         <v>2</v>
       </c>
       <c r="F5" s="2" t="s">
-        <v>438</v>
+        <v>437</v>
       </c>
     </row>
     <row r="6" spans="1:7" ht="28.5" x14ac:dyDescent="0.2">
@@ -2662,22 +2639,22 @@
     <row r="11" spans="1:7" ht="28.5" x14ac:dyDescent="0.2">
       <c r="A11" s="6"/>
       <c r="B11" s="14" t="s">
+        <v>160</v>
+      </c>
+      <c r="C11" s="14" t="s">
         <v>161</v>
       </c>
-      <c r="C11" s="14" t="s">
+      <c r="D11" s="14" t="s">
         <v>162</v>
       </c>
-      <c r="D11" s="14" t="s">
-        <v>163</v>
-      </c>
       <c r="E11" s="15" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="F11" s="16" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="G11" s="22" t="s">
-        <v>475</v>
+        <v>474</v>
       </c>
     </row>
     <row r="12" spans="1:7" ht="28.5" x14ac:dyDescent="0.2">
@@ -2686,13 +2663,13 @@
       <c r="C12" s="14"/>
       <c r="D12" s="14"/>
       <c r="E12" s="15" t="s">
-        <v>473</v>
+        <v>472</v>
       </c>
       <c r="F12" s="16" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="G12" s="23" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.2">
@@ -2701,7 +2678,7 @@
       <c r="C13" s="10"/>
       <c r="D13" s="10"/>
       <c r="E13" s="11" t="s">
-        <v>474</v>
+        <v>473</v>
       </c>
       <c r="F13" s="12" t="s">
         <v>32</v>
@@ -2768,13 +2745,13 @@
       <c r="B17" s="6"/>
       <c r="C17" s="6"/>
       <c r="D17" s="14" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="E17" s="15" t="s">
         <v>15</v>
       </c>
       <c r="F17" s="20" t="s">
-        <v>471</v>
+        <v>470</v>
       </c>
       <c r="G17" s="9"/>
     </row>
@@ -2783,13 +2760,13 @@
       <c r="B18" s="6"/>
       <c r="C18" s="6"/>
       <c r="D18" s="14" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="E18" s="15" t="s">
         <v>18</v>
       </c>
       <c r="F18" s="20" t="s">
-        <v>472</v>
+        <v>471</v>
       </c>
       <c r="G18" s="9"/>
     </row>
@@ -2798,7 +2775,7 @@
       <c r="B19" s="6"/>
       <c r="C19" s="6"/>
       <c r="D19" s="14" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="E19" s="15" t="s">
         <v>20</v>
@@ -2907,7 +2884,7 @@
         <v>59</v>
       </c>
       <c r="G25" s="10" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
     </row>
     <row r="26" spans="1:7" ht="28.5" x14ac:dyDescent="0.2">
@@ -2924,7 +2901,7 @@
         <v>60</v>
       </c>
       <c r="G26" s="10" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
     </row>
     <row r="27" spans="1:7" ht="28.5" x14ac:dyDescent="0.2">
@@ -2941,7 +2918,7 @@
         <v>61</v>
       </c>
       <c r="G27" s="10" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
     </row>
     <row r="28" spans="1:7" ht="28.5" x14ac:dyDescent="0.2">
@@ -2958,7 +2935,7 @@
         <v>62</v>
       </c>
       <c r="G28" s="13" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
     </row>
     <row r="29" spans="1:7" ht="28.5" x14ac:dyDescent="0.2">
@@ -2975,7 +2952,7 @@
         <v>63</v>
       </c>
       <c r="G29" s="13" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
     </row>
     <row r="30" spans="1:7" ht="28.5" x14ac:dyDescent="0.2">
@@ -2992,7 +2969,7 @@
         <v>64</v>
       </c>
       <c r="G30" s="13" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
     </row>
     <row r="31" spans="1:7" ht="28.5" x14ac:dyDescent="0.2">
@@ -3009,7 +2986,7 @@
         <v>65</v>
       </c>
       <c r="G31" s="13" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
     </row>
     <row r="32" spans="1:7" ht="42.75" x14ac:dyDescent="0.2">
@@ -3017,16 +2994,16 @@
       <c r="B32" s="10"/>
       <c r="C32" s="10"/>
       <c r="D32" s="10" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="E32" s="7" t="s">
         <v>53</v>
       </c>
       <c r="F32" s="8" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="G32" s="13" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
     </row>
     <row r="33" spans="1:7" ht="42.75" x14ac:dyDescent="0.2">
@@ -3043,7 +3020,7 @@
         <v>66</v>
       </c>
       <c r="G33" s="13" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
     </row>
     <row r="34" spans="1:7" ht="42.75" x14ac:dyDescent="0.2">
@@ -3060,7 +3037,7 @@
         <v>67</v>
       </c>
       <c r="G34" s="13" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
     </row>
     <row r="35" spans="1:7" ht="42.75" x14ac:dyDescent="0.2">
@@ -3068,16 +3045,16 @@
       <c r="B35" s="10"/>
       <c r="C35" s="10"/>
       <c r="D35" s="10" t="s">
+        <v>448</v>
+      </c>
+      <c r="E35" s="7" t="s">
         <v>449</v>
       </c>
-      <c r="E35" s="7" t="s">
-        <v>450</v>
-      </c>
       <c r="F35" s="19" t="s">
-        <v>452</v>
+        <v>451</v>
       </c>
       <c r="G35" s="13" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
     </row>
     <row r="36" spans="1:7" ht="42.75" x14ac:dyDescent="0.2">
@@ -3085,16 +3062,16 @@
       <c r="B36" s="10"/>
       <c r="C36" s="10"/>
       <c r="D36" s="10" t="s">
-        <v>449</v>
+        <v>448</v>
       </c>
       <c r="E36" s="7" t="s">
-        <v>451</v>
+        <v>450</v>
       </c>
       <c r="F36" s="19" t="s">
-        <v>453</v>
+        <v>452</v>
       </c>
       <c r="G36" s="13" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
     </row>
     <row r="37" spans="1:7" ht="42.75" x14ac:dyDescent="0.2">
@@ -3111,7 +3088,7 @@
         <v>68</v>
       </c>
       <c r="G37" s="13" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
     </row>
     <row r="38" spans="1:7" ht="42.75" x14ac:dyDescent="0.2">
@@ -3128,7 +3105,7 @@
         <v>69</v>
       </c>
       <c r="G38" s="13" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
     </row>
     <row r="39" spans="1:7" ht="42.75" x14ac:dyDescent="0.2">
@@ -3139,13 +3116,13 @@
         <v>58</v>
       </c>
       <c r="E39" s="7" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="F39" s="8" t="s">
         <v>70</v>
       </c>
       <c r="G39" s="13" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
     </row>
     <row r="40" spans="1:7" ht="28.5" x14ac:dyDescent="0.2">
@@ -3156,7 +3133,7 @@
         <v>58</v>
       </c>
       <c r="E40" s="7" t="s">
-        <v>454</v>
+        <v>453</v>
       </c>
       <c r="F40" s="8" t="s">
         <v>71</v>
@@ -3171,7 +3148,7 @@
         <v>58</v>
       </c>
       <c r="E41" s="7" t="s">
-        <v>455</v>
+        <v>454</v>
       </c>
       <c r="F41" s="8" t="s">
         <v>72</v>
@@ -3183,16 +3160,16 @@
       <c r="B42" s="10"/>
       <c r="C42" s="10"/>
       <c r="D42" s="10" t="s">
+        <v>166</v>
+      </c>
+      <c r="E42" s="7" t="s">
+        <v>455</v>
+      </c>
+      <c r="F42" s="8" t="s">
         <v>167</v>
       </c>
-      <c r="E42" s="7" t="s">
-        <v>456</v>
-      </c>
-      <c r="F42" s="8" t="s">
-        <v>168</v>
-      </c>
       <c r="G42" s="10" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
     </row>
     <row r="43" spans="1:7" x14ac:dyDescent="0.2">
@@ -3201,7 +3178,7 @@
       <c r="C43" s="10"/>
       <c r="D43" s="10"/>
       <c r="E43" s="7" t="s">
-        <v>457</v>
+        <v>456</v>
       </c>
       <c r="F43" s="17" t="s">
         <v>32</v>
@@ -3211,22 +3188,22 @@
     <row r="44" spans="1:7" ht="28.5" x14ac:dyDescent="0.2">
       <c r="A44" s="3"/>
       <c r="B44" s="3" t="s">
+        <v>171</v>
+      </c>
+      <c r="C44" s="3" t="s">
+        <v>174</v>
+      </c>
+      <c r="D44" s="3" t="s">
         <v>172</v>
       </c>
-      <c r="C44" s="3" t="s">
-        <v>175</v>
-      </c>
-      <c r="D44" s="3" t="s">
+      <c r="E44" s="4" t="s">
         <v>173</v>
       </c>
-      <c r="E44" s="4" t="s">
-        <v>174</v>
-      </c>
       <c r="F44" s="2" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="G44" s="3" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
     </row>
     <row r="45" spans="1:7" x14ac:dyDescent="0.2">
@@ -3235,7 +3212,7 @@
       <c r="C45" s="3"/>
       <c r="D45" s="3"/>
       <c r="E45" s="4" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="F45" s="2" t="s">
         <v>42</v>
@@ -3245,19 +3222,19 @@
     <row r="46" spans="1:7" ht="28.5" x14ac:dyDescent="0.2">
       <c r="A46" s="3"/>
       <c r="B46" s="3" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="C46" s="3" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="D46" s="3" t="s">
+        <v>192</v>
+      </c>
+      <c r="E46" s="4" t="s">
         <v>193</v>
       </c>
-      <c r="E46" s="4" t="s">
-        <v>194</v>
-      </c>
       <c r="F46" s="2" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="G46" s="3"/>
     </row>
@@ -3266,10 +3243,10 @@
       <c r="B47" s="3"/>
       <c r="C47" s="3"/>
       <c r="D47" s="3" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="E47" s="4" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="F47" s="2" t="s">
         <v>42</v>
@@ -3281,13 +3258,13 @@
       <c r="B48" s="3"/>
       <c r="C48" s="3"/>
       <c r="D48" s="3" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="E48" s="4" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="F48" s="2" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="G48" s="3"/>
     </row>
@@ -3296,10 +3273,10 @@
       <c r="B49" s="3"/>
       <c r="C49" s="3"/>
       <c r="D49" s="3" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="E49" s="4" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="F49" s="2" t="s">
         <v>42</v>
@@ -3311,13 +3288,13 @@
       <c r="B50" s="3"/>
       <c r="C50" s="3"/>
       <c r="D50" s="3" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="E50" s="4" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="F50" s="2" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="G50" s="3"/>
     </row>
@@ -3326,10 +3303,10 @@
       <c r="B51" s="3"/>
       <c r="C51" s="3"/>
       <c r="D51" s="3" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="E51" s="4" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="F51" s="2" t="s">
         <v>42</v>
@@ -3341,13 +3318,13 @@
       <c r="B52" s="3"/>
       <c r="C52" s="3"/>
       <c r="D52" s="3" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="E52" s="4" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="F52" s="2" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="G52" s="3"/>
     </row>
@@ -3356,10 +3333,10 @@
       <c r="B53" s="3"/>
       <c r="C53" s="3"/>
       <c r="D53" s="3" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="E53" s="4" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="F53" s="1" t="s">
         <v>42</v>
@@ -3369,19 +3346,19 @@
     <row r="54" spans="1:7" ht="28.5" x14ac:dyDescent="0.2">
       <c r="A54" s="3"/>
       <c r="B54" s="3" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="C54" s="3" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="D54" s="3" t="s">
+        <v>192</v>
+      </c>
+      <c r="E54" s="4" t="s">
         <v>193</v>
       </c>
-      <c r="E54" s="4" t="s">
-        <v>194</v>
-      </c>
       <c r="F54" s="2" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="G54" s="3"/>
     </row>
@@ -3390,10 +3367,10 @@
       <c r="B55" s="3"/>
       <c r="C55" s="3"/>
       <c r="D55" s="3" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="E55" s="4" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="F55" s="2" t="s">
         <v>42</v>
@@ -3405,13 +3382,13 @@
       <c r="B56" s="3"/>
       <c r="C56" s="3"/>
       <c r="D56" s="3" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="E56" s="4" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="F56" s="2" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="G56" s="3"/>
     </row>
@@ -3420,10 +3397,10 @@
       <c r="B57" s="3"/>
       <c r="C57" s="3"/>
       <c r="D57" s="3" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="E57" s="4" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="F57" s="2" t="s">
         <v>42</v>
@@ -3435,13 +3412,13 @@
       <c r="B58" s="3"/>
       <c r="C58" s="3"/>
       <c r="D58" s="3" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="E58" s="4" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="F58" s="2" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="G58" s="3"/>
     </row>
@@ -3450,10 +3427,10 @@
       <c r="B59" s="3"/>
       <c r="C59" s="3"/>
       <c r="D59" s="3" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="E59" s="4" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="F59" s="2" t="s">
         <v>42</v>
@@ -3465,13 +3442,13 @@
       <c r="B60" s="3"/>
       <c r="C60" s="3"/>
       <c r="D60" s="3" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="E60" s="4" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="F60" s="2" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="G60" s="3"/>
     </row>
@@ -3480,10 +3457,10 @@
       <c r="B61" s="3"/>
       <c r="C61" s="3"/>
       <c r="D61" s="3" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="E61" s="4" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="F61" s="1" t="s">
         <v>42</v>
@@ -3493,19 +3470,19 @@
     <row r="62" spans="1:7" ht="28.5" x14ac:dyDescent="0.2">
       <c r="A62" s="3"/>
       <c r="B62" s="3" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="C62" s="3" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="D62" s="3" t="s">
+        <v>192</v>
+      </c>
+      <c r="E62" s="4" t="s">
         <v>193</v>
       </c>
-      <c r="E62" s="4" t="s">
-        <v>194</v>
-      </c>
       <c r="F62" s="2" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="G62" s="3"/>
     </row>
@@ -3514,10 +3491,10 @@
       <c r="B63" s="3"/>
       <c r="C63" s="3"/>
       <c r="D63" s="3" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="E63" s="4" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="F63" s="2" t="s">
         <v>42</v>
@@ -3529,13 +3506,13 @@
       <c r="B64" s="3"/>
       <c r="C64" s="3"/>
       <c r="D64" s="3" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="E64" s="4" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="F64" s="2" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="G64" s="3"/>
     </row>
@@ -3544,10 +3521,10 @@
       <c r="B65" s="3"/>
       <c r="C65" s="3"/>
       <c r="D65" s="3" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="E65" s="4" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="F65" s="2" t="s">
         <v>42</v>
@@ -3559,13 +3536,13 @@
       <c r="B66" s="3"/>
       <c r="C66" s="3"/>
       <c r="D66" s="3" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="E66" s="4" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="F66" s="2" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="G66" s="3"/>
     </row>
@@ -3574,10 +3551,10 @@
       <c r="B67" s="3"/>
       <c r="C67" s="3"/>
       <c r="D67" s="3" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="E67" s="4" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="F67" s="2" t="s">
         <v>42</v>
@@ -3589,13 +3566,13 @@
       <c r="B68" s="3"/>
       <c r="C68" s="3"/>
       <c r="D68" s="3" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="E68" s="4" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="F68" s="2" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="G68" s="3"/>
     </row>
@@ -3604,10 +3581,10 @@
       <c r="B69" s="3"/>
       <c r="C69" s="3"/>
       <c r="D69" s="3" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="E69" s="4" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="F69" s="1" t="s">
         <v>42</v>
@@ -3617,19 +3594,19 @@
     <row r="70" spans="1:7" ht="28.5" x14ac:dyDescent="0.2">
       <c r="A70" s="3"/>
       <c r="B70" s="3" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="C70" s="3" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="D70" s="3" t="s">
+        <v>192</v>
+      </c>
+      <c r="E70" s="4" t="s">
         <v>193</v>
       </c>
-      <c r="E70" s="4" t="s">
-        <v>194</v>
-      </c>
       <c r="F70" s="2" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="G70" s="3"/>
     </row>
@@ -3638,10 +3615,10 @@
       <c r="B71" s="3"/>
       <c r="C71" s="3"/>
       <c r="D71" s="3" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="E71" s="4" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="F71" s="2" t="s">
         <v>42</v>
@@ -3653,13 +3630,13 @@
       <c r="B72" s="3"/>
       <c r="C72" s="3"/>
       <c r="D72" s="3" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="E72" s="4" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="F72" s="2" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="G72" s="3"/>
     </row>
@@ -3668,10 +3645,10 @@
       <c r="B73" s="3"/>
       <c r="C73" s="3"/>
       <c r="D73" s="3" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="E73" s="4" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="F73" s="2" t="s">
         <v>42</v>
@@ -3683,13 +3660,13 @@
       <c r="B74" s="3"/>
       <c r="C74" s="3"/>
       <c r="D74" s="3" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="E74" s="4" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="F74" s="2" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="G74" s="3"/>
     </row>
@@ -3698,10 +3675,10 @@
       <c r="B75" s="3"/>
       <c r="C75" s="3"/>
       <c r="D75" s="3" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="E75" s="4" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="F75" s="2" t="s">
         <v>42</v>
@@ -3713,13 +3690,13 @@
       <c r="B76" s="3"/>
       <c r="C76" s="3"/>
       <c r="D76" s="3" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="E76" s="4" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="F76" s="2" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="G76" s="3"/>
     </row>
@@ -3728,10 +3705,10 @@
       <c r="B77" s="3"/>
       <c r="C77" s="3"/>
       <c r="D77" s="3" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="E77" s="4" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="F77" s="1" t="s">
         <v>42</v>
@@ -3741,19 +3718,19 @@
     <row r="78" spans="1:7" ht="28.5" x14ac:dyDescent="0.2">
       <c r="A78" s="3"/>
       <c r="B78" s="3" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="C78" s="3" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="D78" s="3" t="s">
+        <v>192</v>
+      </c>
+      <c r="E78" s="4" t="s">
         <v>193</v>
       </c>
-      <c r="E78" s="4" t="s">
-        <v>194</v>
-      </c>
       <c r="F78" s="2" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="G78" s="3"/>
     </row>
@@ -3762,10 +3739,10 @@
       <c r="B79" s="3"/>
       <c r="C79" s="3"/>
       <c r="D79" s="3" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="E79" s="4" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="F79" s="2" t="s">
         <v>42</v>
@@ -3777,13 +3754,13 @@
       <c r="B80" s="3"/>
       <c r="C80" s="3"/>
       <c r="D80" s="3" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="E80" s="4" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="F80" s="2" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="G80" s="3"/>
     </row>
@@ -3792,10 +3769,10 @@
       <c r="B81" s="3"/>
       <c r="C81" s="3"/>
       <c r="D81" s="3" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="E81" s="4" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="F81" s="2" t="s">
         <v>42</v>
@@ -3807,13 +3784,13 @@
       <c r="B82" s="3"/>
       <c r="C82" s="3"/>
       <c r="D82" s="3" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="E82" s="4" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="F82" s="2" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="G82" s="3"/>
     </row>
@@ -3822,10 +3799,10 @@
       <c r="B83" s="3"/>
       <c r="C83" s="3"/>
       <c r="D83" s="3" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="E83" s="4" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="F83" s="2" t="s">
         <v>42</v>
@@ -3837,13 +3814,13 @@
       <c r="B84" s="3"/>
       <c r="C84" s="3"/>
       <c r="D84" s="3" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="E84" s="4" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="F84" s="2" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="G84" s="3"/>
     </row>
@@ -3852,10 +3829,10 @@
       <c r="B85" s="3"/>
       <c r="C85" s="3"/>
       <c r="D85" s="3" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="E85" s="4" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="F85" s="1" t="s">
         <v>42</v>
@@ -3865,19 +3842,19 @@
     <row r="86" spans="1:7" ht="28.5" x14ac:dyDescent="0.2">
       <c r="A86" s="3"/>
       <c r="B86" s="3" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="C86" s="3" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="D86" s="3" t="s">
+        <v>192</v>
+      </c>
+      <c r="E86" s="4" t="s">
         <v>193</v>
       </c>
-      <c r="E86" s="4" t="s">
-        <v>194</v>
-      </c>
       <c r="F86" s="2" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="G86" s="3"/>
     </row>
@@ -3886,10 +3863,10 @@
       <c r="B87" s="3"/>
       <c r="C87" s="3"/>
       <c r="D87" s="3" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="E87" s="4" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="F87" s="2" t="s">
         <v>42</v>
@@ -3901,13 +3878,13 @@
       <c r="B88" s="3"/>
       <c r="C88" s="3"/>
       <c r="D88" s="3" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="E88" s="4" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="F88" s="2" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="G88" s="3"/>
     </row>
@@ -3916,10 +3893,10 @@
       <c r="B89" s="3"/>
       <c r="C89" s="3"/>
       <c r="D89" s="3" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="E89" s="4" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="F89" s="2" t="s">
         <v>42</v>
@@ -3931,13 +3908,13 @@
       <c r="B90" s="3"/>
       <c r="C90" s="3"/>
       <c r="D90" s="3" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="E90" s="4" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="F90" s="2" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="G90" s="3"/>
     </row>
@@ -3946,10 +3923,10 @@
       <c r="B91" s="3"/>
       <c r="C91" s="3"/>
       <c r="D91" s="3" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="E91" s="4" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="F91" s="2" t="s">
         <v>42</v>
@@ -3961,13 +3938,13 @@
       <c r="B92" s="3"/>
       <c r="C92" s="3"/>
       <c r="D92" s="3" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="E92" s="4" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="F92" s="2" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="G92" s="3"/>
     </row>
@@ -3976,10 +3953,10 @@
       <c r="B93" s="3"/>
       <c r="C93" s="3"/>
       <c r="D93" s="3" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="E93" s="4" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="F93" s="1" t="s">
         <v>42</v>
@@ -3989,19 +3966,19 @@
     <row r="94" spans="1:7" ht="28.5" x14ac:dyDescent="0.2">
       <c r="A94" s="3"/>
       <c r="B94" s="3" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="C94" s="3" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="D94" s="3" t="s">
+        <v>192</v>
+      </c>
+      <c r="E94" s="4" t="s">
         <v>193</v>
       </c>
-      <c r="E94" s="4" t="s">
-        <v>194</v>
-      </c>
       <c r="F94" s="2" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="G94" s="3"/>
     </row>
@@ -4010,10 +3987,10 @@
       <c r="B95" s="3"/>
       <c r="C95" s="3"/>
       <c r="D95" s="3" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="E95" s="4" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="F95" s="2" t="s">
         <v>42</v>
@@ -4025,13 +4002,13 @@
       <c r="B96" s="3"/>
       <c r="C96" s="3"/>
       <c r="D96" s="3" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="E96" s="4" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="F96" s="2" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="G96" s="3"/>
     </row>
@@ -4040,10 +4017,10 @@
       <c r="B97" s="3"/>
       <c r="C97" s="3"/>
       <c r="D97" s="3" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="E97" s="4" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="F97" s="2" t="s">
         <v>42</v>
@@ -4055,13 +4032,13 @@
       <c r="B98" s="3"/>
       <c r="C98" s="3"/>
       <c r="D98" s="3" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="E98" s="4" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="F98" s="2" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="G98" s="3"/>
     </row>
@@ -4070,10 +4047,10 @@
       <c r="B99" s="3"/>
       <c r="C99" s="3"/>
       <c r="D99" s="3" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="E99" s="4" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="F99" s="2" t="s">
         <v>42</v>
@@ -4085,13 +4062,13 @@
       <c r="B100" s="3"/>
       <c r="C100" s="3"/>
       <c r="D100" s="3" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="E100" s="4" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="F100" s="2" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="G100" s="3"/>
     </row>
@@ -4100,10 +4077,10 @@
       <c r="B101" s="3"/>
       <c r="C101" s="3"/>
       <c r="D101" s="3" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="E101" s="4" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="F101" s="2" t="s">
         <v>42</v>
@@ -4113,19 +4090,19 @@
     <row r="102" spans="1:7" ht="28.5" x14ac:dyDescent="0.2">
       <c r="A102" s="3"/>
       <c r="B102" s="3" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="C102" s="3" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="D102" s="3" t="s">
+        <v>192</v>
+      </c>
+      <c r="E102" s="4" t="s">
         <v>193</v>
       </c>
-      <c r="E102" s="4" t="s">
-        <v>194</v>
-      </c>
       <c r="F102" s="2" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="G102" s="3"/>
     </row>
@@ -4134,10 +4111,10 @@
       <c r="B103" s="3"/>
       <c r="C103" s="3"/>
       <c r="D103" s="3" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="E103" s="4" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="F103" s="1" t="s">
         <v>42</v>
@@ -4149,13 +4126,13 @@
       <c r="B104" s="3"/>
       <c r="C104" s="3"/>
       <c r="D104" s="3" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="E104" s="4" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="F104" s="2" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="G104" s="3"/>
     </row>
@@ -4164,10 +4141,10 @@
       <c r="B105" s="3"/>
       <c r="C105" s="3"/>
       <c r="D105" s="3" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="E105" s="4" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="F105" s="2" t="s">
         <v>42</v>
@@ -4179,13 +4156,13 @@
       <c r="B106" s="3"/>
       <c r="C106" s="3"/>
       <c r="D106" s="3" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="E106" s="4" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="F106" s="2" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="G106" s="3"/>
     </row>
@@ -4194,10 +4171,10 @@
       <c r="B107" s="3"/>
       <c r="C107" s="3"/>
       <c r="D107" s="3" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="E107" s="4" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="F107" s="2" t="s">
         <v>42</v>
@@ -4209,13 +4186,13 @@
       <c r="B108" s="3"/>
       <c r="C108" s="3"/>
       <c r="D108" s="3" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="E108" s="4" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="F108" s="2" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="G108" s="3"/>
     </row>
@@ -4224,10 +4201,10 @@
       <c r="B109" s="3"/>
       <c r="C109" s="3"/>
       <c r="D109" s="3" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="E109" s="4" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="F109" s="2" t="s">
         <v>42</v>
@@ -4237,19 +4214,19 @@
     <row r="110" spans="1:7" ht="28.5" x14ac:dyDescent="0.2">
       <c r="A110" s="3"/>
       <c r="B110" s="3" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="C110" s="3" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="D110" s="3" t="s">
+        <v>192</v>
+      </c>
+      <c r="E110" s="4" t="s">
         <v>193</v>
       </c>
-      <c r="E110" s="4" t="s">
-        <v>194</v>
-      </c>
       <c r="F110" s="2" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="G110" s="3"/>
     </row>
@@ -4258,10 +4235,10 @@
       <c r="B111" s="3"/>
       <c r="C111" s="3"/>
       <c r="D111" s="3" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="E111" s="4" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="F111" s="1" t="s">
         <v>42</v>
@@ -4273,13 +4250,13 @@
       <c r="B112" s="3"/>
       <c r="C112" s="3"/>
       <c r="D112" s="3" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="E112" s="4" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="F112" s="2" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="G112" s="3"/>
     </row>
@@ -4288,10 +4265,10 @@
       <c r="B113" s="3"/>
       <c r="C113" s="3"/>
       <c r="D113" s="3" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="E113" s="4" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="F113" s="2" t="s">
         <v>42</v>
@@ -4303,13 +4280,13 @@
       <c r="B114" s="3"/>
       <c r="C114" s="3"/>
       <c r="D114" s="3" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="E114" s="4" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="F114" s="2" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="G114" s="3"/>
     </row>
@@ -4318,10 +4295,10 @@
       <c r="B115" s="3"/>
       <c r="C115" s="3"/>
       <c r="D115" s="3" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="E115" s="4" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="F115" s="2" t="s">
         <v>42</v>
@@ -4333,13 +4310,13 @@
       <c r="B116" s="3"/>
       <c r="C116" s="3"/>
       <c r="D116" s="3" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="E116" s="4" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="F116" s="2" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="G116" s="3"/>
     </row>
@@ -4348,10 +4325,10 @@
       <c r="B117" s="3"/>
       <c r="C117" s="3"/>
       <c r="D117" s="3" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="E117" s="4" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="F117" s="1" t="s">
         <v>42</v>
@@ -4361,19 +4338,19 @@
     <row r="118" spans="1:7" ht="28.5" x14ac:dyDescent="0.2">
       <c r="A118" s="3"/>
       <c r="B118" s="3" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="C118" s="3" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="D118" s="3" t="s">
+        <v>192</v>
+      </c>
+      <c r="E118" s="4" t="s">
         <v>193</v>
       </c>
-      <c r="E118" s="4" t="s">
-        <v>194</v>
-      </c>
       <c r="F118" s="2" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="G118" s="3"/>
     </row>
@@ -4382,10 +4359,10 @@
       <c r="B119" s="3"/>
       <c r="C119" s="3"/>
       <c r="D119" s="3" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="E119" s="4" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="F119" s="2" t="s">
         <v>42</v>
@@ -4397,13 +4374,13 @@
       <c r="B120" s="3"/>
       <c r="C120" s="3"/>
       <c r="D120" s="3" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="E120" s="4" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="F120" s="2" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="G120" s="3"/>
     </row>
@@ -4412,10 +4389,10 @@
       <c r="B121" s="3"/>
       <c r="C121" s="3"/>
       <c r="D121" s="3" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="E121" s="4" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="F121" s="2" t="s">
         <v>42</v>
@@ -4427,13 +4404,13 @@
       <c r="B122" s="3"/>
       <c r="C122" s="3"/>
       <c r="D122" s="3" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="E122" s="4" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="F122" s="2" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="G122" s="3"/>
     </row>
@@ -4442,10 +4419,10 @@
       <c r="B123" s="3"/>
       <c r="C123" s="3"/>
       <c r="D123" s="3" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="E123" s="4" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="F123" s="2" t="s">
         <v>42</v>
@@ -4457,13 +4434,13 @@
       <c r="B124" s="3"/>
       <c r="C124" s="3"/>
       <c r="D124" s="3" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="E124" s="4" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="F124" s="2" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="G124" s="3"/>
     </row>
@@ -4472,10 +4449,10 @@
       <c r="B125" s="3"/>
       <c r="C125" s="3"/>
       <c r="D125" s="3" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="E125" s="4" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="F125" s="1" t="s">
         <v>42</v>
@@ -4485,19 +4462,19 @@
     <row r="126" spans="1:7" ht="28.5" x14ac:dyDescent="0.2">
       <c r="A126" s="3"/>
       <c r="B126" s="3" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="C126" s="3" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="D126" s="3" t="s">
+        <v>192</v>
+      </c>
+      <c r="E126" s="4" t="s">
         <v>193</v>
       </c>
-      <c r="E126" s="4" t="s">
-        <v>194</v>
-      </c>
       <c r="F126" s="2" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="G126" s="3"/>
     </row>
@@ -4506,10 +4483,10 @@
       <c r="B127" s="3"/>
       <c r="C127" s="3"/>
       <c r="D127" s="3" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="E127" s="4" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="F127" s="2" t="s">
         <v>42</v>
@@ -4521,13 +4498,13 @@
       <c r="B128" s="3"/>
       <c r="C128" s="3"/>
       <c r="D128" s="3" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="E128" s="4" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="F128" s="2" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="G128" s="3"/>
     </row>
@@ -4536,10 +4513,10 @@
       <c r="B129" s="3"/>
       <c r="C129" s="3"/>
       <c r="D129" s="3" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="E129" s="4" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="F129" s="2" t="s">
         <v>42</v>
@@ -4551,13 +4528,13 @@
       <c r="B130" s="3"/>
       <c r="C130" s="3"/>
       <c r="D130" s="3" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="E130" s="4" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="F130" s="2" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="G130" s="3"/>
     </row>
@@ -4566,10 +4543,10 @@
       <c r="B131" s="3"/>
       <c r="C131" s="3"/>
       <c r="D131" s="3" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="E131" s="4" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="F131" s="2" t="s">
         <v>42</v>
@@ -4581,13 +4558,13 @@
       <c r="B132" s="3"/>
       <c r="C132" s="3"/>
       <c r="D132" s="3" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="E132" s="4" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="F132" s="2" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="G132" s="3"/>
     </row>
@@ -4596,10 +4573,10 @@
       <c r="B133" s="3"/>
       <c r="C133" s="3"/>
       <c r="D133" s="3" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="E133" s="4" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="F133" s="1" t="s">
         <v>42</v>
@@ -4609,19 +4586,19 @@
     <row r="134" spans="1:7" ht="28.5" x14ac:dyDescent="0.2">
       <c r="A134" s="3"/>
       <c r="B134" s="3" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="C134" s="3" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="D134" s="3" t="s">
+        <v>192</v>
+      </c>
+      <c r="E134" s="4" t="s">
         <v>193</v>
       </c>
-      <c r="E134" s="4" t="s">
-        <v>194</v>
-      </c>
       <c r="F134" s="2" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="G134" s="3"/>
     </row>
@@ -4630,10 +4607,10 @@
       <c r="B135" s="3"/>
       <c r="C135" s="3"/>
       <c r="D135" s="3" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="E135" s="4" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="F135" s="2" t="s">
         <v>42</v>
@@ -4645,13 +4622,13 @@
       <c r="B136" s="3"/>
       <c r="C136" s="3"/>
       <c r="D136" s="3" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="E136" s="4" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="F136" s="2" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="G136" s="3"/>
     </row>
@@ -4660,10 +4637,10 @@
       <c r="B137" s="3"/>
       <c r="C137" s="3"/>
       <c r="D137" s="3" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="E137" s="4" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="F137" s="2" t="s">
         <v>42</v>
@@ -4675,13 +4652,13 @@
       <c r="B138" s="3"/>
       <c r="C138" s="3"/>
       <c r="D138" s="3" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="E138" s="4" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="F138" s="2" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="G138" s="3"/>
     </row>
@@ -4690,10 +4667,10 @@
       <c r="B139" s="3"/>
       <c r="C139" s="3"/>
       <c r="D139" s="3" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="E139" s="4" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="F139" s="2" t="s">
         <v>42</v>
@@ -4705,13 +4682,13 @@
       <c r="B140" s="3"/>
       <c r="C140" s="3"/>
       <c r="D140" s="3" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="E140" s="4" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="F140" s="2" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="G140" s="3"/>
     </row>
@@ -4720,10 +4697,10 @@
       <c r="B141" s="3"/>
       <c r="C141" s="3"/>
       <c r="D141" s="3" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="E141" s="4" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="F141" s="1" t="s">
         <v>42</v>
@@ -4733,19 +4710,19 @@
     <row r="142" spans="1:7" ht="28.5" x14ac:dyDescent="0.2">
       <c r="A142" s="3"/>
       <c r="B142" s="3" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="C142" s="3" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="D142" s="3" t="s">
+        <v>192</v>
+      </c>
+      <c r="E142" s="4" t="s">
         <v>193</v>
       </c>
-      <c r="E142" s="4" t="s">
-        <v>194</v>
-      </c>
       <c r="F142" s="2" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="G142" s="3"/>
     </row>
@@ -4754,10 +4731,10 @@
       <c r="B143" s="3"/>
       <c r="C143" s="3"/>
       <c r="D143" s="3" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="E143" s="4" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="F143" s="2" t="s">
         <v>42</v>
@@ -4769,13 +4746,13 @@
       <c r="B144" s="3"/>
       <c r="C144" s="3"/>
       <c r="D144" s="3" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="E144" s="4" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="F144" s="2" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="G144" s="3"/>
     </row>
@@ -4784,10 +4761,10 @@
       <c r="B145" s="3"/>
       <c r="C145" s="3"/>
       <c r="D145" s="3" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="E145" s="4" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="F145" s="2" t="s">
         <v>42</v>
@@ -4799,13 +4776,13 @@
       <c r="B146" s="3"/>
       <c r="C146" s="3"/>
       <c r="D146" s="3" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="E146" s="4" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="F146" s="2" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="G146" s="3"/>
     </row>
@@ -4814,10 +4791,10 @@
       <c r="B147" s="3"/>
       <c r="C147" s="3"/>
       <c r="D147" s="3" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="E147" s="4" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="F147" s="2" t="s">
         <v>42</v>
@@ -4829,13 +4806,13 @@
       <c r="B148" s="3"/>
       <c r="C148" s="3"/>
       <c r="D148" s="3" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="E148" s="4" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="F148" s="2" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="G148" s="3"/>
     </row>
@@ -4844,10 +4821,10 @@
       <c r="B149" s="3"/>
       <c r="C149" s="3"/>
       <c r="D149" s="3" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="E149" s="4" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="F149" s="1" t="s">
         <v>42</v>
@@ -4857,19 +4834,19 @@
     <row r="150" spans="1:7" ht="28.5" x14ac:dyDescent="0.2">
       <c r="A150" s="3"/>
       <c r="B150" s="3" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="C150" s="3" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="D150" s="3" t="s">
+        <v>192</v>
+      </c>
+      <c r="E150" s="4" t="s">
         <v>193</v>
       </c>
-      <c r="E150" s="4" t="s">
-        <v>194</v>
-      </c>
       <c r="F150" s="2" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="G150" s="3"/>
     </row>
@@ -4878,10 +4855,10 @@
       <c r="B151" s="3"/>
       <c r="C151" s="3"/>
       <c r="D151" s="3" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="E151" s="4" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="F151" s="2" t="s">
         <v>42</v>
@@ -4893,13 +4870,13 @@
       <c r="B152" s="3"/>
       <c r="C152" s="3"/>
       <c r="D152" s="3" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="E152" s="4" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="F152" s="2" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="G152" s="3"/>
     </row>
@@ -4908,10 +4885,10 @@
       <c r="B153" s="3"/>
       <c r="C153" s="3"/>
       <c r="D153" s="3" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="E153" s="4" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="F153" s="2" t="s">
         <v>42</v>
@@ -4923,13 +4900,13 @@
       <c r="B154" s="3"/>
       <c r="C154" s="3"/>
       <c r="D154" s="3" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="E154" s="4" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="F154" s="2" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="G154" s="3"/>
     </row>
@@ -4938,10 +4915,10 @@
       <c r="B155" s="3"/>
       <c r="C155" s="3"/>
       <c r="D155" s="3" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="E155" s="4" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="F155" s="2" t="s">
         <v>42</v>
@@ -4953,13 +4930,13 @@
       <c r="B156" s="3"/>
       <c r="C156" s="3"/>
       <c r="D156" s="3" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="E156" s="4" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="F156" s="2" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="G156" s="3"/>
     </row>
@@ -4968,10 +4945,10 @@
       <c r="B157" s="3"/>
       <c r="C157" s="3"/>
       <c r="D157" s="3" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="E157" s="4" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="F157" s="1" t="s">
         <v>42</v>
@@ -4981,19 +4958,19 @@
     <row r="158" spans="1:7" ht="28.5" x14ac:dyDescent="0.2">
       <c r="A158" s="3"/>
       <c r="B158" s="3" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="C158" s="3" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="D158" s="3" t="s">
+        <v>192</v>
+      </c>
+      <c r="E158" s="4" t="s">
         <v>193</v>
       </c>
-      <c r="E158" s="4" t="s">
-        <v>194</v>
-      </c>
       <c r="F158" s="2" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="G158" s="3"/>
     </row>
@@ -5002,10 +4979,10 @@
       <c r="B159" s="3"/>
       <c r="C159" s="3"/>
       <c r="D159" s="3" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="E159" s="4" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="F159" s="2" t="s">
         <v>42</v>
@@ -5017,13 +4994,13 @@
       <c r="B160" s="3"/>
       <c r="C160" s="3"/>
       <c r="D160" s="3" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="E160" s="4" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="F160" s="2" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="G160" s="3"/>
     </row>
@@ -5032,10 +5009,10 @@
       <c r="B161" s="3"/>
       <c r="C161" s="3"/>
       <c r="D161" s="3" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="E161" s="4" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="F161" s="2" t="s">
         <v>42</v>
@@ -5047,13 +5024,13 @@
       <c r="B162" s="3"/>
       <c r="C162" s="3"/>
       <c r="D162" s="3" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="E162" s="4" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="F162" s="2" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="G162" s="3"/>
     </row>
@@ -5062,10 +5039,10 @@
       <c r="B163" s="3"/>
       <c r="C163" s="3"/>
       <c r="D163" s="3" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="E163" s="4" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="F163" s="2" t="s">
         <v>42</v>
@@ -5077,13 +5054,13 @@
       <c r="B164" s="3"/>
       <c r="C164" s="3"/>
       <c r="D164" s="3" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="E164" s="4" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="F164" s="2" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="G164" s="3"/>
     </row>
@@ -5092,10 +5069,10 @@
       <c r="B165" s="3"/>
       <c r="C165" s="3"/>
       <c r="D165" s="3" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="E165" s="4" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="F165" s="1" t="s">
         <v>42</v>
@@ -5105,19 +5082,19 @@
     <row r="166" spans="1:7" ht="28.5" x14ac:dyDescent="0.2">
       <c r="A166" s="3"/>
       <c r="B166" s="3" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="C166" s="3" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="D166" s="3" t="s">
+        <v>192</v>
+      </c>
+      <c r="E166" s="4" t="s">
         <v>193</v>
       </c>
-      <c r="E166" s="4" t="s">
-        <v>194</v>
-      </c>
       <c r="F166" s="2" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="G166" s="3"/>
     </row>
@@ -5126,10 +5103,10 @@
       <c r="B167" s="3"/>
       <c r="C167" s="3"/>
       <c r="D167" s="3" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="E167" s="4" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="F167" s="2" t="s">
         <v>42</v>
@@ -5141,13 +5118,13 @@
       <c r="B168" s="3"/>
       <c r="C168" s="3"/>
       <c r="D168" s="3" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="E168" s="4" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="F168" s="2" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="G168" s="3"/>
     </row>
@@ -5156,10 +5133,10 @@
       <c r="B169" s="3"/>
       <c r="C169" s="3"/>
       <c r="D169" s="3" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="E169" s="4" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="F169" s="2" t="s">
         <v>42</v>
@@ -5171,13 +5148,13 @@
       <c r="B170" s="3"/>
       <c r="C170" s="3"/>
       <c r="D170" s="3" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="E170" s="4" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="F170" s="2" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="G170" s="3"/>
     </row>
@@ -5186,10 +5163,10 @@
       <c r="B171" s="3"/>
       <c r="C171" s="3"/>
       <c r="D171" s="3" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="E171" s="4" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="F171" s="2" t="s">
         <v>42</v>
@@ -5201,13 +5178,13 @@
       <c r="B172" s="3"/>
       <c r="C172" s="3"/>
       <c r="D172" s="3" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="E172" s="4" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="F172" s="2" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="G172" s="3"/>
     </row>
@@ -5216,10 +5193,10 @@
       <c r="B173" s="3"/>
       <c r="C173" s="3"/>
       <c r="D173" s="3" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="E173" s="4" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="F173" s="1" t="s">
         <v>42</v>
@@ -5229,22 +5206,22 @@
     <row r="174" spans="1:7" ht="28.5" x14ac:dyDescent="0.2">
       <c r="A174" s="3"/>
       <c r="B174" s="3" t="s">
+        <v>302</v>
+      </c>
+      <c r="C174" s="3" t="s">
         <v>303</v>
       </c>
-      <c r="C174" s="3" t="s">
+      <c r="D174" s="3" t="s">
+        <v>192</v>
+      </c>
+      <c r="E174" s="4" t="s">
         <v>304</v>
       </c>
-      <c r="D174" s="3" t="s">
-        <v>193</v>
-      </c>
-      <c r="E174" s="4" t="s">
-        <v>305</v>
-      </c>
       <c r="F174" s="2" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="G174" s="21" t="s">
-        <v>477</v>
+        <v>476</v>
       </c>
     </row>
     <row r="175" spans="1:7" ht="28.5" x14ac:dyDescent="0.2">
@@ -5252,32 +5229,32 @@
       <c r="B175" s="3"/>
       <c r="C175" s="3"/>
       <c r="D175" s="3" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="E175" s="4" t="s">
         <v>46</v>
       </c>
       <c r="F175" s="2" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="G175" s="3"/>
     </row>
     <row r="176" spans="1:7" ht="28.5" x14ac:dyDescent="0.2">
       <c r="A176" s="3"/>
       <c r="B176" s="3" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="C176" s="3" t="s">
+        <v>311</v>
+      </c>
+      <c r="D176" s="3" t="s">
+        <v>192</v>
+      </c>
+      <c r="E176" s="4" t="s">
+        <v>304</v>
+      </c>
+      <c r="F176" s="2" t="s">
         <v>312</v>
-      </c>
-      <c r="D176" s="3" t="s">
-        <v>193</v>
-      </c>
-      <c r="E176" s="4" t="s">
-        <v>305</v>
-      </c>
-      <c r="F176" s="2" t="s">
-        <v>313</v>
       </c>
       <c r="G176" s="3"/>
     </row>
@@ -5286,32 +5263,32 @@
       <c r="B177" s="3"/>
       <c r="C177" s="3"/>
       <c r="D177" s="3" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="E177" s="4" t="s">
         <v>46</v>
       </c>
       <c r="F177" s="2" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="G177" s="3"/>
     </row>
     <row r="178" spans="1:7" ht="28.5" x14ac:dyDescent="0.2">
       <c r="A178" s="3"/>
       <c r="B178" s="3" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="C178" s="3" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="D178" s="3" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="E178" s="4" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="F178" s="2" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="G178" s="3"/>
     </row>
@@ -5320,32 +5297,32 @@
       <c r="B179" s="3"/>
       <c r="C179" s="3"/>
       <c r="D179" s="3" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="E179" s="4" t="s">
         <v>46</v>
       </c>
       <c r="F179" s="2" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="G179" s="3"/>
     </row>
     <row r="180" spans="1:7" ht="28.5" x14ac:dyDescent="0.2">
       <c r="A180" s="3"/>
       <c r="B180" s="3" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="C180" s="3" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="D180" s="3" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="E180" s="4" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="F180" s="2" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="G180" s="3"/>
     </row>
@@ -5354,32 +5331,32 @@
       <c r="B181" s="3"/>
       <c r="C181" s="3"/>
       <c r="D181" s="3" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="E181" s="4" t="s">
         <v>46</v>
       </c>
       <c r="F181" s="2" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="G181" s="3"/>
     </row>
     <row r="182" spans="1:7" ht="28.5" x14ac:dyDescent="0.2">
       <c r="A182" s="3"/>
       <c r="B182" s="3" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="C182" s="3" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="D182" s="3" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="E182" s="4" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="F182" s="2" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="G182" s="3"/>
     </row>
@@ -5388,32 +5365,32 @@
       <c r="B183" s="3"/>
       <c r="C183" s="3"/>
       <c r="D183" s="3" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="E183" s="4" t="s">
         <v>46</v>
       </c>
       <c r="F183" s="2" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="G183" s="3"/>
     </row>
     <row r="184" spans="1:7" ht="28.5" x14ac:dyDescent="0.2">
       <c r="A184" s="3"/>
       <c r="B184" s="3" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="C184" s="3" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="D184" s="3" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="E184" s="4" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="F184" s="2" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="G184" s="2"/>
     </row>
@@ -5422,32 +5399,32 @@
       <c r="B185" s="3"/>
       <c r="C185" s="3"/>
       <c r="D185" s="3" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="E185" s="4" t="s">
         <v>46</v>
       </c>
       <c r="F185" s="2" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="G185" s="2"/>
     </row>
     <row r="186" spans="1:7" ht="28.5" x14ac:dyDescent="0.2">
       <c r="A186" s="3"/>
       <c r="B186" s="3" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="C186" s="3" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
       <c r="D186" s="3" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="E186" s="4" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="F186" s="2" t="s">
-        <v>336</v>
+        <v>335</v>
       </c>
       <c r="G186" s="2"/>
     </row>
@@ -5456,32 +5433,32 @@
       <c r="B187" s="3"/>
       <c r="C187" s="3"/>
       <c r="D187" s="3" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="E187" s="4" t="s">
         <v>46</v>
       </c>
       <c r="F187" s="2" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="G187" s="2"/>
     </row>
     <row r="188" spans="1:7" ht="28.5" x14ac:dyDescent="0.2">
       <c r="A188" s="3"/>
       <c r="B188" s="3" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="C188" s="3" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c r="D188" s="3" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="E188" s="4" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="F188" s="2" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="G188" s="2"/>
     </row>
@@ -5490,32 +5467,32 @@
       <c r="B189" s="3"/>
       <c r="C189" s="3"/>
       <c r="D189" s="3" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="E189" s="4" t="s">
         <v>46</v>
       </c>
       <c r="F189" s="2" t="s">
-        <v>339</v>
+        <v>338</v>
       </c>
       <c r="G189" s="2"/>
     </row>
     <row r="190" spans="1:7" ht="28.5" x14ac:dyDescent="0.2">
       <c r="A190" s="3"/>
       <c r="B190" s="3" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="C190" s="3" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="D190" s="3" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="E190" s="4" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="F190" s="2" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="G190" s="2"/>
     </row>
@@ -5524,32 +5501,32 @@
       <c r="B191" s="3"/>
       <c r="C191" s="3"/>
       <c r="D191" s="3" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="E191" s="4" t="s">
         <v>46</v>
       </c>
       <c r="F191" s="2" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
       <c r="G191" s="2"/>
     </row>
     <row r="192" spans="1:7" ht="28.5" x14ac:dyDescent="0.2">
       <c r="A192" s="3"/>
       <c r="B192" s="3" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="C192" s="3" t="s">
-        <v>349</v>
+        <v>348</v>
       </c>
       <c r="D192" s="3" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="E192" s="4" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="F192" s="2" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="G192" s="2"/>
     </row>
@@ -5558,32 +5535,32 @@
       <c r="B193" s="3"/>
       <c r="C193" s="3"/>
       <c r="D193" s="3" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="E193" s="4" t="s">
         <v>46</v>
       </c>
       <c r="F193" s="2" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="G193" s="2"/>
     </row>
     <row r="194" spans="1:7" ht="28.5" x14ac:dyDescent="0.2">
       <c r="A194" s="3"/>
       <c r="B194" s="3" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="C194" s="3" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="D194" s="3" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="E194" s="4" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="F194" s="2" t="s">
-        <v>360</v>
+        <v>359</v>
       </c>
       <c r="G194" s="2"/>
     </row>
@@ -5592,32 +5569,32 @@
       <c r="B195" s="3"/>
       <c r="C195" s="3"/>
       <c r="D195" s="3" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="E195" s="4" t="s">
         <v>46</v>
       </c>
       <c r="F195" s="2" t="s">
-        <v>361</v>
+        <v>360</v>
       </c>
       <c r="G195" s="2"/>
     </row>
     <row r="196" spans="1:7" ht="28.5" x14ac:dyDescent="0.2">
       <c r="A196" s="3"/>
       <c r="B196" s="3" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
       <c r="C196" s="3" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="D196" s="3" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="E196" s="4" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="F196" s="2" t="s">
-        <v>362</v>
+        <v>361</v>
       </c>
       <c r="G196" s="2"/>
     </row>
@@ -5626,32 +5603,32 @@
       <c r="B197" s="3"/>
       <c r="C197" s="3"/>
       <c r="D197" s="3" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="E197" s="4" t="s">
         <v>46</v>
       </c>
       <c r="F197" s="2" t="s">
-        <v>363</v>
+        <v>362</v>
       </c>
       <c r="G197" s="2"/>
     </row>
     <row r="198" spans="1:7" ht="28.5" x14ac:dyDescent="0.2">
       <c r="A198" s="3"/>
       <c r="B198" s="3" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="C198" s="3" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="D198" s="3" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="E198" s="4" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="F198" s="2" t="s">
-        <v>364</v>
+        <v>363</v>
       </c>
       <c r="G198" s="2"/>
     </row>
@@ -5660,32 +5637,32 @@
       <c r="B199" s="3"/>
       <c r="C199" s="3"/>
       <c r="D199" s="3" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="E199" s="4" t="s">
         <v>46</v>
       </c>
       <c r="F199" s="2" t="s">
-        <v>365</v>
+        <v>364</v>
       </c>
       <c r="G199" s="2"/>
     </row>
     <row r="200" spans="1:7" ht="28.5" x14ac:dyDescent="0.2">
       <c r="A200" s="3"/>
       <c r="B200" s="3" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="C200" s="3" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="D200" s="3" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="E200" s="4" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="F200" s="2" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
       <c r="G200" s="2"/>
     </row>
@@ -5694,32 +5671,32 @@
       <c r="B201" s="3"/>
       <c r="C201" s="3"/>
       <c r="D201" s="3" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="E201" s="4" t="s">
         <v>46</v>
       </c>
       <c r="F201" s="2" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
       <c r="G201" s="2"/>
     </row>
     <row r="202" spans="1:7" ht="28.5" x14ac:dyDescent="0.2">
       <c r="A202" s="3"/>
       <c r="B202" s="3" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="C202" s="3" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="D202" s="3" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="E202" s="4" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="F202" s="2" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="G202" s="2"/>
     </row>
@@ -5728,32 +5705,32 @@
       <c r="B203" s="3"/>
       <c r="C203" s="3"/>
       <c r="D203" s="3" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="E203" s="4" t="s">
         <v>46</v>
       </c>
       <c r="F203" s="2" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
       <c r="G203" s="2"/>
     </row>
     <row r="204" spans="1:7" ht="28.5" x14ac:dyDescent="0.2">
       <c r="A204" s="3"/>
       <c r="B204" s="3" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="C204" s="3" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="D204" s="3" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="E204" s="4" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="F204" s="2" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
       <c r="G204" s="2"/>
     </row>
@@ -5762,32 +5739,32 @@
       <c r="B205" s="3"/>
       <c r="C205" s="3"/>
       <c r="D205" s="3" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="E205" s="4" t="s">
         <v>46</v>
       </c>
       <c r="F205" s="2" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="G205" s="2"/>
     </row>
     <row r="206" spans="1:7" ht="28.5" x14ac:dyDescent="0.2">
       <c r="A206" s="3"/>
       <c r="B206" s="3" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="C206" s="3" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="D206" s="3" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="E206" s="4" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="F206" s="2" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="G206" s="2"/>
     </row>
@@ -5796,32 +5773,32 @@
       <c r="B207" s="3"/>
       <c r="C207" s="3"/>
       <c r="D207" s="3" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="E207" s="4" t="s">
         <v>46</v>
       </c>
       <c r="F207" s="2" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="G207" s="2"/>
     </row>
     <row r="208" spans="1:7" ht="28.5" x14ac:dyDescent="0.2">
       <c r="A208" s="3"/>
       <c r="B208" s="3" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
       <c r="C208" s="3" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="D208" s="3" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="E208" s="4" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="F208" s="2" t="s">
-        <v>379</v>
+        <v>378</v>
       </c>
       <c r="G208" s="2"/>
     </row>
@@ -5830,32 +5807,32 @@
       <c r="B209" s="3"/>
       <c r="C209" s="3"/>
       <c r="D209" s="3" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="E209" s="4" t="s">
         <v>46</v>
       </c>
       <c r="F209" s="2" t="s">
-        <v>380</v>
+        <v>379</v>
       </c>
       <c r="G209" s="2"/>
     </row>
     <row r="210" spans="1:7" ht="28.5" x14ac:dyDescent="0.2">
       <c r="A210" s="3"/>
       <c r="B210" s="3" t="s">
-        <v>334</v>
+        <v>333</v>
       </c>
       <c r="C210" s="3" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="D210" s="3" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="E210" s="4" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="F210" s="2" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="G210" s="2"/>
     </row>
@@ -5864,32 +5841,32 @@
       <c r="B211" s="3"/>
       <c r="C211" s="3"/>
       <c r="D211" s="3" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="E211" s="4" t="s">
         <v>46</v>
       </c>
       <c r="F211" s="2" t="s">
-        <v>382</v>
+        <v>381</v>
       </c>
       <c r="G211" s="2"/>
     </row>
     <row r="212" spans="1:7" ht="28.5" x14ac:dyDescent="0.2">
       <c r="A212" s="3"/>
       <c r="B212" s="3" t="s">
-        <v>335</v>
+        <v>334</v>
       </c>
       <c r="C212" s="3" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="D212" s="3" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="E212" s="4" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="F212" s="2" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
       <c r="G212" s="2"/>
     </row>
@@ -5898,32 +5875,32 @@
       <c r="B213" s="3"/>
       <c r="C213" s="3"/>
       <c r="D213" s="3" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="E213" s="4" t="s">
         <v>46</v>
       </c>
       <c r="F213" s="2" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
       <c r="G213" s="2"/>
     </row>
     <row r="214" spans="1:7" ht="28.5" x14ac:dyDescent="0.2">
       <c r="A214" s="3"/>
       <c r="B214" s="3" t="s">
-        <v>350</v>
+        <v>349</v>
       </c>
       <c r="C214" s="3" t="s">
-        <v>370</v>
+        <v>369</v>
       </c>
       <c r="D214" s="3" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="E214" s="4" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="F214" s="2" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="G214" s="2"/>
     </row>
@@ -5932,32 +5909,32 @@
       <c r="B215" s="3"/>
       <c r="C215" s="3"/>
       <c r="D215" s="3" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="E215" s="4" t="s">
         <v>46</v>
       </c>
       <c r="F215" s="2" t="s">
-        <v>398</v>
+        <v>397</v>
       </c>
       <c r="G215" s="2"/>
     </row>
     <row r="216" spans="1:7" ht="28.5" x14ac:dyDescent="0.2">
       <c r="A216" s="3"/>
       <c r="B216" s="3" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="C216" s="3" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
       <c r="D216" s="3" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="E216" s="4" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="F216" s="2" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
       <c r="G216" s="2"/>
     </row>
@@ -5966,32 +5943,32 @@
       <c r="B217" s="3"/>
       <c r="C217" s="3"/>
       <c r="D217" s="3" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="E217" s="4" t="s">
         <v>46</v>
       </c>
       <c r="F217" s="2" t="s">
-        <v>400</v>
+        <v>399</v>
       </c>
       <c r="G217" s="2"/>
     </row>
     <row r="218" spans="1:7" ht="28.5" x14ac:dyDescent="0.2">
       <c r="A218" s="3"/>
       <c r="B218" s="3" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
       <c r="C218" s="3" t="s">
-        <v>372</v>
+        <v>371</v>
       </c>
       <c r="D218" s="3" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="E218" s="4" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="F218" s="2" t="s">
-        <v>401</v>
+        <v>400</v>
       </c>
       <c r="G218" s="2"/>
     </row>
@@ -6000,32 +5977,32 @@
       <c r="B219" s="3"/>
       <c r="C219" s="3"/>
       <c r="D219" s="3" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="E219" s="4" t="s">
         <v>46</v>
       </c>
       <c r="F219" s="2" t="s">
-        <v>402</v>
+        <v>401</v>
       </c>
       <c r="G219" s="2"/>
     </row>
     <row r="220" spans="1:7" ht="28.5" x14ac:dyDescent="0.2">
       <c r="A220" s="3"/>
       <c r="B220" s="3" t="s">
-        <v>353</v>
+        <v>352</v>
       </c>
       <c r="C220" s="3" t="s">
-        <v>373</v>
+        <v>372</v>
       </c>
       <c r="D220" s="3" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="E220" s="4" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="F220" s="2" t="s">
-        <v>403</v>
+        <v>402</v>
       </c>
       <c r="G220" s="2"/>
     </row>
@@ -6034,32 +6011,32 @@
       <c r="B221" s="3"/>
       <c r="C221" s="3"/>
       <c r="D221" s="3" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="E221" s="4" t="s">
         <v>46</v>
       </c>
       <c r="F221" s="2" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="G221" s="2"/>
     </row>
     <row r="222" spans="1:7" ht="28.5" x14ac:dyDescent="0.2">
       <c r="A222" s="3"/>
       <c r="B222" s="3" t="s">
-        <v>354</v>
+        <v>353</v>
       </c>
       <c r="C222" s="3" t="s">
-        <v>374</v>
+        <v>373</v>
       </c>
       <c r="D222" s="3" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="E222" s="4" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="F222" s="2" t="s">
-        <v>405</v>
+        <v>404</v>
       </c>
       <c r="G222" s="2"/>
     </row>
@@ -6068,32 +6045,32 @@
       <c r="B223" s="3"/>
       <c r="C223" s="3"/>
       <c r="D223" s="3" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="E223" s="4" t="s">
         <v>46</v>
       </c>
       <c r="F223" s="2" t="s">
-        <v>406</v>
+        <v>405</v>
       </c>
       <c r="G223" s="2"/>
     </row>
     <row r="224" spans="1:7" ht="28.5" x14ac:dyDescent="0.2">
       <c r="A224" s="3"/>
       <c r="B224" s="3" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="C224" s="3" t="s">
-        <v>387</v>
+        <v>386</v>
       </c>
       <c r="D224" s="3" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="E224" s="4" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="F224" s="2" t="s">
-        <v>417</v>
+        <v>416</v>
       </c>
       <c r="G224" s="2"/>
     </row>
@@ -6102,32 +6079,32 @@
       <c r="B225" s="3"/>
       <c r="C225" s="3"/>
       <c r="D225" s="3" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="E225" s="4" t="s">
         <v>46</v>
       </c>
       <c r="F225" s="2" t="s">
-        <v>418</v>
+        <v>417</v>
       </c>
       <c r="G225" s="2"/>
     </row>
     <row r="226" spans="1:7" ht="28.5" x14ac:dyDescent="0.2">
       <c r="A226" s="3"/>
       <c r="B226" s="3" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="C226" s="3" t="s">
-        <v>388</v>
+        <v>387</v>
       </c>
       <c r="D226" s="3" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="E226" s="4" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="F226" s="2" t="s">
-        <v>419</v>
+        <v>418</v>
       </c>
       <c r="G226" s="2"/>
     </row>
@@ -6136,32 +6113,32 @@
       <c r="B227" s="3"/>
       <c r="C227" s="3"/>
       <c r="D227" s="3" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="E227" s="4" t="s">
         <v>46</v>
       </c>
       <c r="F227" s="2" t="s">
-        <v>420</v>
+        <v>419</v>
       </c>
       <c r="G227" s="2"/>
     </row>
     <row r="228" spans="1:7" ht="28.5" x14ac:dyDescent="0.2">
       <c r="A228" s="3"/>
       <c r="B228" s="3" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="C228" s="3" t="s">
-        <v>389</v>
+        <v>388</v>
       </c>
       <c r="D228" s="3" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="E228" s="4" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="F228" s="2" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="G228" s="2"/>
     </row>
@@ -6170,32 +6147,32 @@
       <c r="B229" s="3"/>
       <c r="C229" s="3"/>
       <c r="D229" s="3" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="E229" s="4" t="s">
         <v>46</v>
       </c>
       <c r="F229" s="2" t="s">
-        <v>422</v>
+        <v>421</v>
       </c>
       <c r="G229" s="2"/>
     </row>
     <row r="230" spans="1:7" ht="28.5" x14ac:dyDescent="0.2">
       <c r="A230" s="3"/>
       <c r="B230" s="3" t="s">
-        <v>358</v>
+        <v>357</v>
       </c>
       <c r="C230" s="3" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="D230" s="3" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="E230" s="4" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="F230" s="2" t="s">
-        <v>423</v>
+        <v>422</v>
       </c>
       <c r="G230" s="2"/>
     </row>
@@ -6204,32 +6181,32 @@
       <c r="B231" s="3"/>
       <c r="C231" s="3"/>
       <c r="D231" s="3" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="E231" s="4" t="s">
         <v>46</v>
       </c>
       <c r="F231" s="2" t="s">
-        <v>424</v>
+        <v>423</v>
       </c>
       <c r="G231" s="2"/>
     </row>
     <row r="232" spans="1:7" ht="28.5" x14ac:dyDescent="0.2">
       <c r="A232" s="3"/>
       <c r="B232" s="3" t="s">
-        <v>359</v>
+        <v>358</v>
       </c>
       <c r="C232" s="3" t="s">
-        <v>391</v>
+        <v>390</v>
       </c>
       <c r="D232" s="3" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="E232" s="4" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="F232" s="2" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
       <c r="G232" s="2"/>
     </row>
@@ -6238,32 +6215,32 @@
       <c r="B233" s="3"/>
       <c r="C233" s="3"/>
       <c r="D233" s="3" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="E233" s="4" t="s">
         <v>46</v>
       </c>
       <c r="F233" s="2" t="s">
-        <v>426</v>
+        <v>425</v>
       </c>
       <c r="G233" s="2"/>
     </row>
     <row r="234" spans="1:7" ht="28.5" x14ac:dyDescent="0.2">
       <c r="A234" s="3"/>
       <c r="B234" s="3" t="s">
-        <v>385</v>
+        <v>384</v>
       </c>
       <c r="C234" s="3" t="s">
-        <v>392</v>
+        <v>391</v>
       </c>
       <c r="D234" s="3" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="E234" s="4" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="F234" s="2" t="s">
-        <v>434</v>
+        <v>433</v>
       </c>
       <c r="G234" s="2"/>
     </row>
@@ -6272,32 +6249,32 @@
       <c r="B235" s="3"/>
       <c r="C235" s="3"/>
       <c r="D235" s="3" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="E235" s="4" t="s">
         <v>46</v>
       </c>
       <c r="F235" s="2" t="s">
-        <v>435</v>
+        <v>434</v>
       </c>
       <c r="G235" s="2"/>
     </row>
     <row r="236" spans="1:7" ht="28.5" x14ac:dyDescent="0.2">
       <c r="A236" s="3"/>
       <c r="B236" s="3" t="s">
-        <v>386</v>
+        <v>385</v>
       </c>
       <c r="C236" s="3" t="s">
-        <v>393</v>
+        <v>392</v>
       </c>
       <c r="D236" s="3" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="E236" s="4" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="F236" s="2" t="s">
-        <v>436</v>
+        <v>435</v>
       </c>
       <c r="G236" s="2"/>
     </row>
@@ -6306,19 +6283,19 @@
       <c r="B237" s="3"/>
       <c r="C237" s="3"/>
       <c r="D237" s="3" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="E237" s="4" t="s">
         <v>46</v>
       </c>
       <c r="F237" s="2" t="s">
-        <v>437</v>
+        <v>436</v>
       </c>
       <c r="G237" s="2"/>
     </row>
     <row r="238" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A238" s="3" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="B238" s="3"/>
       <c r="C238" s="3"/>
@@ -6333,16 +6310,16 @@
         <v>75</v>
       </c>
       <c r="C239" s="3" t="s">
-        <v>394</v>
+        <v>393</v>
       </c>
       <c r="D239" s="3" t="s">
         <v>8</v>
       </c>
       <c r="E239" s="4" t="s">
+        <v>207</v>
+      </c>
+      <c r="F239" s="5" t="s">
         <v>208</v>
-      </c>
-      <c r="F239" s="5" t="s">
-        <v>209</v>
       </c>
       <c r="G239" s="5" t="s">
         <v>78</v>
@@ -6354,7 +6331,7 @@
       <c r="C240" s="3"/>
       <c r="D240" s="3"/>
       <c r="E240" s="4" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="F240" s="3" t="s">
         <v>79</v>
@@ -6369,10 +6346,10 @@
         <v>8</v>
       </c>
       <c r="E241" s="4" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="F241" s="5" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="G241" s="3"/>
     </row>
@@ -6382,7 +6359,7 @@
       <c r="C242" s="3"/>
       <c r="D242" s="3"/>
       <c r="E242" s="4" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="F242" s="3" t="s">
         <v>79</v>
@@ -6397,10 +6374,10 @@
         <v>8</v>
       </c>
       <c r="E243" s="4" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="F243" s="5" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="G243" s="3"/>
     </row>
@@ -6410,7 +6387,7 @@
       <c r="C244" s="3"/>
       <c r="D244" s="3"/>
       <c r="E244" s="4" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="F244" s="3" t="s">
         <v>79</v>
@@ -6423,7 +6400,7 @@
         <v>80</v>
       </c>
       <c r="C245" s="3" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="D245" s="3" t="s">
         <v>8</v>
@@ -6440,16 +6417,16 @@
       <c r="A246" s="3"/>
       <c r="B246" s="3"/>
       <c r="C246" s="3"/>
-      <c r="D246" s="24" t="s">
+      <c r="D246" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="E246" s="25" t="s">
+      <c r="E246" s="24" t="s">
         <v>12</v>
       </c>
-      <c r="F246" s="26" t="s">
-        <v>87</v>
-      </c>
-      <c r="G246" s="24"/>
+      <c r="F246" s="5" t="s">
+        <v>85</v>
+      </c>
+      <c r="G246" s="3"/>
     </row>
     <row r="247" spans="1:7" ht="28.5" x14ac:dyDescent="0.2">
       <c r="A247" s="3"/>
@@ -6458,39 +6435,39 @@
       <c r="D247" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="E247" s="27" t="s">
-        <v>12</v>
+      <c r="E247" s="24" t="s">
+        <v>35</v>
       </c>
       <c r="F247" s="5" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="G247" s="3"/>
     </row>
-    <row r="248" spans="1:7" ht="28.5" x14ac:dyDescent="0.2">
+    <row r="248" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A248" s="3"/>
       <c r="B248" s="3"/>
       <c r="C248" s="3"/>
-      <c r="D248" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="E248" s="27" t="s">
-        <v>35</v>
-      </c>
-      <c r="F248" s="5" t="s">
-        <v>88</v>
+      <c r="D248" s="3"/>
+      <c r="E248" s="4" t="s">
+        <v>477</v>
+      </c>
+      <c r="F248" s="3" t="s">
+        <v>32</v>
       </c>
       <c r="G248" s="3"/>
     </row>
-    <row r="249" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="249" spans="1:7" ht="28.5" x14ac:dyDescent="0.2">
       <c r="A249" s="3"/>
       <c r="B249" s="3"/>
       <c r="C249" s="3"/>
-      <c r="D249" s="3"/>
+      <c r="D249" s="3" t="s">
+        <v>8</v>
+      </c>
       <c r="E249" s="4" t="s">
-        <v>478</v>
-      </c>
-      <c r="F249" s="3" t="s">
-        <v>32</v>
+        <v>81</v>
+      </c>
+      <c r="F249" s="5" t="s">
+        <v>89</v>
       </c>
       <c r="G249" s="3"/>
     </row>
@@ -6502,7 +6479,7 @@
         <v>8</v>
       </c>
       <c r="E250" s="4" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="F250" s="5" t="s">
         <v>90</v>
@@ -6517,7 +6494,7 @@
         <v>8</v>
       </c>
       <c r="E251" s="4" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="F251" s="5" t="s">
         <v>91</v>
@@ -6532,12 +6509,14 @@
         <v>8</v>
       </c>
       <c r="E252" s="4" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="F252" s="5" t="s">
+        <v>88</v>
+      </c>
+      <c r="G252" s="3" t="s">
         <v>92</v>
       </c>
-      <c r="G252" s="3"/>
     </row>
     <row r="253" spans="1:7" ht="28.5" x14ac:dyDescent="0.2">
       <c r="A253" s="3"/>
@@ -6547,82 +6526,78 @@
         <v>8</v>
       </c>
       <c r="E253" s="4" t="s">
-        <v>84</v>
+        <v>443</v>
       </c>
       <c r="F253" s="5" t="s">
-        <v>89</v>
+        <v>189</v>
       </c>
       <c r="G253" s="3" t="s">
-        <v>93</v>
-      </c>
-    </row>
-    <row r="254" spans="1:7" ht="28.5" x14ac:dyDescent="0.2">
+        <v>442</v>
+      </c>
+    </row>
+    <row r="254" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A254" s="3"/>
       <c r="B254" s="3"/>
       <c r="C254" s="3"/>
-      <c r="D254" s="3" t="s">
-        <v>8</v>
-      </c>
+      <c r="D254" s="3"/>
       <c r="E254" s="4" t="s">
         <v>444</v>
       </c>
-      <c r="F254" s="5" t="s">
-        <v>190</v>
-      </c>
-      <c r="G254" s="3" t="s">
-        <v>443</v>
-      </c>
-    </row>
-    <row r="255" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="F254" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="G254" s="3"/>
+    </row>
+    <row r="255" spans="1:7" ht="28.5" x14ac:dyDescent="0.2">
       <c r="A255" s="3"/>
-      <c r="B255" s="3"/>
-      <c r="C255" s="3"/>
-      <c r="D255" s="3"/>
+      <c r="B255" s="3" t="s">
+        <v>93</v>
+      </c>
+      <c r="C255" s="3" t="s">
+        <v>395</v>
+      </c>
+      <c r="D255" s="3" t="s">
+        <v>8</v>
+      </c>
       <c r="E255" s="4" t="s">
-        <v>445</v>
-      </c>
-      <c r="F255" s="3" t="s">
-        <v>32</v>
+        <v>74</v>
+      </c>
+      <c r="F255" s="5" t="s">
+        <v>94</v>
       </c>
       <c r="G255" s="3"/>
     </row>
     <row r="256" spans="1:7" ht="28.5" x14ac:dyDescent="0.2">
-      <c r="A256" s="3" t="s">
-        <v>99</v>
-      </c>
-      <c r="B256" s="3" t="s">
-        <v>94</v>
-      </c>
-      <c r="C256" s="3" t="s">
-        <v>396</v>
-      </c>
-      <c r="D256" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="E256" s="4" t="s">
-        <v>74</v>
-      </c>
-      <c r="F256" s="5" t="s">
+      <c r="A256" s="3"/>
+      <c r="B256" s="10" t="s">
         <v>95</v>
       </c>
-      <c r="G256" s="3"/>
+      <c r="C256" s="10" t="s">
+        <v>406</v>
+      </c>
+      <c r="D256" s="10" t="s">
+        <v>16</v>
+      </c>
+      <c r="E256" s="7" t="s">
+        <v>33</v>
+      </c>
+      <c r="F256" s="18" t="s">
+        <v>459</v>
+      </c>
+      <c r="G256" s="10"/>
     </row>
     <row r="257" spans="1:7" ht="28.5" x14ac:dyDescent="0.2">
       <c r="A257" s="3"/>
-      <c r="B257" s="10" t="s">
-        <v>96</v>
-      </c>
-      <c r="C257" s="10" t="s">
-        <v>407</v>
-      </c>
+      <c r="B257" s="10"/>
+      <c r="C257" s="10"/>
       <c r="D257" s="10" t="s">
-        <v>16</v>
+        <v>457</v>
       </c>
       <c r="E257" s="7" t="s">
-        <v>33</v>
+        <v>458</v>
       </c>
       <c r="F257" s="18" t="s">
-        <v>460</v>
+        <v>464</v>
       </c>
       <c r="G257" s="10"/>
     </row>
@@ -6631,15 +6606,17 @@
       <c r="B258" s="10"/>
       <c r="C258" s="10"/>
       <c r="D258" s="10" t="s">
-        <v>458</v>
+        <v>16</v>
       </c>
       <c r="E258" s="7" t="s">
-        <v>459</v>
+        <v>35</v>
       </c>
       <c r="F258" s="18" t="s">
-        <v>465</v>
-      </c>
-      <c r="G258" s="10"/>
+        <v>460</v>
+      </c>
+      <c r="G258" s="10" t="s">
+        <v>97</v>
+      </c>
     </row>
     <row r="259" spans="1:7" ht="28.5" x14ac:dyDescent="0.2">
       <c r="A259" s="3"/>
@@ -6649,13 +6626,13 @@
         <v>16</v>
       </c>
       <c r="E259" s="7" t="s">
-        <v>35</v>
+        <v>15</v>
       </c>
       <c r="F259" s="18" t="s">
-        <v>461</v>
+        <v>468</v>
       </c>
       <c r="G259" s="10" t="s">
-        <v>98</v>
+        <v>176</v>
       </c>
     </row>
     <row r="260" spans="1:7" ht="28.5" x14ac:dyDescent="0.2">
@@ -6663,16 +6640,16 @@
       <c r="B260" s="10"/>
       <c r="C260" s="10"/>
       <c r="D260" s="10" t="s">
-        <v>16</v>
+        <v>465</v>
       </c>
       <c r="E260" s="7" t="s">
-        <v>15</v>
+        <v>466</v>
       </c>
       <c r="F260" s="18" t="s">
-        <v>469</v>
+        <v>467</v>
       </c>
       <c r="G260" s="10" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
     </row>
     <row r="261" spans="1:7" ht="28.5" x14ac:dyDescent="0.2">
@@ -6680,19 +6657,17 @@
       <c r="B261" s="10"/>
       <c r="C261" s="10"/>
       <c r="D261" s="10" t="s">
-        <v>466</v>
+        <v>16</v>
       </c>
       <c r="E261" s="7" t="s">
-        <v>467</v>
-      </c>
-      <c r="F261" s="18" t="s">
-        <v>468</v>
-      </c>
-      <c r="G261" s="10" t="s">
-        <v>177</v>
-      </c>
-    </row>
-    <row r="262" spans="1:7" ht="28.5" x14ac:dyDescent="0.2">
+        <v>19</v>
+      </c>
+      <c r="F261" s="13" t="s">
+        <v>96</v>
+      </c>
+      <c r="G261" s="10"/>
+    </row>
+    <row r="262" spans="1:7" ht="42.75" x14ac:dyDescent="0.2">
       <c r="A262" s="3"/>
       <c r="B262" s="10"/>
       <c r="C262" s="10"/>
@@ -6700,12 +6675,14 @@
         <v>16</v>
       </c>
       <c r="E262" s="7" t="s">
-        <v>19</v>
-      </c>
-      <c r="F262" s="13" t="s">
-        <v>97</v>
-      </c>
-      <c r="G262" s="10"/>
+        <v>23</v>
+      </c>
+      <c r="F262" s="18" t="s">
+        <v>463</v>
+      </c>
+      <c r="G262" s="10" t="s">
+        <v>176</v>
+      </c>
     </row>
     <row r="263" spans="1:7" ht="42.75" x14ac:dyDescent="0.2">
       <c r="A263" s="3"/>
@@ -6715,58 +6692,56 @@
         <v>16</v>
       </c>
       <c r="E263" s="7" t="s">
-        <v>23</v>
+        <v>53</v>
       </c>
       <c r="F263" s="18" t="s">
-        <v>464</v>
+        <v>461</v>
       </c>
       <c r="G263" s="10" t="s">
-        <v>177</v>
-      </c>
-    </row>
-    <row r="264" spans="1:7" ht="42.75" x14ac:dyDescent="0.2">
+        <v>462</v>
+      </c>
+    </row>
+    <row r="264" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A264" s="3"/>
       <c r="B264" s="10"/>
       <c r="C264" s="10"/>
-      <c r="D264" s="10" t="s">
-        <v>16</v>
-      </c>
+      <c r="D264" s="10"/>
       <c r="E264" s="7" t="s">
-        <v>53</v>
-      </c>
-      <c r="F264" s="18" t="s">
-        <v>462</v>
-      </c>
-      <c r="G264" s="10" t="s">
-        <v>463</v>
-      </c>
-    </row>
-    <row r="265" spans="1:7" x14ac:dyDescent="0.2">
+        <v>469</v>
+      </c>
+      <c r="F264" s="10" t="s">
+        <v>32</v>
+      </c>
+      <c r="G264" s="10"/>
+    </row>
+    <row r="265" spans="1:7" ht="28.5" x14ac:dyDescent="0.2">
       <c r="A265" s="3"/>
-      <c r="B265" s="10"/>
-      <c r="C265" s="10"/>
-      <c r="D265" s="10"/>
-      <c r="E265" s="7" t="s">
-        <v>470</v>
-      </c>
-      <c r="F265" s="10" t="s">
-        <v>32</v>
-      </c>
-      <c r="G265" s="10"/>
+      <c r="B265" s="3" t="s">
+        <v>99</v>
+      </c>
+      <c r="C265" s="3" t="s">
+        <v>407</v>
+      </c>
+      <c r="D265" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="E265" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="F265" s="5" t="s">
+        <v>89</v>
+      </c>
+      <c r="G265" s="3"/>
     </row>
     <row r="266" spans="1:7" ht="28.5" x14ac:dyDescent="0.2">
       <c r="A266" s="3"/>
-      <c r="B266" s="3" t="s">
-        <v>100</v>
-      </c>
-      <c r="C266" s="3" t="s">
-        <v>408</v>
-      </c>
+      <c r="B266" s="3"/>
+      <c r="C266" s="3"/>
       <c r="D266" s="3" t="s">
         <v>10</v>
       </c>
       <c r="E266" s="4" t="s">
-        <v>33</v>
+        <v>12</v>
       </c>
       <c r="F266" s="5" t="s">
         <v>90</v>
@@ -6781,7 +6756,7 @@
         <v>10</v>
       </c>
       <c r="E267" s="4" t="s">
-        <v>12</v>
+        <v>35</v>
       </c>
       <c r="F267" s="5" t="s">
         <v>91</v>
@@ -6796,10 +6771,10 @@
         <v>10</v>
       </c>
       <c r="E268" s="4" t="s">
-        <v>35</v>
+        <v>15</v>
       </c>
       <c r="F268" s="5" t="s">
-        <v>92</v>
+        <v>88</v>
       </c>
       <c r="G268" s="3"/>
     </row>
@@ -6811,67 +6786,73 @@
         <v>10</v>
       </c>
       <c r="E269" s="4" t="s">
-        <v>15</v>
+        <v>441</v>
       </c>
       <c r="F269" s="5" t="s">
-        <v>89</v>
+        <v>438</v>
       </c>
       <c r="G269" s="3"/>
     </row>
-    <row r="270" spans="1:7" ht="28.5" x14ac:dyDescent="0.2">
+    <row r="270" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A270" s="3"/>
       <c r="B270" s="3"/>
       <c r="C270" s="3"/>
-      <c r="D270" s="3" t="s">
+      <c r="D270" s="3"/>
+      <c r="E270" s="4" t="s">
+        <v>445</v>
+      </c>
+      <c r="F270" s="3" t="s">
+        <v>168</v>
+      </c>
+      <c r="G270" s="3"/>
+    </row>
+    <row r="271" spans="1:7" ht="28.5" x14ac:dyDescent="0.2">
+      <c r="A271" s="3"/>
+      <c r="B271" s="3" t="s">
+        <v>447</v>
+      </c>
+      <c r="C271" s="3" t="s">
+        <v>408</v>
+      </c>
+      <c r="D271" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="E270" s="4" t="s">
-        <v>442</v>
-      </c>
-      <c r="F270" s="5" t="s">
-        <v>439</v>
-      </c>
-      <c r="G270" s="3"/>
-    </row>
-    <row r="271" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A271" s="3"/>
-      <c r="B271" s="3"/>
-      <c r="C271" s="3"/>
-      <c r="D271" s="3"/>
       <c r="E271" s="4" t="s">
-        <v>446</v>
-      </c>
-      <c r="F271" s="3" t="s">
-        <v>169</v>
+        <v>74</v>
+      </c>
+      <c r="F271" s="5" t="s">
+        <v>100</v>
       </c>
       <c r="G271" s="3"/>
     </row>
-    <row r="272" spans="1:7" ht="28.5" x14ac:dyDescent="0.2">
-      <c r="A272" s="3"/>
-      <c r="B272" s="3" t="s">
-        <v>448</v>
-      </c>
-      <c r="C272" s="3" t="s">
+    <row r="272" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A272" s="3" t="s">
+        <v>98</v>
+      </c>
+      <c r="B272" s="3"/>
+      <c r="C272" s="3"/>
+      <c r="D272" s="3"/>
+      <c r="E272" s="4"/>
+      <c r="F272" s="3"/>
+      <c r="G272" s="3"/>
+    </row>
+    <row r="273" spans="1:7" ht="28.5" x14ac:dyDescent="0.2">
+      <c r="A273" s="3"/>
+      <c r="B273" s="3" t="s">
+        <v>101</v>
+      </c>
+      <c r="C273" s="3" t="s">
         <v>409</v>
       </c>
-      <c r="D272" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="E272" s="4" t="s">
-        <v>74</v>
-      </c>
-      <c r="F272" s="5" t="s">
-        <v>101</v>
-      </c>
-      <c r="G272" s="3"/>
-    </row>
-    <row r="273" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A273" s="3"/>
-      <c r="B273" s="3"/>
-      <c r="C273" s="3"/>
-      <c r="D273" s="3"/>
-      <c r="E273" s="4"/>
-      <c r="F273" s="3"/>
+      <c r="D273" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E273" s="4" t="s">
+        <v>76</v>
+      </c>
+      <c r="F273" s="5" t="s">
+        <v>103</v>
+      </c>
       <c r="G273" s="3"/>
     </row>
     <row r="274" spans="1:7" x14ac:dyDescent="0.2">
@@ -6879,23 +6860,23 @@
       <c r="B274" s="3"/>
       <c r="C274" s="3"/>
       <c r="D274" s="3"/>
-      <c r="E274" s="4"/>
-      <c r="F274" s="3"/>
+      <c r="E274" s="4" t="s">
+        <v>77</v>
+      </c>
+      <c r="F274" s="3" t="s">
+        <v>32</v>
+      </c>
       <c r="G274" s="3"/>
     </row>
     <row r="275" spans="1:7" ht="28.5" x14ac:dyDescent="0.2">
       <c r="A275" s="3"/>
-      <c r="B275" s="3" t="s">
-        <v>102</v>
-      </c>
-      <c r="C275" s="3" t="s">
-        <v>410</v>
-      </c>
+      <c r="B275" s="3"/>
+      <c r="C275" s="3"/>
       <c r="D275" s="3" t="s">
         <v>8</v>
       </c>
       <c r="E275" s="4" t="s">
-        <v>76</v>
+        <v>156</v>
       </c>
       <c r="F275" s="5" t="s">
         <v>104</v>
@@ -6908,10 +6889,10 @@
       <c r="C276" s="3"/>
       <c r="D276" s="3"/>
       <c r="E276" s="4" t="s">
-        <v>77</v>
+        <v>157</v>
       </c>
       <c r="F276" s="3" t="s">
-        <v>32</v>
+        <v>105</v>
       </c>
       <c r="G276" s="3"/>
     </row>
@@ -6923,10 +6904,10 @@
         <v>8</v>
       </c>
       <c r="E277" s="4" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="F277" s="5" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="G277" s="3"/>
     </row>
@@ -6936,380 +6917,390 @@
       <c r="C278" s="3"/>
       <c r="D278" s="3"/>
       <c r="E278" s="4" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="F278" s="3" t="s">
-        <v>106</v>
+        <v>32</v>
       </c>
       <c r="G278" s="3"/>
     </row>
     <row r="279" spans="1:7" ht="28.5" x14ac:dyDescent="0.2">
       <c r="A279" s="3"/>
-      <c r="B279" s="3"/>
-      <c r="C279" s="3"/>
+      <c r="B279" s="3" t="s">
+        <v>107</v>
+      </c>
+      <c r="C279" s="3" t="s">
+        <v>410</v>
+      </c>
       <c r="D279" s="3" t="s">
-        <v>8</v>
+        <v>109</v>
       </c>
       <c r="E279" s="4" t="s">
-        <v>159</v>
+        <v>110</v>
       </c>
       <c r="F279" s="5" t="s">
-        <v>107</v>
+        <v>112</v>
       </c>
       <c r="G279" s="3"/>
     </row>
-    <row r="280" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="280" spans="1:7" ht="28.5" x14ac:dyDescent="0.2">
       <c r="A280" s="3"/>
       <c r="B280" s="3"/>
       <c r="C280" s="3"/>
-      <c r="D280" s="3"/>
+      <c r="D280" s="3" t="s">
+        <v>109</v>
+      </c>
       <c r="E280" s="4" t="s">
-        <v>160</v>
-      </c>
-      <c r="F280" s="3" t="s">
-        <v>32</v>
+        <v>111</v>
+      </c>
+      <c r="F280" s="5" t="s">
+        <v>113</v>
       </c>
       <c r="G280" s="3"/>
     </row>
     <row r="281" spans="1:7" ht="28.5" x14ac:dyDescent="0.2">
       <c r="A281" s="3"/>
-      <c r="B281" s="3" t="s">
-        <v>108</v>
-      </c>
-      <c r="C281" s="3" t="s">
-        <v>411</v>
-      </c>
+      <c r="B281" s="3"/>
+      <c r="C281" s="3"/>
       <c r="D281" s="3" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="E281" s="4" t="s">
-        <v>111</v>
+        <v>440</v>
       </c>
       <c r="F281" s="5" t="s">
-        <v>113</v>
+        <v>439</v>
       </c>
       <c r="G281" s="3"/>
     </row>
-    <row r="282" spans="1:7" ht="28.5" x14ac:dyDescent="0.2">
+    <row r="282" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A282" s="3"/>
       <c r="B282" s="3"/>
       <c r="C282" s="3"/>
-      <c r="D282" s="3" t="s">
-        <v>110</v>
-      </c>
+      <c r="D282" s="3"/>
       <c r="E282" s="4" t="s">
-        <v>112</v>
-      </c>
-      <c r="F282" s="5" t="s">
-        <v>114</v>
+        <v>446</v>
+      </c>
+      <c r="F282" s="3" t="s">
+        <v>32</v>
       </c>
       <c r="G282" s="3"/>
     </row>
     <row r="283" spans="1:7" ht="28.5" x14ac:dyDescent="0.2">
       <c r="A283" s="3"/>
-      <c r="B283" s="3"/>
-      <c r="C283" s="3"/>
+      <c r="B283" s="3" t="s">
+        <v>114</v>
+      </c>
+      <c r="C283" s="3" t="s">
+        <v>411</v>
+      </c>
       <c r="D283" s="3" t="s">
+        <v>116</v>
+      </c>
+      <c r="E283" s="4" t="s">
         <v>110</v>
       </c>
-      <c r="E283" s="4" t="s">
-        <v>441</v>
-      </c>
       <c r="F283" s="5" t="s">
-        <v>440</v>
+        <v>118</v>
       </c>
       <c r="G283" s="3"/>
     </row>
-    <row r="284" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="284" spans="1:7" ht="28.5" x14ac:dyDescent="0.2">
       <c r="A284" s="3"/>
       <c r="B284" s="3"/>
       <c r="C284" s="3"/>
-      <c r="D284" s="3"/>
+      <c r="D284" s="3" t="s">
+        <v>116</v>
+      </c>
       <c r="E284" s="4" t="s">
-        <v>447</v>
-      </c>
-      <c r="F284" s="3" t="s">
-        <v>32</v>
+        <v>111</v>
+      </c>
+      <c r="F284" s="5" t="s">
+        <v>119</v>
       </c>
       <c r="G284" s="3"/>
     </row>
     <row r="285" spans="1:7" ht="28.5" x14ac:dyDescent="0.2">
       <c r="A285" s="3"/>
-      <c r="B285" s="3" t="s">
-        <v>115</v>
-      </c>
-      <c r="C285" s="3" t="s">
-        <v>412</v>
-      </c>
+      <c r="B285" s="3"/>
+      <c r="C285" s="3"/>
       <c r="D285" s="3" t="s">
+        <v>116</v>
+      </c>
+      <c r="E285" s="4" t="s">
         <v>117</v>
       </c>
-      <c r="E285" s="4" t="s">
-        <v>111</v>
-      </c>
       <c r="F285" s="5" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="G285" s="3"/>
     </row>
-    <row r="286" spans="1:7" ht="28.5" x14ac:dyDescent="0.2">
+    <row r="286" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A286" s="3"/>
       <c r="B286" s="3"/>
       <c r="C286" s="3"/>
-      <c r="D286" s="3" t="s">
-        <v>117</v>
-      </c>
+      <c r="D286" s="3"/>
       <c r="E286" s="4" t="s">
-        <v>112</v>
+        <v>122</v>
       </c>
       <c r="F286" s="5" t="s">
-        <v>120</v>
+        <v>32</v>
       </c>
       <c r="G286" s="3"/>
     </row>
     <row r="287" spans="1:7" ht="28.5" x14ac:dyDescent="0.2">
       <c r="A287" s="3"/>
-      <c r="B287" s="3"/>
-      <c r="C287" s="3"/>
+      <c r="B287" s="3" t="s">
+        <v>121</v>
+      </c>
+      <c r="C287" s="3" t="s">
+        <v>412</v>
+      </c>
       <c r="D287" s="3" t="s">
-        <v>117</v>
+        <v>123</v>
       </c>
       <c r="E287" s="4" t="s">
-        <v>118</v>
+        <v>110</v>
       </c>
       <c r="F287" s="5" t="s">
-        <v>121</v>
+        <v>112</v>
       </c>
       <c r="G287" s="3"/>
     </row>
-    <row r="288" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="288" spans="1:7" ht="28.5" x14ac:dyDescent="0.2">
       <c r="A288" s="3"/>
       <c r="B288" s="3"/>
       <c r="C288" s="3"/>
       <c r="D288" s="3"/>
       <c r="E288" s="4" t="s">
-        <v>123</v>
+        <v>111</v>
       </c>
       <c r="F288" s="5" t="s">
-        <v>32</v>
+        <v>113</v>
       </c>
       <c r="G288" s="3"/>
     </row>
     <row r="289" spans="1:7" ht="28.5" x14ac:dyDescent="0.2">
       <c r="A289" s="3"/>
-      <c r="B289" s="3" t="s">
-        <v>122</v>
-      </c>
-      <c r="C289" s="3" t="s">
-        <v>413</v>
-      </c>
-      <c r="D289" s="3" t="s">
-        <v>124</v>
-      </c>
+      <c r="B289" s="3"/>
+      <c r="C289" s="3"/>
+      <c r="D289" s="3"/>
       <c r="E289" s="4" t="s">
-        <v>111</v>
+        <v>440</v>
       </c>
       <c r="F289" s="5" t="s">
-        <v>113</v>
+        <v>190</v>
       </c>
       <c r="G289" s="3"/>
     </row>
-    <row r="290" spans="1:7" ht="28.5" x14ac:dyDescent="0.2">
+    <row r="290" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A290" s="3"/>
       <c r="B290" s="3"/>
       <c r="C290" s="3"/>
       <c r="D290" s="3"/>
       <c r="E290" s="4" t="s">
-        <v>112</v>
-      </c>
-      <c r="F290" s="5" t="s">
-        <v>114</v>
+        <v>446</v>
+      </c>
+      <c r="F290" s="3" t="s">
+        <v>32</v>
       </c>
       <c r="G290" s="3"/>
     </row>
-    <row r="291" spans="1:7" ht="28.5" x14ac:dyDescent="0.2">
-      <c r="A291" s="3"/>
+    <row r="291" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A291" s="3" t="s">
+        <v>124</v>
+      </c>
       <c r="B291" s="3"/>
       <c r="C291" s="3"/>
       <c r="D291" s="3"/>
-      <c r="E291" s="4" t="s">
-        <v>441</v>
-      </c>
-      <c r="F291" s="5" t="s">
-        <v>191</v>
-      </c>
+      <c r="E291" s="4"/>
+      <c r="F291" s="3"/>
       <c r="G291" s="3"/>
     </row>
     <row r="292" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A292" s="3"/>
-      <c r="B292" s="3"/>
-      <c r="C292" s="3"/>
-      <c r="D292" s="3"/>
+      <c r="B292" s="3" t="s">
+        <v>135</v>
+      </c>
+      <c r="C292" s="3" t="s">
+        <v>413</v>
+      </c>
+      <c r="D292" s="3" t="s">
+        <v>123</v>
+      </c>
       <c r="E292" s="4" t="s">
-        <v>447</v>
+        <v>145</v>
       </c>
       <c r="F292" s="3" t="s">
-        <v>32</v>
+        <v>146</v>
       </c>
       <c r="G292" s="3"/>
     </row>
     <row r="293" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A293" s="3" t="s">
-        <v>125</v>
-      </c>
-      <c r="B293" s="3"/>
-      <c r="C293" s="3"/>
-      <c r="D293" s="3"/>
-      <c r="E293" s="4"/>
-      <c r="F293" s="3"/>
+      <c r="A293" s="3"/>
+      <c r="B293" s="3" t="s">
+        <v>136</v>
+      </c>
+      <c r="C293" s="3" t="s">
+        <v>414</v>
+      </c>
+      <c r="D293" s="3" t="s">
+        <v>123</v>
+      </c>
+      <c r="E293" s="4" t="s">
+        <v>145</v>
+      </c>
+      <c r="F293" s="3" t="s">
+        <v>147</v>
+      </c>
       <c r="G293" s="3"/>
     </row>
     <row r="294" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A294" s="3"/>
       <c r="B294" s="3" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="C294" s="3" t="s">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="D294" s="3" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="E294" s="4" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="F294" s="3" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="G294" s="3"/>
     </row>
     <row r="295" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A295" s="3"/>
       <c r="B295" s="3" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="C295" s="3" t="s">
-        <v>415</v>
+        <v>426</v>
       </c>
       <c r="D295" s="3" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="E295" s="4" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="F295" s="3" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="G295" s="3"/>
     </row>
     <row r="296" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A296" s="3"/>
       <c r="B296" s="3" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="C296" s="3" t="s">
-        <v>416</v>
+        <v>427</v>
       </c>
       <c r="D296" s="3" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="E296" s="4" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="F296" s="3" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="G296" s="3"/>
     </row>
     <row r="297" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A297" s="3"/>
       <c r="B297" s="3" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="C297" s="3" t="s">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="D297" s="3" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="E297" s="4" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="F297" s="3" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="G297" s="3"/>
     </row>
     <row r="298" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A298" s="3"/>
       <c r="B298" s="3" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="C298" s="3" t="s">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="D298" s="3" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="E298" s="4" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="F298" s="3" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="G298" s="3"/>
     </row>
     <row r="299" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A299" s="3"/>
       <c r="B299" s="3" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="C299" s="3" t="s">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="D299" s="3" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="E299" s="4" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="F299" s="3" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="G299" s="3"/>
     </row>
     <row r="300" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A300" s="3"/>
       <c r="B300" s="3" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="C300" s="3" t="s">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="D300" s="3" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="E300" s="4" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="F300" s="3" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="G300" s="3"/>
     </row>
     <row r="301" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A301" s="3"/>
       <c r="B301" s="3" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="C301" s="3" t="s">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="D301" s="3" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="E301" s="4" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="F301" s="3" t="s">
         <v>154</v>
@@ -7318,40 +7309,20 @@
     </row>
     <row r="302" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A302" s="3"/>
-      <c r="B302" s="3" t="s">
-        <v>144</v>
-      </c>
-      <c r="C302" s="3" t="s">
-        <v>432</v>
-      </c>
-      <c r="D302" s="3" t="s">
-        <v>124</v>
-      </c>
-      <c r="E302" s="4" t="s">
-        <v>146</v>
-      </c>
-      <c r="F302" s="3" t="s">
-        <v>156</v>
-      </c>
+      <c r="B302" s="3"/>
+      <c r="C302" s="3"/>
+      <c r="D302" s="3"/>
+      <c r="E302" s="4"/>
+      <c r="F302" s="3"/>
       <c r="G302" s="3"/>
     </row>
     <row r="303" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A303" s="3"/>
-      <c r="B303" s="3" t="s">
-        <v>145</v>
-      </c>
-      <c r="C303" s="3" t="s">
-        <v>433</v>
-      </c>
-      <c r="D303" s="3" t="s">
-        <v>124</v>
-      </c>
-      <c r="E303" s="4" t="s">
-        <v>146</v>
-      </c>
-      <c r="F303" s="3" t="s">
-        <v>155</v>
-      </c>
+      <c r="B303" s="3"/>
+      <c r="C303" s="3"/>
+      <c r="D303" s="3"/>
+      <c r="E303" s="4"/>
+      <c r="F303" s="5"/>
       <c r="G303" s="3"/>
     </row>
     <row r="304" spans="1:7" x14ac:dyDescent="0.2">
@@ -7369,7 +7340,7 @@
       <c r="C305" s="3"/>
       <c r="D305" s="3"/>
       <c r="E305" s="4"/>
-      <c r="F305" s="5"/>
+      <c r="F305" s="3"/>
       <c r="G305" s="3"/>
     </row>
     <row r="306" spans="1:7" x14ac:dyDescent="0.2">
@@ -9667,8 +9638,7 @@
       <c r="F560" s="3"/>
       <c r="G560" s="3"/>
     </row>
-    <row r="561" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A561" s="3"/>
+    <row r="561" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B561" s="3"/>
       <c r="C561" s="3"/>
       <c r="D561" s="3"/>
@@ -9676,8 +9646,7 @@
       <c r="F561" s="3"/>
       <c r="G561" s="3"/>
     </row>
-    <row r="562" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A562" s="3"/>
+    <row r="562" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B562" s="3"/>
       <c r="C562" s="3"/>
       <c r="D562" s="3"/>
@@ -9685,7 +9654,7 @@
       <c r="F562" s="3"/>
       <c r="G562" s="3"/>
     </row>
-    <row r="563" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="563" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B563" s="3"/>
       <c r="C563" s="3"/>
       <c r="D563" s="3"/>
@@ -9693,7 +9662,7 @@
       <c r="F563" s="3"/>
       <c r="G563" s="3"/>
     </row>
-    <row r="564" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="564" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B564" s="3"/>
       <c r="C564" s="3"/>
       <c r="D564" s="3"/>
@@ -9701,7 +9670,7 @@
       <c r="F564" s="3"/>
       <c r="G564" s="3"/>
     </row>
-    <row r="565" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="565" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B565" s="3"/>
       <c r="C565" s="3"/>
       <c r="D565" s="3"/>
@@ -9709,7 +9678,7 @@
       <c r="F565" s="3"/>
       <c r="G565" s="3"/>
     </row>
-    <row r="566" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="566" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B566" s="3"/>
       <c r="C566" s="3"/>
       <c r="D566" s="3"/>
@@ -9717,7 +9686,7 @@
       <c r="F566" s="3"/>
       <c r="G566" s="3"/>
     </row>
-    <row r="567" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="567" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B567" s="3"/>
       <c r="C567" s="3"/>
       <c r="D567" s="3"/>
@@ -9725,7 +9694,7 @@
       <c r="F567" s="3"/>
       <c r="G567" s="3"/>
     </row>
-    <row r="568" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="568" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B568" s="3"/>
       <c r="C568" s="3"/>
       <c r="D568" s="3"/>
@@ -9733,7 +9702,7 @@
       <c r="F568" s="3"/>
       <c r="G568" s="3"/>
     </row>
-    <row r="569" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="569" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B569" s="3"/>
       <c r="C569" s="3"/>
       <c r="D569" s="3"/>
@@ -9741,7 +9710,7 @@
       <c r="F569" s="3"/>
       <c r="G569" s="3"/>
     </row>
-    <row r="570" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="570" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B570" s="3"/>
       <c r="C570" s="3"/>
       <c r="D570" s="3"/>
@@ -9749,7 +9718,7 @@
       <c r="F570" s="3"/>
       <c r="G570" s="3"/>
     </row>
-    <row r="571" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="571" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B571" s="3"/>
       <c r="C571" s="3"/>
       <c r="D571" s="3"/>
@@ -9757,7 +9726,7 @@
       <c r="F571" s="3"/>
       <c r="G571" s="3"/>
     </row>
-    <row r="572" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="572" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B572" s="3"/>
       <c r="C572" s="3"/>
       <c r="D572" s="3"/>
@@ -9765,40 +9734,24 @@
       <c r="F572" s="3"/>
       <c r="G572" s="3"/>
     </row>
-    <row r="573" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="573" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B573" s="3"/>
       <c r="C573" s="3"/>
       <c r="D573" s="3"/>
-      <c r="E573" s="4"/>
+      <c r="E573" s="3"/>
       <c r="F573" s="3"/>
       <c r="G573" s="3"/>
     </row>
-    <row r="574" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="574" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B574" s="3"/>
       <c r="C574" s="3"/>
       <c r="D574" s="3"/>
-      <c r="E574" s="4"/>
-      <c r="F574" s="3"/>
+      <c r="E574" s="3"/>
       <c r="G574" s="3"/>
     </row>
-    <row r="575" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="575" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B575" s="3"/>
-      <c r="C575" s="3"/>
-      <c r="D575" s="3"/>
-      <c r="E575" s="3"/>
-      <c r="F575" s="3"/>
       <c r="G575" s="3"/>
-    </row>
-    <row r="576" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="B576" s="3"/>
-      <c r="C576" s="3"/>
-      <c r="D576" s="3"/>
-      <c r="E576" s="3"/>
-      <c r="G576" s="3"/>
-    </row>
-    <row r="577" spans="2:7" x14ac:dyDescent="0.2">
-      <c r="B577" s="3"/>
-      <c r="G577" s="3"/>
     </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>

--- a/rtl/pbit_register_file.xlsx
+++ b/rtl/pbit_register_file.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Study_material\Study_material\Pbit\pbit_kings\pbit_kings\rtl\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{388BEF30-27AD-4423-A56C-9533B99C327C}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D6632C4D-425F-41F0-BACA-B8C3F8749817}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="15360" windowHeight="12645" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
